--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D25FF87-4DC0-4CAF-9D70-B72C162998CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFD7B2EC-3F1B-4978-8BE4-3555D9428547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="461">
   <si>
     <t>Titel</t>
   </si>
@@ -278,12 +278,15 @@
     <t>"Beslagbeslissing"@nl</t>
   </si>
   <si>
-    <t>"Een feitelijke beslissing over wat er (op grond van een bepaalde wettelijke bepaling) met een beslagvoorwerp moet gebeuren."@nl</t>
+    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
   </si>
   <si>
     <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
   </si>
   <si>
+    <t>ChatGPT – Semantic Review 02</t>
+  </si>
+  <si>
     <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
   </si>
   <si>
@@ -356,7 +359,7 @@
     <t>"Beslaggebeurtenis"@nl</t>
   </si>
   <si>
-    <t>"Een handeling ten aanzien van een beslag."@nl</t>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
@@ -365,9 +368,6 @@
     <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
   </si>
   <si>
-    <t>"EB 2026-05-01: Bestaat er (al) een volledige lijst van alle voorkomende beslaghandelingen?"@nl</t>
-  </si>
-  <si>
     <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
   </si>
   <si>
@@ -383,7 +383,7 @@
     <t>"Beslagproces"@nl</t>
   </si>
   <si>
-    <t>"De verzameling van beslaghandelingen die heeft plaatsgevonden in de afhandeling van een beslag."@nl</t>
+    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
@@ -392,7 +392,7 @@
     <t>"Beslagrol"@nl</t>
   </si>
   <si>
-    <t>"Een rol van een persoon ten aanzien van een beslag."@nl</t>
+    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
   </si>
   <si>
     <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
@@ -1350,6 +1350,9 @@
   </si>
   <si>
     <t>Besluitname</t>
+  </si>
+  <si>
+    <t>Definitie aangescherpt en proces/activiteit verduidelijkt.</t>
   </si>
   <si>
     <t>PROV</t>
@@ -1413,7 +1416,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1424,13 +1427,23 @@
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1450,9 +1463,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -2117,7 +2131,7 @@
       <c r="D11" t="s">
         <v>82</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="2" t="s">
         <v>83</v>
       </c>
       <c r="L11" t="s">
@@ -2126,13 +2140,13 @@
       <c r="AJ11" t="s">
         <v>48</v>
       </c>
-      <c r="AO11" t="s">
-        <v>64</v>
+      <c r="AO11" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2141,19 +2155,19 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ12" t="s">
         <v>48</v>
       </c>
       <c r="AO12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
@@ -2167,19 +2181,19 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R13" t="s">
         <v>71</v>
       </c>
       <c r="X13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AJ13" t="s">
         <v>48</v>
@@ -2190,7 +2204,7 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
@@ -2199,18 +2213,18 @@
         <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AO14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
@@ -2219,13 +2233,13 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AJ15" t="s">
         <v>48</v>
@@ -2236,7 +2250,7 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
@@ -2245,16 +2259,16 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R16" t="s">
         <v>71</v>
@@ -2268,7 +2282,7 @@
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s">
         <v>43</v>
@@ -2277,28 +2291,28 @@
         <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" t="s">
         <v>109</v>
       </c>
+      <c r="J17" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AJ17" t="s">
         <v>48</v>
       </c>
-      <c r="AO17" t="s">
-        <v>112</v>
+      <c r="AO17" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
@@ -2337,7 +2351,7 @@
       <c r="D19" t="s">
         <v>117</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="2" t="s">
         <v>118</v>
       </c>
       <c r="R19" t="s">
@@ -2346,10 +2360,13 @@
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
+      <c r="AO19" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
@@ -2360,7 +2377,7 @@
       <c r="D20" t="s">
         <v>120</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="2" t="s">
         <v>121</v>
       </c>
       <c r="L20" t="s">
@@ -2371,6 +2388,9 @@
       </c>
       <c r="AJ20" t="s">
         <v>48</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -2413,7 +2433,7 @@
         <v>130</v>
       </c>
       <c r="AO22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
@@ -2488,7 +2508,7 @@
         <v>142</v>
       </c>
       <c r="W25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ25" t="s">
         <v>48</v>
@@ -2543,7 +2563,7 @@
         <v>48</v>
       </c>
       <c r="AO27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
@@ -2572,7 +2592,7 @@
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
@@ -2592,7 +2612,7 @@
         <v>157</v>
       </c>
       <c r="P29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R29" t="s">
         <v>158</v>
@@ -2670,13 +2690,13 @@
         <v>170</v>
       </c>
       <c r="W32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AJ32" t="s">
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
@@ -2702,7 +2722,7 @@
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
@@ -2797,7 +2817,7 @@
         <v>188</v>
       </c>
       <c r="W37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ37" t="s">
         <v>48</v>
@@ -2849,7 +2869,7 @@
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
@@ -2901,7 +2921,7 @@
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
@@ -2930,7 +2950,7 @@
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
@@ -3082,7 +3102,7 @@
         <v>225</v>
       </c>
       <c r="P49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R49" t="s">
         <v>155</v>
@@ -3134,7 +3154,7 @@
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
@@ -3232,7 +3252,7 @@
         <v>245</v>
       </c>
       <c r="AO55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
@@ -3321,7 +3341,7 @@
         <v>257</v>
       </c>
       <c r="AO59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
@@ -3603,7 +3623,7 @@
         <v>296</v>
       </c>
       <c r="W71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AJ71" t="s">
         <v>48</v>
@@ -3661,7 +3681,7 @@
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
@@ -3779,7 +3799,7 @@
         <v>316</v>
       </c>
       <c r="L78" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ78" t="s">
         <v>48</v>
@@ -3877,7 +3897,7 @@
         <v>328</v>
       </c>
       <c r="R82" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ82" t="s">
         <v>48</v>
@@ -4067,7 +4087,7 @@
         <v>353</v>
       </c>
       <c r="W90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ90" t="s">
         <v>48</v>
@@ -4116,7 +4136,7 @@
         <v>359</v>
       </c>
       <c r="W92" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ92" t="s">
         <v>48</v>
@@ -4191,7 +4211,7 @@
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
@@ -4286,7 +4306,7 @@
         <v>375</v>
       </c>
       <c r="W99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ99" t="s">
         <v>48</v>
@@ -4381,7 +4401,7 @@
         <v>392</v>
       </c>
       <c r="W103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AJ103" t="s">
         <v>48</v>
@@ -4522,7 +4542,7 @@
         <v>410</v>
       </c>
       <c r="L109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R109" t="s">
         <v>411</v>
@@ -4534,7 +4554,7 @@
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
@@ -4688,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4733,6 +4753,50 @@
       </c>
       <c r="C4" t="s">
         <v>438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -4753,7 +4817,7 @@
         <v>434</v>
       </c>
       <c r="C1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,10 +4825,10 @@
         <v>436</v>
       </c>
       <c r="B2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4772,10 +4836,10 @@
         <v>439</v>
       </c>
       <c r="B3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C3" t="s">
         <v>444</v>
-      </c>
-      <c r="C3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,87 +4847,87 @@
         <v>440</v>
       </c>
       <c r="B4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" t="s">
         <v>444</v>
-      </c>
-      <c r="C4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" t="s">
         <v>448</v>
-      </c>
-      <c r="B6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B9" t="s">
+        <v>457</v>
+      </c>
+      <c r="C9" t="s">
         <v>455</v>
-      </c>
-      <c r="B9" t="s">
-        <v>456</v>
-      </c>
-      <c r="C9" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" t="s">
         <v>459</v>
       </c>
-      <c r="B11" t="s">
-        <v>458</v>
-      </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFD7B2EC-3F1B-4978-8BE4-3555D9428547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A77FE9-6264-4885-91CD-FA3D8397C23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="437">
   <si>
     <t>Titel</t>
   </si>
@@ -239,9 +239,6 @@
     <t>"Beslag bewaring"@nl</t>
   </si>
   <si>
-    <t>Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust.</t>
-  </si>
-  <si>
     <t>Begrip:Id-0c79c3d8-bdd3-b152-fa07-ac4cad6f33a7</t>
   </si>
   <si>
@@ -1337,86 +1334,17 @@
     <t>Toelichting</t>
   </si>
   <si>
-    <t>Beslag beheer</t>
-  </si>
-  <si>
-    <t>Inhoudelijk</t>
-  </si>
-  <si>
-    <t>Definitie aangescherpt.</t>
-  </si>
-  <si>
-    <t>Beslag bewaring</t>
-  </si>
-  <si>
-    <t>Besluitname</t>
-  </si>
-  <si>
-    <t>Definitie aangescherpt en proces/activiteit verduidelijkt.</t>
-  </si>
-  <si>
     <t>PROV</t>
   </si>
   <si>
-    <t>Proces</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Activiteit</t>
-  </si>
-  <si>
-    <t>Beslagbeheerder</t>
-  </si>
-  <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>Beslagbewaarder</t>
-  </si>
-  <si>
-    <t>Beslagportaal</t>
-  </si>
-  <si>
-    <t>Informatiesysteem</t>
-  </si>
-  <si>
-    <t>Agent?</t>
-  </si>
-  <si>
-    <t>Beslagvoorwerp</t>
-  </si>
-  <si>
-    <t>Voorwerp</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Beslagzaak</t>
-  </si>
-  <si>
-    <t>Zaak</t>
-  </si>
-  <si>
-    <t>Beslag</t>
-  </si>
-  <si>
-    <t>Juridisch begrip</t>
-  </si>
-  <si>
-    <t>Beslagbeslissing</t>
+    <t>"Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust."@nl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1431,6 +1359,23 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1460,15 +1405,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1773,6 +1723,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="9.140625" style="4"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1802,7 +1755,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1915,7 +1868,7 @@
       <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W2" t="s">
@@ -1941,7 +1894,7 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="W3" t="s">
@@ -1967,7 +1920,7 @@
       <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
         <v>55</v>
       </c>
       <c r="AJ4" t="s">
@@ -1987,7 +1940,7 @@
       <c r="D5" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="AJ5" t="s">
@@ -2010,7 +1963,7 @@
       <c r="D6" t="s">
         <v>61</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="4" t="s">
         <v>62</v>
       </c>
       <c r="P6" t="s">
@@ -2036,7 +1989,7 @@
       <c r="D7" t="s">
         <v>66</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AJ7" t="s">
@@ -2056,8 +2009,8 @@
       <c r="D8" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>70</v>
+      <c r="J8" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
@@ -2068,106 +2021,106 @@
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
         <v>71</v>
       </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="J9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J9" t="s">
+      <c r="R9" t="s">
         <v>73</v>
       </c>
-      <c r="R9" t="s">
+      <c r="T9" t="s">
         <v>74</v>
       </c>
-      <c r="T9" t="s">
+      <c r="AJ9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO9" t="s">
         <v>75</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="J10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J10" t="s">
+      <c r="AJ10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO10" t="s">
         <v>79</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="J11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" t="s">
         <v>83</v>
       </c>
-      <c r="L11" t="s">
+      <c r="AJ11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO11" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO11" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
         <v>86</v>
       </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="J12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>88</v>
       </c>
-      <c r="L12" t="s">
+      <c r="AJ12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO12" t="s">
         <v>89</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
@@ -2181,65 +2134,65 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" t="s">
+        <v>70</v>
+      </c>
+      <c r="X13" t="s">
         <v>92</v>
       </c>
-      <c r="L13" t="s">
-        <v>89</v>
-      </c>
-      <c r="R13" t="s">
-        <v>71</v>
-      </c>
-      <c r="X13" t="s">
-        <v>93</v>
-      </c>
       <c r="AJ13" t="s">
         <v>48</v>
       </c>
       <c r="AO13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>94</v>
       </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="J14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J14" t="s">
+      <c r="AO14" t="s">
         <v>96</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
         <v>98</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="J15" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J15" t="s">
+      <c r="W15" t="s">
         <v>100</v>
-      </c>
-      <c r="W15" t="s">
-        <v>101</v>
       </c>
       <c r="AJ15" t="s">
         <v>48</v>
@@ -2250,123 +2203,123 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
         <v>102</v>
       </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>103</v>
       </c>
-      <c r="E16" t="s">
+      <c r="J16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J16" t="s">
+      <c r="Q16" t="s">
         <v>105</v>
       </c>
-      <c r="Q16" t="s">
-        <v>106</v>
-      </c>
       <c r="R16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="s">
         <v>48</v>
       </c>
       <c r="AO16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
         <v>107</v>
       </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>108</v>
       </c>
-      <c r="E17" t="s">
+      <c r="J17" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="M17" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" t="s">
         <v>110</v>
       </c>
-      <c r="M17" t="s">
-        <v>89</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="X17" t="s">
         <v>111</v>
       </c>
-      <c r="X17" t="s">
-        <v>112</v>
-      </c>
       <c r="AJ17" t="s">
         <v>48</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
         <v>113</v>
       </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="J18" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J18" t="s">
-        <v>115</v>
-      </c>
       <c r="AJ18" t="s">
         <v>48</v>
       </c>
       <c r="AO18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="J19" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="R19" t="s">
         <v>118</v>
       </c>
-      <c r="R19" t="s">
-        <v>119</v>
-      </c>
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
@@ -2375,163 +2328,163 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="L20" t="s">
         <v>121</v>
       </c>
-      <c r="L20" t="s">
+      <c r="X20" t="s">
         <v>122</v>
       </c>
-      <c r="X20" t="s">
-        <v>123</v>
-      </c>
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
         <v>124</v>
       </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="J21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J21" t="s">
+      <c r="AJ21" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO21" t="s">
         <v>126</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
         <v>128</v>
       </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="J22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="J22" t="s">
-        <v>130</v>
-      </c>
       <c r="AO22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
         <v>131</v>
       </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>132</v>
       </c>
-      <c r="E23" t="s">
+      <c r="J23" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="J23" t="s">
+      <c r="L23" t="s">
         <v>134</v>
       </c>
-      <c r="L23" t="s">
-        <v>135</v>
-      </c>
       <c r="AJ23" t="s">
         <v>48</v>
       </c>
       <c r="AO23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
         <v>136</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="J24" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="J24" t="s">
-        <v>138</v>
-      </c>
       <c r="AJ24" t="s">
         <v>48</v>
       </c>
       <c r="AO24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
         <v>139</v>
       </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>140</v>
       </c>
-      <c r="E25" t="s">
+      <c r="J25" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J25" t="s">
+      <c r="W25" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO25" t="s">
         <v>142</v>
-      </c>
-      <c r="W25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
         <v>144</v>
       </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="J26" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
@@ -2542,80 +2495,80 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
         <v>147</v>
       </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="J27" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J27" t="s">
+      <c r="L27" t="s">
         <v>149</v>
       </c>
-      <c r="L27" t="s">
-        <v>150</v>
-      </c>
       <c r="AJ27" t="s">
         <v>48</v>
       </c>
       <c r="AO27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
         <v>151</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="J28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="J28" t="s">
+      <c r="R28" t="s">
         <v>153</v>
       </c>
-      <c r="R28" t="s">
-        <v>154</v>
-      </c>
       <c r="S28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="s">
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
         <v>155</v>
       </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="J29" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="J29" t="s">
+      <c r="P29" t="s">
+        <v>101</v>
+      </c>
+      <c r="R29" t="s">
         <v>157</v>
-      </c>
-      <c r="P29" t="s">
-        <v>102</v>
-      </c>
-      <c r="R29" t="s">
-        <v>158</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2623,126 +2576,126 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
         <v>159</v>
       </c>
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="J30" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="J30" t="s">
-        <v>161</v>
-      </c>
       <c r="AJ30" t="s">
         <v>48</v>
       </c>
       <c r="AO30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
         <v>162</v>
       </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="J31" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J31" t="s">
+      <c r="L31" t="s">
         <v>164</v>
       </c>
-      <c r="L31" t="s">
+      <c r="S31" t="s">
         <v>165</v>
       </c>
-      <c r="S31" t="s">
+      <c r="AJ31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO31" t="s">
         <v>166</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
         <v>168</v>
       </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="J32" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="J32" t="s">
-        <v>170</v>
-      </c>
       <c r="W32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ32" t="s">
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
         <v>171</v>
       </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="J33" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="J33" t="s">
+      <c r="S33" t="s">
         <v>173</v>
       </c>
-      <c r="S33" t="s">
-        <v>174</v>
-      </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
         <v>175</v>
       </c>
-      <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="J34" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="J34" t="s">
+      <c r="P34" t="s">
         <v>177</v>
-      </c>
-      <c r="P34" t="s">
-        <v>178</v>
       </c>
       <c r="AJ34" t="s">
         <v>48</v>
@@ -2753,48 +2706,48 @@
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
         <v>179</v>
       </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="J35" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="J35" t="s">
-        <v>181</v>
-      </c>
       <c r="AJ35" t="s">
         <v>48</v>
       </c>
       <c r="AO35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
         <v>182</v>
       </c>
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="J36" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="J36" t="s">
+      <c r="L36" t="s">
         <v>184</v>
       </c>
-      <c r="L36" t="s">
-        <v>185</v>
-      </c>
       <c r="R36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2802,22 +2755,22 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
         <v>186</v>
       </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="J37" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J37" t="s">
-        <v>188</v>
-      </c>
       <c r="W37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AJ37" t="s">
         <v>48</v>
@@ -2828,19 +2781,19 @@
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
         <v>189</v>
       </c>
-      <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="J38" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="J38" t="s">
-        <v>191</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2848,56 +2801,56 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
         <v>192</v>
       </c>
-      <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>193</v>
       </c>
-      <c r="E39" t="s">
+      <c r="J39" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="J39" t="s">
-        <v>195</v>
-      </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
         <v>196</v>
       </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="J40" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="J40" t="s">
-        <v>198</v>
-      </c>
       <c r="AJ40" t="s">
         <v>48</v>
       </c>
       <c r="AO40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -2906,91 +2859,91 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
+        <v>198</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="J41" t="s">
-        <v>200</v>
-      </c>
       <c r="R41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ41" t="s">
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
         <v>201</v>
       </c>
-      <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>202</v>
       </c>
-      <c r="F42" t="s">
+      <c r="J42" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="J42" t="s">
+      <c r="L42" t="s">
         <v>204</v>
       </c>
-      <c r="L42" t="s">
-        <v>205</v>
-      </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" t="s">
         <v>206</v>
       </c>
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="J43" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="J43" t="s">
-        <v>208</v>
-      </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
         <v>209</v>
       </c>
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="J44" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="J44" t="s">
-        <v>211</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -2998,88 +2951,88 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>211</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
         <v>212</v>
       </c>
-      <c r="B45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="J45" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J45" t="s">
-        <v>214</v>
-      </c>
       <c r="AJ45" t="s">
         <v>48</v>
       </c>
       <c r="AO45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
         <v>215</v>
       </c>
-      <c r="B46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="J46" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="J46" t="s">
-        <v>217</v>
-      </c>
       <c r="AJ46" t="s">
         <v>48</v>
       </c>
       <c r="AO46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
         <v>218</v>
       </c>
-      <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="J47" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="J47" t="s">
-        <v>220</v>
-      </c>
       <c r="AJ47" t="s">
         <v>48</v>
       </c>
       <c r="AO47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
         <v>221</v>
       </c>
-      <c r="B48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="J48" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="J48" t="s">
-        <v>223</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3087,7 +3040,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3096,16 +3049,16 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
+        <v>223</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J49" t="s">
-        <v>225</v>
-      </c>
       <c r="P49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3122,10 +3075,10 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
+        <v>225</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="J50" t="s">
-        <v>227</v>
       </c>
       <c r="Q50" t="s">
         <v>60</v>
@@ -3136,48 +3089,48 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
         <v>228</v>
       </c>
-      <c r="B51" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="J51" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J51" t="s">
-        <v>230</v>
-      </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>230</v>
+      </c>
+      <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
         <v>231</v>
       </c>
-      <c r="B52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="G52" t="s">
         <v>232</v>
       </c>
-      <c r="G52" t="s">
+      <c r="J52" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="J52" t="s">
-        <v>234</v>
-      </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3185,255 +3138,255 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
         <v>235</v>
       </c>
-      <c r="B53" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="J53" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="J53" t="s">
+      <c r="R53" t="s">
         <v>237</v>
       </c>
-      <c r="R53" t="s">
+      <c r="S53" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO53" t="s">
         <v>238</v>
-      </c>
-      <c r="S53" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO53" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>239</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
         <v>240</v>
       </c>
-      <c r="B54" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="J54" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="J54" t="s">
-        <v>242</v>
-      </c>
       <c r="AJ54" t="s">
         <v>48</v>
       </c>
       <c r="AO54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>242</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" t="s">
         <v>243</v>
       </c>
-      <c r="B55" t="s">
-        <v>43</v>
-      </c>
-      <c r="C55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="J55" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="J55" t="s">
-        <v>245</v>
-      </c>
       <c r="AO55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>245</v>
+      </c>
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" t="s">
         <v>246</v>
       </c>
-      <c r="B56" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="J56" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="J56" t="s">
-        <v>248</v>
-      </c>
       <c r="AJ56" t="s">
         <v>48</v>
       </c>
       <c r="AO56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>248</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" t="s">
         <v>249</v>
       </c>
-      <c r="B57" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="J57" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="J57" t="s">
-        <v>251</v>
-      </c>
       <c r="AJ57" t="s">
         <v>48</v>
       </c>
       <c r="AO57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>251</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" t="s">
         <v>252</v>
       </c>
-      <c r="B58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="J58" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="J58" t="s">
-        <v>254</v>
-      </c>
       <c r="AJ58" t="s">
         <v>48</v>
       </c>
       <c r="AO58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" t="s">
         <v>255</v>
       </c>
-      <c r="B59" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="J59" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="J59" t="s">
-        <v>257</v>
-      </c>
       <c r="AO59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>257</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" t="s">
         <v>258</v>
       </c>
-      <c r="B60" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="J60" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J60" t="s">
-        <v>260</v>
-      </c>
       <c r="AJ60" t="s">
         <v>48</v>
       </c>
       <c r="AO60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>260</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" t="s">
         <v>261</v>
       </c>
-      <c r="B61" t="s">
-        <v>43</v>
-      </c>
-      <c r="C61" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="J61" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="J61" t="s">
+      <c r="S61" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO61" t="s">
         <v>263</v>
-      </c>
-      <c r="S61" t="s">
-        <v>174</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO61" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>264</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" t="s">
         <v>265</v>
       </c>
-      <c r="B62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="J62" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="J62" t="s">
+      <c r="S62" t="s">
         <v>267</v>
       </c>
-      <c r="S62" t="s">
+      <c r="AJ62" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO62" t="s">
         <v>268</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO62" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" t="s">
         <v>270</v>
       </c>
-      <c r="B63" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="J63" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="J63" t="s">
-        <v>272</v>
       </c>
       <c r="AJ63" t="s">
         <v>48</v>
@@ -3444,88 +3397,88 @@
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>272</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" t="s">
         <v>273</v>
       </c>
-      <c r="B64" t="s">
-        <v>43</v>
-      </c>
-      <c r="C64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="J64" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="J64" t="s">
-        <v>275</v>
-      </c>
       <c r="AJ64" t="s">
         <v>48</v>
       </c>
       <c r="AO64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>275</v>
+      </c>
+      <c r="B65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
         <v>276</v>
       </c>
-      <c r="B65" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="J65" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="J65" t="s">
-        <v>278</v>
-      </c>
       <c r="AJ65" t="s">
         <v>48</v>
       </c>
       <c r="AO65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
         <v>279</v>
       </c>
-      <c r="B66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C66" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="J66" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="J66" t="s">
-        <v>281</v>
-      </c>
       <c r="AJ66" t="s">
         <v>48</v>
       </c>
       <c r="AO66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>281</v>
+      </c>
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
         <v>282</v>
       </c>
-      <c r="B67" t="s">
-        <v>43</v>
-      </c>
-      <c r="C67" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="J67" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="J67" t="s">
-        <v>284</v>
       </c>
       <c r="AJ67" t="s">
         <v>48</v>
@@ -3536,7 +3489,7 @@
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3545,16 +3498,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
+        <v>284</v>
+      </c>
+      <c r="J68" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="J68" t="s">
+      <c r="Q68" t="s">
+        <v>174</v>
+      </c>
+      <c r="T68" t="s">
         <v>286</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>175</v>
-      </c>
-      <c r="T68" t="s">
-        <v>287</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3562,45 +3515,45 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>287</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" t="s">
         <v>288</v>
       </c>
-      <c r="B69" t="s">
-        <v>43</v>
-      </c>
-      <c r="C69" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="J69" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="J69" t="s">
-        <v>290</v>
-      </c>
       <c r="AJ69" t="s">
         <v>48</v>
       </c>
       <c r="AO69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C70" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" t="s">
         <v>291</v>
       </c>
-      <c r="B70" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="J70" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="J70" t="s">
-        <v>293</v>
-      </c>
       <c r="R70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AJ70" t="s">
         <v>48</v>
@@ -3608,22 +3561,22 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>293</v>
+      </c>
+      <c r="B71" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" t="s">
         <v>294</v>
       </c>
-      <c r="B71" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="J71" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="J71" t="s">
-        <v>296</v>
-      </c>
       <c r="W71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s">
         <v>48</v>
@@ -3634,7 +3587,7 @@
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3643,16 +3596,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
+        <v>296</v>
+      </c>
+      <c r="J72" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="J72" t="s">
+      <c r="S72" t="s">
+        <v>177</v>
+      </c>
+      <c r="T72" t="s">
         <v>298</v>
-      </c>
-      <c r="S72" t="s">
-        <v>178</v>
-      </c>
-      <c r="T72" t="s">
-        <v>299</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3660,120 +3613,120 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>299</v>
+      </c>
+      <c r="B73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" t="s">
         <v>300</v>
       </c>
-      <c r="B73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="J73" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="J73" t="s">
-        <v>302</v>
-      </c>
       <c r="S73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>302</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" t="s">
         <v>303</v>
       </c>
-      <c r="B74" t="s">
-        <v>43</v>
-      </c>
-      <c r="C74" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="J74" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="J74" t="s">
-        <v>305</v>
-      </c>
       <c r="AJ74" t="s">
         <v>48</v>
       </c>
       <c r="AO74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>305</v>
+      </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" t="s">
         <v>306</v>
       </c>
-      <c r="B75" t="s">
-        <v>43</v>
-      </c>
-      <c r="C75" t="s">
-        <v>44</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="J75" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="J75" t="s">
-        <v>308</v>
-      </c>
       <c r="AJ75" t="s">
         <v>48</v>
       </c>
       <c r="AO75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>237</v>
+      </c>
+      <c r="B76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" t="s">
+        <v>308</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="R76" t="s">
+        <v>234</v>
+      </c>
+      <c r="S76" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO76" t="s">
         <v>238</v>
-      </c>
-      <c r="B76" t="s">
-        <v>43</v>
-      </c>
-      <c r="C76" t="s">
-        <v>44</v>
-      </c>
-      <c r="D76" t="s">
-        <v>309</v>
-      </c>
-      <c r="J76" t="s">
-        <v>310</v>
-      </c>
-      <c r="R76" t="s">
-        <v>235</v>
-      </c>
-      <c r="S76" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ76" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO76" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>310</v>
+      </c>
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" t="s">
         <v>311</v>
       </c>
-      <c r="B77" t="s">
-        <v>43</v>
-      </c>
-      <c r="C77" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="J77" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="J77" t="s">
-        <v>313</v>
       </c>
       <c r="AJ77" t="s">
         <v>48</v>
@@ -3784,22 +3737,22 @@
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>313</v>
+      </c>
+      <c r="B78" t="s">
+        <v>43</v>
+      </c>
+      <c r="C78" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" t="s">
         <v>314</v>
       </c>
-      <c r="B78" t="s">
-        <v>43</v>
-      </c>
-      <c r="C78" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="J78" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="J78" t="s">
-        <v>316</v>
-      </c>
       <c r="L78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AJ78" t="s">
         <v>48</v>
@@ -3810,120 +3763,120 @@
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>316</v>
+      </c>
+      <c r="B79" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" t="s">
         <v>317</v>
       </c>
-      <c r="B79" t="s">
-        <v>43</v>
-      </c>
-      <c r="C79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="J79" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="J79" t="s">
-        <v>319</v>
-      </c>
       <c r="AJ79" t="s">
         <v>48</v>
       </c>
       <c r="AO79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>319</v>
+      </c>
+      <c r="B80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" t="s">
         <v>320</v>
       </c>
-      <c r="B80" t="s">
-        <v>43</v>
-      </c>
-      <c r="C80" t="s">
-        <v>44</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="J80" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="J80" t="s">
-        <v>322</v>
-      </c>
       <c r="S80" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
       </c>
       <c r="AO80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>322</v>
+      </c>
+      <c r="B81" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" t="s">
         <v>323</v>
       </c>
-      <c r="B81" t="s">
-        <v>43</v>
-      </c>
-      <c r="C81" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="J81" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="J81" t="s">
-        <v>325</v>
-      </c>
       <c r="AJ81" t="s">
         <v>48</v>
       </c>
       <c r="AO81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>43</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
         <v>326</v>
       </c>
-      <c r="B82" t="s">
-        <v>43</v>
-      </c>
-      <c r="C82" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="J82" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="J82" t="s">
+      <c r="R82" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ82" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO82" t="s">
         <v>328</v>
-      </c>
-      <c r="R82" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ82" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO82" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>329</v>
+      </c>
+      <c r="B83" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" t="s">
         <v>330</v>
       </c>
-      <c r="B83" t="s">
-        <v>43</v>
-      </c>
-      <c r="C83" t="s">
-        <v>44</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="J83" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="J83" t="s">
+      <c r="L83" t="s">
         <v>332</v>
-      </c>
-      <c r="L83" t="s">
-        <v>333</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
@@ -3934,91 +3887,91 @@
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>333</v>
+      </c>
+      <c r="B84" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" t="s">
         <v>334</v>
       </c>
-      <c r="B84" t="s">
-        <v>43</v>
-      </c>
-      <c r="C84" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="J84" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="J84" t="s">
-        <v>336</v>
-      </c>
       <c r="AJ84" t="s">
         <v>48</v>
       </c>
       <c r="AO84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>336</v>
+      </c>
+      <c r="B85" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" t="s">
         <v>337</v>
       </c>
-      <c r="B85" t="s">
-        <v>43</v>
-      </c>
-      <c r="C85" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="J85" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="J85" t="s">
-        <v>339</v>
-      </c>
       <c r="AJ85" t="s">
         <v>48</v>
       </c>
       <c r="AO85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>339</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" t="s">
         <v>340</v>
       </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>341</v>
-      </c>
-      <c r="J86" t="s">
-        <v>339</v>
+      <c r="J86" s="4" t="s">
+        <v>338</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
       </c>
       <c r="AO86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>341</v>
+      </c>
+      <c r="B87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" t="s">
         <v>342</v>
       </c>
-      <c r="B87" t="s">
-        <v>43</v>
-      </c>
-      <c r="C87" t="s">
-        <v>44</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="J87" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="J87" t="s">
-        <v>344</v>
-      </c>
       <c r="P87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4026,313 +3979,313 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>344</v>
+      </c>
+      <c r="B88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" t="s">
         <v>345</v>
       </c>
-      <c r="B88" t="s">
-        <v>43</v>
-      </c>
-      <c r="C88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="J88" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="J88" t="s">
-        <v>347</v>
-      </c>
       <c r="AJ88" t="s">
         <v>48</v>
       </c>
       <c r="AO88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>347</v>
+      </c>
+      <c r="B89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" t="s">
         <v>348</v>
       </c>
-      <c r="B89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C89" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="J89" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="J89" t="s">
-        <v>350</v>
-      </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>350</v>
+      </c>
+      <c r="B90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" t="s">
         <v>351</v>
       </c>
-      <c r="B90" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" t="s">
-        <v>44</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="J90" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="J90" t="s">
-        <v>353</v>
-      </c>
       <c r="W90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AJ90" t="s">
         <v>48</v>
       </c>
       <c r="AO90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>353</v>
+      </c>
+      <c r="B91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" t="s">
         <v>354</v>
       </c>
-      <c r="B91" t="s">
-        <v>43</v>
-      </c>
-      <c r="C91" t="s">
-        <v>44</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="J91" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="J91" t="s">
-        <v>356</v>
-      </c>
       <c r="AJ91" t="s">
         <v>48</v>
       </c>
       <c r="AO91" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>356</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" t="s">
         <v>357</v>
       </c>
-      <c r="B92" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="J92" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="J92" t="s">
-        <v>359</v>
-      </c>
       <c r="W92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AJ92" t="s">
         <v>48</v>
       </c>
       <c r="AO92" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>359</v>
+      </c>
+      <c r="B93" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" t="s">
         <v>360</v>
       </c>
-      <c r="B93" t="s">
-        <v>43</v>
-      </c>
-      <c r="C93" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="J93" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="J93" t="s">
-        <v>362</v>
-      </c>
       <c r="AJ93" t="s">
         <v>48</v>
       </c>
       <c r="AO93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>362</v>
+      </c>
+      <c r="B94" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" t="s">
         <v>363</v>
       </c>
-      <c r="B94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="J94" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="J94" t="s">
-        <v>365</v>
-      </c>
       <c r="AJ94" t="s">
         <v>48</v>
       </c>
       <c r="AO94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" t="s">
+        <v>43</v>
+      </c>
+      <c r="C95" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" t="s">
         <v>366</v>
       </c>
-      <c r="B95" t="s">
-        <v>43</v>
-      </c>
-      <c r="C95" t="s">
-        <v>44</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="J95" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="J95" t="s">
-        <v>368</v>
-      </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>368</v>
+      </c>
+      <c r="B96" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" t="s">
         <v>369</v>
       </c>
-      <c r="B96" t="s">
-        <v>43</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="J96" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="J96" t="s">
-        <v>371</v>
-      </c>
       <c r="AJ96" t="s">
         <v>48</v>
       </c>
       <c r="AO96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>371</v>
+      </c>
+      <c r="B97" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" t="s">
         <v>372</v>
       </c>
-      <c r="B97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" t="s">
-        <v>44</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="J97" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="J97" t="s">
-        <v>374</v>
-      </c>
       <c r="AJ97" t="s">
         <v>48</v>
       </c>
       <c r="AO97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>374</v>
+      </c>
+      <c r="B98" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" t="s">
         <v>375</v>
       </c>
-      <c r="B98" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="J98" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="J98" t="s">
+      <c r="R98" t="s">
         <v>377</v>
       </c>
-      <c r="R98" t="s">
-        <v>378</v>
-      </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>377</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" t="s">
         <v>378</v>
       </c>
-      <c r="B99" t="s">
-        <v>43</v>
-      </c>
-      <c r="C99" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="J99" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="J99" t="s">
-        <v>380</v>
-      </c>
       <c r="R99" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="W99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AJ99" t="s">
         <v>48</v>
       </c>
       <c r="AO99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>380</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" t="s">
         <v>381</v>
       </c>
-      <c r="B100" t="s">
-        <v>43</v>
-      </c>
-      <c r="C100" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="J100" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="J100" t="s">
-        <v>383</v>
-      </c>
       <c r="S100" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4340,194 +4293,194 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>383</v>
+      </c>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" t="s">
         <v>384</v>
       </c>
-      <c r="B101" t="s">
-        <v>43</v>
-      </c>
-      <c r="C101" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="J101" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="J101" t="s">
-        <v>386</v>
-      </c>
       <c r="AJ101" t="s">
         <v>48</v>
       </c>
       <c r="AO101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>386</v>
+      </c>
+      <c r="B102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" t="s">
         <v>387</v>
       </c>
-      <c r="B102" t="s">
-        <v>43</v>
-      </c>
-      <c r="C102" t="s">
-        <v>44</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="J102" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="J102" t="s">
-        <v>389</v>
-      </c>
       <c r="AJ102" t="s">
         <v>48</v>
       </c>
       <c r="AO102" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>389</v>
+      </c>
+      <c r="B103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C103" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" t="s">
         <v>390</v>
       </c>
-      <c r="B103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C103" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="J103" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="J103" t="s">
+      <c r="W103" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ103" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO103" t="s">
         <v>392</v>
-      </c>
-      <c r="W103" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ103" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO103" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>393</v>
+      </c>
+      <c r="B104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" t="s">
         <v>394</v>
       </c>
-      <c r="B104" t="s">
-        <v>43</v>
-      </c>
-      <c r="C104" t="s">
-        <v>44</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="J104" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="J104" t="s">
-        <v>396</v>
-      </c>
       <c r="AJ104" t="s">
         <v>48</v>
       </c>
       <c r="AO104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>396</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" t="s">
         <v>397</v>
       </c>
-      <c r="B105" t="s">
-        <v>43</v>
-      </c>
-      <c r="C105" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="J105" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="J105" t="s">
-        <v>399</v>
-      </c>
       <c r="AJ105" t="s">
         <v>48</v>
       </c>
       <c r="AO105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>399</v>
+      </c>
+      <c r="B106" t="s">
+        <v>43</v>
+      </c>
+      <c r="C106" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" t="s">
         <v>400</v>
       </c>
-      <c r="B106" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" t="s">
-        <v>44</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="J106" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="J106" t="s">
-        <v>402</v>
-      </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>402</v>
+      </c>
+      <c r="B107" t="s">
+        <v>43</v>
+      </c>
+      <c r="C107" t="s">
+        <v>44</v>
+      </c>
+      <c r="D107" t="s">
         <v>403</v>
       </c>
-      <c r="B107" t="s">
-        <v>43</v>
-      </c>
-      <c r="C107" t="s">
-        <v>44</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="J107" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="J107" t="s">
-        <v>405</v>
-      </c>
       <c r="AJ107" t="s">
         <v>48</v>
       </c>
       <c r="AO107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>405</v>
+      </c>
+      <c r="B108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108" t="s">
+        <v>44</v>
+      </c>
+      <c r="D108" t="s">
         <v>406</v>
       </c>
-      <c r="B108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C108" t="s">
-        <v>44</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="J108" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="J108" t="s">
-        <v>408</v>
-      </c>
       <c r="AJ108" t="s">
         <v>48</v>
       </c>
       <c r="AO108" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4536,48 +4489,48 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
+        <v>408</v>
+      </c>
+      <c r="J109" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="J109" t="s">
+      <c r="L109" t="s">
+        <v>88</v>
+      </c>
+      <c r="R109" t="s">
         <v>410</v>
       </c>
-      <c r="L109" t="s">
+      <c r="T109" t="s">
+        <v>411</v>
+      </c>
+      <c r="AJ109" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO109" t="s">
         <v>89</v>
-      </c>
-      <c r="R109" t="s">
-        <v>411</v>
-      </c>
-      <c r="T109" t="s">
-        <v>412</v>
-      </c>
-      <c r="AJ109" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO109" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>412</v>
+      </c>
+      <c r="B110" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" t="s">
         <v>413</v>
       </c>
-      <c r="B110" t="s">
-        <v>43</v>
-      </c>
-      <c r="C110" t="s">
-        <v>44</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>414</v>
       </c>
-      <c r="E110" t="s">
+      <c r="J110" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="J110" t="s">
-        <v>416</v>
-      </c>
       <c r="R110" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4585,50 +4538,50 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>416</v>
+      </c>
+      <c r="B111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" t="s">
+        <v>44</v>
+      </c>
+      <c r="D111" t="s">
         <v>417</v>
       </c>
-      <c r="B111" t="s">
-        <v>43</v>
-      </c>
-      <c r="C111" t="s">
-        <v>44</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="J111" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="J111" t="s">
-        <v>419</v>
-      </c>
       <c r="AJ111" t="s">
         <v>48</v>
       </c>
       <c r="AO111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>419</v>
+      </c>
+      <c r="B112" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" t="s">
+        <v>44</v>
+      </c>
+      <c r="D112" t="s">
         <v>420</v>
       </c>
-      <c r="B112" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" t="s">
-        <v>44</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="J112" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="J112" t="s">
+      <c r="AI112" t="s">
         <v>422</v>
-      </c>
-      <c r="AI112" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4637,16 +4590,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
+        <v>423</v>
+      </c>
+      <c r="J113" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="J113" t="s">
+      <c r="Q113" t="s">
+        <v>341</v>
+      </c>
+      <c r="T113" t="s">
         <v>425</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>342</v>
-      </c>
-      <c r="T113" t="s">
-        <v>426</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4654,19 +4607,19 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>426</v>
+      </c>
+      <c r="B114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" t="s">
         <v>427</v>
       </c>
-      <c r="B114" t="s">
-        <v>43</v>
-      </c>
-      <c r="C114" t="s">
-        <v>44</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="J114" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="J114" t="s">
-        <v>429</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4680,123 +4633,52 @@
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>429</v>
+      </c>
+      <c r="B115" t="s">
+        <v>43</v>
+      </c>
+      <c r="C115" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" t="s">
         <v>430</v>
       </c>
-      <c r="B115" t="s">
-        <v>43</v>
-      </c>
-      <c r="C115" t="s">
-        <v>44</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="J115" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="J115" t="s">
-        <v>432</v>
-      </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J30" r:id="rId1" xr:uid="{5D7A6E1D-005A-4356-9DEB-92E97E8666C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B1" t="s">
         <v>433</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>434</v>
-      </c>
-      <c r="C1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C4" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" t="s">
-        <v>437</v>
-      </c>
-      <c r="C7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8" t="s">
-        <v>437</v>
-      </c>
-      <c r="C8" t="s">
-        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -4806,128 +4688,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B1" t="s">
         <v>433</v>
       </c>
-      <c r="B1" t="s">
-        <v>434</v>
-      </c>
       <c r="C1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C5" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>449</v>
-      </c>
-      <c r="B6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>450</v>
-      </c>
-      <c r="B7" t="s">
-        <v>451</v>
-      </c>
-      <c r="C7" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B8" t="s">
-        <v>454</v>
-      </c>
-      <c r="C8" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>456</v>
-      </c>
-      <c r="B9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>458</v>
-      </c>
-      <c r="B10" t="s">
-        <v>459</v>
-      </c>
-      <c r="C10" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>460</v>
-      </c>
-      <c r="B11" t="s">
-        <v>459</v>
-      </c>
-      <c r="C11" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A77FE9-6264-4885-91CD-FA3D8397C23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB6C730-E912-42F2-AD01-AB1A2A5ED5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="448">
   <si>
     <t>Titel</t>
   </si>
@@ -200,285 +200,273 @@
     <t>Begrip:Id-eaea5461-5322-95aa-10d5-da9bda358feb</t>
   </si>
   <si>
-    <t>"Beslag beheer"@nl</t>
-  </si>
-  <si>
-    <t>Het geheel van activiteiten gericht op het administreren, bewaren en afwikkelen van strafvorderlijk beslag.</t>
-  </si>
-  <si>
     <t>ChatGPT – Semantic Review 01</t>
   </si>
   <si>
     <t>Begrip:Id-e9d43e6f-32ce-5056-6947-21b0e0343469</t>
   </si>
   <si>
-    <t>"Beslag bewaarlocatie"@nl</t>
-  </si>
-  <si>
-    <t>"Een locatie waar beslagvoorwerpen worden bewaard."@nl</t>
+    <t>"Een locatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
   </si>
   <si>
     <t>Begrip:Id-0f48dc14-e263-3478-30c9-1a4e99473cbc</t>
   </si>
   <si>
+    <t>Begrip:Id-2ffe6d0f-df5f-7c71-8829-1da2adf6a17c</t>
+  </si>
+  <si>
+    <t>"Een afgebakende ruimte binnen een beslagbewaarlocatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1691472e-de30-fd37-242a-4023c87e3bde</t>
+  </si>
+  <si>
+    <t>"Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0c79c3d8-bdd3-b152-fa07-ac4cad6f33a7</t>
+  </si>
+  <si>
+    <t>"Beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Het strafvorderlijk dwangmiddel beslag dat rust op een voorwerp op basis van een beslaggrondslag met een beslagdoel."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d","Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9","Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e"</t>
+  </si>
+  <si>
+    <t>"Overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-3989598e-4421-f771-2c30-be4aaabbe84b</t>
+  </si>
+  <si>
+    <t>"Beslagbeheerder"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon of organisatie die verantwoordelijk is voor het beheer van in beslag genomen voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>"ChatGPT"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-245ba0cc-b46c-3743-f8ee-c976743b48cc</t>
+  </si>
+  <si>
+    <t>"Beslagbeslissing"@nl</t>
+  </si>
+  <si>
+    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
+  </si>
+  <si>
+    <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
+  </si>
+  <si>
+    <t>ChatGPT – Semantic Review 02</t>
+  </si>
+  <si>
+    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarder"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon of organisatie die verantwoordelijk is voor de feitelijke bewaring van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>"@nl"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagdoel"@nl</t>
+  </si>
+  <si>
+    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
+  </si>
+  <si>
+    <t>"Beslagdossier"@nl</t>
+  </si>
+  <si>
+    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
+  </si>
+  <si>
+    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
+  </si>
+  <si>
+    <t>"Beslagene"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
+  </si>
+  <si>
     <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-2ffe6d0f-df5f-7c71-8829-1da2adf6a17c</t>
-  </si>
-  <si>
-    <t>"Beslag bewaarruimte"@nl</t>
-  </si>
-  <si>
-    <t>"Een locatie binnen een beslag bewaarlocatie waar beslagvoorwerpen worden bewaard."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1691472e-de30-fd37-242a-4023c87e3bde</t>
-  </si>
-  <si>
-    <t>"Beslag bewaring"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0c79c3d8-bdd3-b152-fa07-ac4cad6f33a7</t>
-  </si>
-  <si>
-    <t>"Beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Het strafvorderlijk dwangmiddel beslag dat rust op een voorwerp op basis van een beslaggrondslag met een beslagdoel."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d","Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9","Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e"</t>
-  </si>
-  <si>
-    <t>"Overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-3989598e-4421-f771-2c30-be4aaabbe84b</t>
-  </si>
-  <si>
-    <t>"Beslagbeheerder"@nl</t>
-  </si>
-  <si>
-    <t>"Persoon of organisatie die verantwoordelijk is voor het beheer van in beslag genomen voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>"ChatGPT"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-245ba0cc-b46c-3743-f8ee-c976743b48cc</t>
-  </si>
-  <si>
-    <t>"Beslagbeslissing"@nl</t>
-  </si>
-  <si>
-    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
-  </si>
-  <si>
-    <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
-  </si>
-  <si>
-    <t>ChatGPT – Semantic Review 02</t>
-  </si>
-  <si>
-    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
-  </si>
-  <si>
-    <t>"Beslagbewaarder"@nl</t>
-  </si>
-  <si>
-    <t>"Een persoon die belast is met de bewaring van voorwerpen waarop beslag is toegepast."@nl</t>
-  </si>
-  <si>
-    <t>"@nl"@nl</t>
+    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
+  </si>
+  <si>
+    <t>"Beslaggrondslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagtitel"@nl</t>
+  </si>
+  <si>
+    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
+  </si>
+  <si>
+    <t>"Beslaghandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Beslaggebeurtenis"@nl</t>
+  </si>
+  <si>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
+  </si>
+  <si>
+    <t>"Beslagportaal"@nl</t>
+  </si>
+  <si>
+    <t>"Informatiesysteem voor de registratie en ondersteuning van processen rondom strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
+  </si>
+  <si>
+    <t>"Beslagproces"@nl</t>
+  </si>
+  <si>
+    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
+  </si>
+  <si>
+    <t>"Beslagrol"@nl</t>
+  </si>
+  <si>
+    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
+  </si>
+  <si>
+    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
+  </si>
+  <si>
+    <t>"Beslagstatus"@nl</t>
+  </si>
+  <si>
+    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
+  </si>
+  <si>
+    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
+  </si>
+  <si>
+    <t>"Beslagstuk"@nl</t>
+  </si>
+  <si>
+    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
+  </si>
+  <si>
+    <t>"Beslagvoorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagobject"@nl</t>
+  </si>
+  <si>
+    <t>"Een voorwerp waarop beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
+  </si>
+  <si>
+    <t>"Beslagzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Samenhangend geheel van gegevens en handelingen met betrekking tot een strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
+  </si>
+  <si>
+    <t>"Beslissen over beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Over beslag beslissen"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
+  </si>
+  <si>
+    <t>"Besluitname"@nl</t>
+  </si>
+  <si>
+    <t>Het vormen en vaststellen van een besluit.</t>
+  </si>
+  <si>
+    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
+  </si>
+  <si>
+    <t>"Bewijs van ontvangst"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
   </si>
   <si>
     <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
   </si>
   <si>
-    <t>"Beslagdoel"@nl</t>
-  </si>
-  <si>
-    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
-  </si>
-  <si>
-    <t>"Beslagdossier"@nl</t>
-  </si>
-  <si>
-    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
-  </si>
-  <si>
-    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
-  </si>
-  <si>
-    <t>"Beslagene"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
-  </si>
-  <si>
-    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
-  </si>
-  <si>
-    <t>"Beslaggrondslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagtitel"@nl</t>
-  </si>
-  <si>
-    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
-  </si>
-  <si>
-    <t>"Beslaghandeling"@nl</t>
-  </si>
-  <si>
-    <t>"Beslaggebeurtenis"@nl</t>
-  </si>
-  <si>
-    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
-  </si>
-  <si>
-    <t>"Beslagportaal"@nl</t>
-  </si>
-  <si>
-    <t>"Informatiesysteem voor de registratie en ondersteuning van processen rondom strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
-  </si>
-  <si>
-    <t>"Beslagproces"@nl</t>
-  </si>
-  <si>
-    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
-  </si>
-  <si>
-    <t>"Beslagrol"@nl</t>
-  </si>
-  <si>
-    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
-  </si>
-  <si>
-    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
-  </si>
-  <si>
-    <t>"Beslagstatus"@nl</t>
-  </si>
-  <si>
-    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
-  </si>
-  <si>
-    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
-  </si>
-  <si>
-    <t>"Beslagstuk"@nl</t>
-  </si>
-  <si>
-    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
-  </si>
-  <si>
-    <t>"Beslagvoorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagobject"@nl</t>
-  </si>
-  <si>
-    <t>"Een voorwerp waarop beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
-  </si>
-  <si>
-    <t>"Beslagzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Samenhangend geheel van gegevens en handelingen met betrekking tot een strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
-  </si>
-  <si>
-    <t>"Beslissen over beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Over beslag beslissen"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
-  </si>
-  <si>
-    <t>"Besluitname"@nl</t>
-  </si>
-  <si>
-    <t>Het vormen en vaststellen van een besluit.</t>
-  </si>
-  <si>
-    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
-  </si>
-  <si>
-    <t>"Bewijs van ontvangst"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
-  </si>
-  <si>
     <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
   </si>
   <si>
@@ -1328,16 +1316,61 @@
     <t>Begrip</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Toelichting</t>
+    <t>Wijziging</t>
+  </si>
+  <si>
+    <t>Motivatie</t>
+  </si>
+  <si>
+    <t>Definitie uitgebreid met verplaatsen.</t>
+  </si>
+  <si>
+    <t>Inhoudelijke aanscherping</t>
+  </si>
+  <si>
+    <t>Definitie aangescherpt.</t>
+  </si>
+  <si>
+    <t>Rol verduidelijkt.</t>
   </si>
   <si>
     <t>PROV</t>
   </si>
   <si>
-    <t>"Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust."@nl</t>
+    <t>Begripstype</t>
+  </si>
+  <si>
+    <t>Activiteit</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Voorziening</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>"Het geheel van activiteiten gericht op het administreren van strafvorderlijk beslag en het beheren van de voorwerpen waarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Beslagbeheer"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarlocatie"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarruimte"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagbewaring"@nl</t>
   </si>
 </sst>
 </file>
@@ -1354,17 +1387,20 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1407,12 +1443,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -1724,7 +1761,7 @@
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="9.140625" style="4"/>
+    <col min="10" max="10" width="9.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -1755,7 +1792,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1868,7 +1905,7 @@
       <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>46</v>
       </c>
       <c r="W2" t="s">
@@ -1894,7 +1931,7 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>52</v>
       </c>
       <c r="W3" t="s">
@@ -1920,7 +1957,7 @@
       <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AJ4" t="s">
@@ -1937,48 +1974,48 @@
       <c r="C5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO5" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" t="s">
         <v>60</v>
       </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" t="s">
-        <v>63</v>
-      </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AO6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
@@ -1986,19 +2023,22 @@
       <c r="C7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>67</v>
+      <c r="D7" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
@@ -2006,51 +2046,51 @@
       <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>436</v>
+      <c r="D8" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="R9" t="s">
+        <v>68</v>
+      </c>
+      <c r="T9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO9" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" t="s">
-        <v>73</v>
-      </c>
-      <c r="T9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
@@ -2059,21 +2099,21 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="AJ10" t="s">
         <v>48</v>
       </c>
       <c r="AO10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -2082,24 +2122,24 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="L11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s">
         <v>48</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2108,19 +2148,19 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="L12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="AJ12" t="s">
         <v>48</v>
       </c>
       <c r="AO12" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
@@ -2134,30 +2174,30 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="R13" t="s">
+        <v>65</v>
+      </c>
+      <c r="X13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO13" t="s">
         <v>70</v>
-      </c>
-      <c r="X13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
@@ -2166,18 +2206,18 @@
         <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="AO14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
@@ -2186,24 +2226,24 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="W15" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="AJ15" t="s">
         <v>48</v>
       </c>
       <c r="AO15" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
@@ -2212,65 +2252,65 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="Q16" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="R16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO16" t="s">
         <v>70</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" t="s">
+        <v>83</v>
+      </c>
+      <c r="R17" t="s">
+        <v>105</v>
+      </c>
+      <c r="X17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="M17" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" t="s">
-        <v>110</v>
-      </c>
-      <c r="X17" t="s">
-        <v>111</v>
-      </c>
       <c r="AJ17" t="s">
         <v>48</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
         <v>43</v>
@@ -2279,21 +2319,21 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="AJ18" t="s">
         <v>48</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
         <v>43</v>
@@ -2302,24 +2342,24 @@
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="R19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
@@ -2328,27 +2368,27 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="L20" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="X20" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
@@ -2357,21 +2397,21 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="AJ21" t="s">
         <v>48</v>
       </c>
       <c r="AO21" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
@@ -2380,18 +2420,18 @@
         <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="AO22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
@@ -2400,27 +2440,27 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="L23" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AJ23" t="s">
         <v>48</v>
       </c>
       <c r="AO23" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
@@ -2429,21 +2469,21 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="AJ24" t="s">
         <v>48</v>
       </c>
       <c r="AO24" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
@@ -2452,27 +2492,27 @@
         <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="W25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ25" t="s">
         <v>48</v>
       </c>
       <c r="AO25" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
@@ -2481,21 +2521,21 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
@@ -2504,24 +2544,24 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="L27" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AJ27" t="s">
         <v>48</v>
       </c>
       <c r="AO27" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
@@ -2530,27 +2570,27 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="R28" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="S28" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="s">
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
@@ -2559,16 +2599,16 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="P29" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="R29" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2576,7 +2616,7 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -2585,50 +2625,50 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
       </c>
       <c r="AO30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L31" t="s">
+        <v>160</v>
+      </c>
+      <c r="S31" t="s">
         <v>161</v>
       </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="AJ31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO31" t="s">
         <v>162</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="L31" t="s">
-        <v>164</v>
-      </c>
-      <c r="S31" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -2637,24 +2677,24 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="W32" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="AJ32" t="s">
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -2663,24 +2703,24 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="S33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -2689,24 +2729,24 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AJ34" t="s">
         <v>48</v>
       </c>
       <c r="AO34" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2715,21 +2755,21 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
       </c>
       <c r="AO35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
@@ -2738,16 +2778,16 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="L36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="R36" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2755,7 +2795,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2764,24 +2804,24 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="W37" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ37" t="s">
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -2790,10 +2830,10 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2801,7 +2841,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2810,24 +2850,24 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -2836,21 +2876,21 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
       </c>
       <c r="AO40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -2859,56 +2899,56 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="R41" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="S41" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ41" t="s">
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" t="s">
+        <v>198</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L42" t="s">
         <v>200</v>
       </c>
-      <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
-        <v>201</v>
-      </c>
-      <c r="F42" t="s">
-        <v>202</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="L42" t="s">
-        <v>204</v>
-      </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -2917,21 +2957,21 @@
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
         <v>43</v>
@@ -2940,10 +2980,10 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -2951,7 +2991,7 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -2960,21 +3000,21 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>212</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
       </c>
       <c r="AO45" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
         <v>43</v>
@@ -2983,21 +3023,21 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
       </c>
       <c r="AO46" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
         <v>43</v>
@@ -3006,21 +3046,21 @@
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>218</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
       </c>
       <c r="AO47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
         <v>43</v>
@@ -3029,10 +3069,10 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>221</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3040,7 +3080,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3049,16 +3089,16 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>223</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="P49" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="R49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3066,7 +3106,7 @@
     </row>
     <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
         <v>43</v>
@@ -3075,13 +3115,13 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>225</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="Q50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AJ50" t="s">
         <v>48</v>
@@ -3089,7 +3129,7 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s">
         <v>43</v>
@@ -3098,21 +3138,21 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>228</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -3121,16 +3161,16 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G52" t="s">
-        <v>232</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="S52" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3138,36 +3178,36 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
+        <v>231</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="R53" t="s">
+        <v>233</v>
+      </c>
+      <c r="S53" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO53" t="s">
         <v>234</v>
-      </c>
-      <c r="B53" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
-        <v>235</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="R53" t="s">
-        <v>237</v>
-      </c>
-      <c r="S53" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO53" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s">
         <v>43</v>
@@ -3176,21 +3216,21 @@
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>240</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
       </c>
       <c r="AO54" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
@@ -3199,18 +3239,18 @@
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>243</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="AO55" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
@@ -3219,21 +3259,21 @@
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>246</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
       </c>
       <c r="AO56" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
@@ -3242,21 +3282,21 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>249</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
       </c>
       <c r="AO57" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B58" t="s">
         <v>43</v>
@@ -3265,21 +3305,21 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>252</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
       </c>
       <c r="AO58" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B59" t="s">
         <v>43</v>
@@ -3288,18 +3328,18 @@
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>255</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="AO59" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -3308,21 +3348,21 @@
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>258</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
       </c>
       <c r="AO60" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
@@ -3331,50 +3371,50 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>261</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="S61" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AJ61" t="s">
         <v>48</v>
       </c>
       <c r="AO61" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>260</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" t="s">
+        <v>261</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="S62" t="s">
+        <v>263</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO62" t="s">
         <v>264</v>
-      </c>
-      <c r="B62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" t="s">
-        <v>265</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="S62" t="s">
-        <v>267</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO62" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -3383,21 +3423,21 @@
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>270</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="AJ63" t="s">
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B64" t="s">
         <v>43</v>
@@ -3406,21 +3446,21 @@
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>273</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>274</v>
+        <v>269</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>270</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
       </c>
       <c r="AO64" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -3429,21 +3469,21 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>276</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>277</v>
+        <v>272</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
       </c>
       <c r="AO65" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
@@ -3452,21 +3492,21 @@
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>279</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
       </c>
       <c r="AO66" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
@@ -3475,21 +3515,21 @@
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>282</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="AJ67" t="s">
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3498,16 +3538,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="Q68" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="T68" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3515,7 +3555,7 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -3524,21 +3564,21 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>288</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>289</v>
+        <v>284</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
       </c>
       <c r="AO69" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -3547,13 +3587,13 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>291</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="R70" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AJ70" t="s">
         <v>48</v>
@@ -3561,7 +3601,7 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B71" t="s">
         <v>43</v>
@@ -3570,24 +3610,24 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>294</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="W71" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="AJ71" t="s">
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3596,16 +3636,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>296</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="S72" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="T72" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3613,7 +3653,7 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -3622,24 +3662,24 @@
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>300</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="S73" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s">
         <v>43</v>
@@ -3648,21 +3688,21 @@
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>303</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
       </c>
       <c r="AO74" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s">
         <v>43</v>
@@ -3671,21 +3711,21 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>306</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
       </c>
       <c r="AO75" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3694,27 +3734,27 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>308</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>309</v>
+        <v>304</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>305</v>
       </c>
       <c r="R76" t="s">
+        <v>230</v>
+      </c>
+      <c r="S76" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO76" t="s">
         <v>234</v>
-      </c>
-      <c r="S76" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ76" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO76" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s">
         <v>43</v>
@@ -3723,21 +3763,21 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>311</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="AJ77" t="s">
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s">
         <v>43</v>
@@ -3746,24 +3786,24 @@
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="L78" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="AJ78" t="s">
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s">
         <v>43</v>
@@ -3772,21 +3812,21 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>317</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>318</v>
+        <v>313</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>314</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
       </c>
       <c r="AO79" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B80" t="s">
         <v>43</v>
@@ -3795,24 +3835,24 @@
         <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>320</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>321</v>
+        <v>316</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="S80" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
       </c>
       <c r="AO80" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B81" t="s">
         <v>43</v>
@@ -3821,21 +3861,21 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>323</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>320</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
       </c>
       <c r="AO81" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B82" t="s">
         <v>43</v>
@@ -3844,24 +3884,24 @@
         <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>326</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>327</v>
+        <v>322</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="R82" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ82" t="s">
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B83" t="s">
         <v>43</v>
@@ -3870,24 +3910,24 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>330</v>
-      </c>
-      <c r="J83" s="4" t="s">
-        <v>331</v>
+        <v>326</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>327</v>
       </c>
       <c r="L83" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s">
         <v>43</v>
@@ -3896,21 +3936,21 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>334</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
       </c>
       <c r="AO84" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B85" t="s">
         <v>43</v>
@@ -3919,21 +3959,21 @@
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>337</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
       </c>
       <c r="AO85" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s">
         <v>43</v>
@@ -3942,21 +3982,21 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>340</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
       </c>
       <c r="AO86" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -3965,13 +4005,13 @@
         <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>342</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>339</v>
       </c>
       <c r="P87" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -3979,7 +4019,7 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -3988,21 +4028,21 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
       </c>
       <c r="AO88" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -4011,21 +4051,21 @@
         <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -4034,24 +4074,24 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>351</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>348</v>
       </c>
       <c r="W90" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ90" t="s">
         <v>48</v>
       </c>
       <c r="AO90" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -4060,21 +4100,21 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>351</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
       </c>
       <c r="AO91" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -4083,24 +4123,24 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>357</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>354</v>
       </c>
       <c r="W92" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ92" t="s">
         <v>48</v>
       </c>
       <c r="AO92" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -4109,21 +4149,21 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
       </c>
       <c r="AO93" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -4132,21 +4172,21 @@
         <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>363</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>360</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
       </c>
       <c r="AO94" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -4155,21 +4195,21 @@
         <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>366</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>363</v>
       </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -4178,21 +4218,21 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>369</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>370</v>
+        <v>365</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
       </c>
       <c r="AO96" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -4201,21 +4241,21 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>372</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
       </c>
       <c r="AO97" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -4224,24 +4264,24 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>375</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>372</v>
       </c>
       <c r="R98" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -4250,27 +4290,27 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>378</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>375</v>
       </c>
       <c r="R99" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W99" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ99" t="s">
         <v>48</v>
       </c>
       <c r="AO99" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -4279,13 +4319,13 @@
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>381</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>378</v>
       </c>
       <c r="S100" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4293,7 +4333,7 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -4302,21 +4342,21 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>384</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
       </c>
       <c r="AO101" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -4325,21 +4365,21 @@
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>387</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>384</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
       </c>
       <c r="AO102" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -4348,24 +4388,24 @@
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>390</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="W103" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AJ103" t="s">
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -4374,21 +4414,21 @@
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>394</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
       </c>
       <c r="AO104" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -4397,21 +4437,21 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>397</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
       </c>
       <c r="AO105" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -4420,21 +4460,21 @@
         <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>400</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>397</v>
       </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -4443,21 +4483,21 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>403</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>400</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
       </c>
       <c r="AO107" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -4466,21 +4506,21 @@
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>406</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>403</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
       </c>
       <c r="AO108" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4489,30 +4529,30 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>408</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>405</v>
       </c>
       <c r="L109" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="R109" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="T109" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AJ109" t="s">
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -4521,16 +4561,16 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E110" t="s">
-        <v>414</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="R110" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4538,7 +4578,7 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -4547,21 +4587,21 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>417</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>414</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
       </c>
       <c r="AO111" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -4570,18 +4610,18 @@
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>420</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>421</v>
+        <v>416</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="AI112" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4590,16 +4630,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>423</v>
-      </c>
-      <c r="J113" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="Q113" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="T113" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4607,7 +4647,7 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -4616,10 +4656,10 @@
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>427</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>424</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4633,7 +4673,7 @@
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -4642,43 +4682,85 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>430</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>427</v>
       </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J30" r:id="rId1" xr:uid="{5D7A6E1D-005A-4356-9DEB-92E97E8666C6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C2" t="s">
         <v>432</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B3" t="s">
         <v>433</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
         <v>434</v>
+      </c>
+      <c r="C5" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4688,21 +4770,66 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>432</v>
+      <c r="A1" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="B1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C1" t="s">
         <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C5" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB6C730-E912-42F2-AD01-AB1A2A5ED5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74601483-0C97-438A-826A-EDBBA5A39931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="454">
   <si>
     <t>Titel</t>
   </si>
@@ -167,7 +167,7 @@
     <t>"Aantonen wederrechtelijk voordeel"@nl</t>
   </si>
   <si>
-    <t>"Het onderbouwen en aannemelijk maken dat een verdachte financieel voordeel heeft behaald uit strafbare feiten, met als doel dit voordeel te kunnen ontnemen (bijvoorbeeld via een ontnemingsmaatregel of beslag)."@nl</t>
+    <t>"Het onderbouwen en aannemelijk maken dat wederrechtelijk verkregen voordeel is behaald, teneinde dit voordeel te kunnen ontnemen."@nl</t>
   </si>
   <si>
     <t>Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c</t>
@@ -176,1134 +176,1152 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>"ChatGPT – Semantic Review 02"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6</t>
+  </si>
+  <si>
+    <t>"Achterhalen waarheid"@nl</t>
+  </si>
+  <si>
+    <t>"Het vaststellen van de feiten en omstandigheden van een strafbaar feit door het verzamelen en onderzoeken van relevante informatie en voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-2f300aa8-6e57-e42c-b962-eb1ad70ee980</t>
+  </si>
+  <si>
+    <t>"Afname afstandverklaring"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij de beslagene of rechthebbende verklaart afstand te doen van een voorwerp waarop beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-eaea5461-5322-95aa-10d5-da9bda358feb</t>
+  </si>
+  <si>
+    <t>"Beslagbeheer"@nl</t>
+  </si>
+  <si>
+    <t>"Het geheel van activiteiten gericht op het administreren van strafvorderlijk beslag en het beheren van de voorwerpen waarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>ChatGPT – Semantic Review 01</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e9d43e6f-32ce-5056-6947-21b0e0343469</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarlocatie"@nl</t>
+  </si>
+  <si>
+    <t>"Een locatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0f48dc14-e263-3478-30c9-1a4e99473cbc</t>
+  </si>
+  <si>
+    <t>Begrip:Id-2ffe6d0f-df5f-7c71-8829-1da2adf6a17c</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarruimte"@nl</t>
+  </si>
+  <si>
+    <t>"Een afgebakende ruimte binnen een beslagbewaarlocatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1691472e-de30-fd37-242a-4023c87e3bde</t>
+  </si>
+  <si>
+    <t>"Beslagbewaring"@nl</t>
+  </si>
+  <si>
+    <t>"Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0c79c3d8-bdd3-b152-fa07-ac4cad6f33a7</t>
+  </si>
+  <si>
+    <t>"Beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Het strafvorderlijk dwangmiddel beslag dat rust op een voorwerp op basis van een beslaggrondslag met een beslagdoel."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d","Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9","Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e"</t>
+  </si>
+  <si>
+    <t>"Overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-3989598e-4421-f771-2c30-be4aaabbe84b</t>
+  </si>
+  <si>
+    <t>"Beslagbeheerder"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon of organisatie die verantwoordelijk is voor het beheer van in beslag genomen voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>"ChatGPT"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-245ba0cc-b46c-3743-f8ee-c976743b48cc</t>
+  </si>
+  <si>
+    <t>"Beslagbeslissing"@nl</t>
+  </si>
+  <si>
+    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
+  </si>
+  <si>
+    <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
+  </si>
+  <si>
+    <t>ChatGPT – Semantic Review 02</t>
+  </si>
+  <si>
+    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarder"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon of organisatie die verantwoordelijk is voor de feitelijke bewaring van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>"@nl"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagdoel"@nl</t>
+  </si>
+  <si>
+    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
+  </si>
+  <si>
+    <t>"Beslagdossier"@nl</t>
+  </si>
+  <si>
+    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
+  </si>
+  <si>
+    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
+  </si>
+  <si>
+    <t>"Beslagene"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
+  </si>
+  <si>
+    <t>"Beslaggrondslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagtitel"@nl</t>
+  </si>
+  <si>
+    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
+  </si>
+  <si>
+    <t>"Beslaghandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Beslaggebeurtenis"@nl</t>
+  </si>
+  <si>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
+  </si>
+  <si>
+    <t>"Beslagportaal"@nl</t>
+  </si>
+  <si>
+    <t>"Informatiesysteem voor de registratie en ondersteuning van processen rondom strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
+  </si>
+  <si>
+    <t>"Beslagproces"@nl</t>
+  </si>
+  <si>
+    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
+  </si>
+  <si>
+    <t>"Beslagrol"@nl</t>
+  </si>
+  <si>
+    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
+  </si>
+  <si>
+    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
+  </si>
+  <si>
+    <t>"Beslagstatus"@nl</t>
+  </si>
+  <si>
+    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
+  </si>
+  <si>
+    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
+  </si>
+  <si>
+    <t>"Beslagstuk"@nl</t>
+  </si>
+  <si>
+    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
+  </si>
+  <si>
+    <t>"Beslagvoorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagobject"@nl</t>
+  </si>
+  <si>
+    <t>"Een voorwerp waarop beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
+  </si>
+  <si>
+    <t>"Beslagzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Samenhangend geheel van gegevens en handelingen met betrekking tot een strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
+  </si>
+  <si>
+    <t>"Beslissen over beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Over beslag beslissen"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
+  </si>
+  <si>
+    <t>"Besluitname"@nl</t>
+  </si>
+  <si>
+    <t>Het vormen en vaststellen van een besluit.</t>
+  </si>
+  <si>
+    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
+  </si>
+  <si>
+    <t>"Bewijs van ontvangst"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
+  </si>
+  <si>
+    <t>"Buitenlands beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
+  </si>
+  <si>
+    <t>"Conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
+  </si>
+  <si>
+    <t>"Deponeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
+  </si>
+  <si>
+    <t>"Dier"@nl</t>
+  </si>
+  <si>
+    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
+  </si>
+  <si>
+    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
+  </si>
+  <si>
+    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
+  </si>
+  <si>
+    <t>"Eigenaar"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
+  </si>
+  <si>
+    <t>"Forensisch onderzoek"@nl</t>
+  </si>
+  <si>
+    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
+  </si>
+  <si>
+    <t>"Functionaris"@nl</t>
+  </si>
+  <si>
+    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
+  </si>
+  <si>
+    <t>"Geldboete"@nl</t>
+  </si>
+  <si>
+    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
+  </si>
+  <si>
+    <t>"Goed"@nl</t>
+  </si>
+  <si>
+    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
+  </si>
+  <si>
+    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
+  </si>
+  <si>
+    <t>"In beslag nemen"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
+  </si>
+  <si>
+    <t>"Inbeheername"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
+  </si>
+  <si>
+    <t>"Inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"Inbeslagname"@nl</t>
+  </si>
+  <si>
+    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
+  </si>
+  <si>
+    <t>"Inbewaringname"@nl</t>
+  </si>
+  <si>
+    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
+  </si>
+  <si>
+    <t>"Internationaal beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
+  </si>
+  <si>
+    <t>"Kennisgeving van inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"KVI"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
+  </si>
+  <si>
+    <t>"Ketenbeslaghuis"@nl</t>
+  </si>
+  <si>
+    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ccfae3bb-46be-0eac-3cf9-8cb4b9301522</t>
+  </si>
+  <si>
+    <t>"Ketenpartner"@nl</t>
+  </si>
+  <si>
+    <t>"De rechtspersoon waarvan de functionaris een rol heeft in het beslagproces."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b92f545-d3f4-7775-845e-2b4d8d7d7339</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag beschikking/arrest ontvangen"@nl</t>
+  </si>
+  <si>
+    <t>"Het ontvangen van een klaagschrift tegen een beschikking of arrest inzake beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c38718ba-8796-ee51-b1af-f20619ea8d7e</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag intrekken"@nl</t>
+  </si>
+  <si>
+    <t>"Het door de indiener beëindigen van een eerder ingediend klaagschrift."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c9e37df7-a24c-7d35-ce7a-93c18f184746</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag ontvangen"@nl</t>
+  </si>
+  <si>
+    <t>"Het ontvangen van een klaagschrift dat betrekking heeft op beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89190bf7-9961-04e0-3769-f03df5a4b1af</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een bij de Rechtspraak ingediende klacht of verzoek ten aanzien van de toepassing van beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Klassiek beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94 Sv."@nl</t>
+  </si>
+  <si>
+    <t>"Locatie"@nl</t>
+  </si>
+  <si>
+    <t>"Een bepaald punt of afgebakend gebied in de ruimte."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-af7b5f03-2b9a-72c0-a1de-2959bc89a3f4</t>
+  </si>
+  <si>
+    <t>"Machtiging tot conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een door de rechter-commissaris verleende machtiging tot het leggen of handhaven van conservatoir beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8</t>
+  </si>
+  <si>
+    <t>"Natuurlijk persoon"@nl</t>
+  </si>
+  <si>
+    <t>"Natuurlijke persoon"@nl</t>
+  </si>
+  <si>
+    <t>"Een mens, in juridische context beschouwd als een drager van subjectieve rechten en plichten."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb</t>
+  </si>
+  <si>
+    <t>"Onroerende zaak"@nl</t>
+  </si>
+  <si>
+    <t>"Grond, nog niet gewonnen delfstoffen, met de grond verenigde beplantingen, alsmede gebouwen en andere werken zoals viaducten die al dan niet rechtstreeks duurzaam met de grond zijn verenigd (wortel en nagelvast)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'. In die definitie wordt art. 3:3.1 BW als bron genoemd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a415d88a-0766-091f-7ea5-e2863a832873</t>
+  </si>
+  <si>
+    <t>"Ontbinden verkoop"@nl</t>
+  </si>
+  <si>
+    <t>"Het ongedaan maken van een eerder gesloten verkoopovereenkomst."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a1df63b-27e8-389e-5b77-0a423db2ba3e</t>
+  </si>
+  <si>
+    <t>"Ontbinding verkoop"@nl</t>
+  </si>
+  <si>
+    <t>"Ontbinding ná levering van het beslagvoorwerp door de koper wanneer dit is toegestaan vanuit de voorwaarden die door de DRZ aan de verkoop zijn verbonden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-01124c7a-0890-9d62-881c-7458464cefdf</t>
+  </si>
+  <si>
+    <t>"Ontnemingsmaatregel"@nl</t>
+  </si>
+  <si>
+    <t>"Maatregel waarbij de veroordeelde wordt verplicht een geldbedrag aan de Staat te betalen ter ontneming van wederrechtelijk verkregen voordeel."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-2b9d7e51-3f8d-028f-c3fb-810af6f80d74</t>
+  </si>
+  <si>
+    <t>"Ontnemingszaak"@nl</t>
+  </si>
+  <si>
+    <t>"Zaak waarin wordt beoordeeld of wederrechtelijk verkregen voordeel moet worden ontnomen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba5b8b30-5bc3-0df5-a0e4-a6891903560d</t>
+  </si>
+  <si>
+    <t>"Onttrekken maatschappelijk verkeer"@nl</t>
+  </si>
+  <si>
+    <t>"Het door rechterlijke beslissing blijvend uit de maatschappij nemen van een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fe9d369c-f9bd-1765-bfc8-c0aca4fb3aea</t>
+  </si>
+  <si>
+    <t>"Ontvanger"@nl</t>
+  </si>
+  <si>
+    <t>"De (rechts)persoon aan wie een inbeslaggenomen voorwerp feitelijk wordt teruggegeven."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4a1714cb-91ba-f0d5-3d7a-1f939579cdbd</t>
+  </si>
+  <si>
+    <t>"Opbrengst"@nl</t>
+  </si>
+  <si>
+    <t>"Geldbedrag dat wordt verkregen uit de verkoop of vervreemding van een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7cfb4fd3-49bc-2ca4-83ef-9a2aef13f222</t>
+  </si>
+  <si>
+    <t>"Opvolgingszaak"@nl</t>
+  </si>
+  <si>
+    <t>"Bundeling van opsporings- en/of handhavings-handelingen waarmee opvolging wordt gegeven aan signalen uit de samenleving en van ketenpartners zoals aangiften, tips, incidenten en eigen waarnemingen en signaleringen."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx' (maar enigszins ingekort)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9083f370-93d6-c3b5-2868-936d857f462f</t>
+  </si>
+  <si>
+    <t>"Organisatie"@nl</t>
+  </si>
+  <si>
+    <t>"Een doelgerichte samenbundeling van kennis, vaardigheden en capaciteit (of middelen) om te voorzien in de behoefte aan producten en/of diensten."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e8c02b1f-7796-6137-4bec-fb2f514ea56b</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx' (maar enigszins ingekort)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-967318df-37f5-494b-5fa3-f9ddecc3b218</t>
+  </si>
+  <si>
+    <t>"Overboeken"@nl</t>
+  </si>
+  <si>
+    <t>"De financiële beweging van een beslagvoorwerp (vermogensrecht) van de ene bankrekening naar een andere."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-3be3ab34-744c-1952-798e-6f61ea022664</t>
+  </si>
+  <si>
+    <t>"Overboeking"@nl</t>
+  </si>
+  <si>
+    <t>"De overdracht van een geldbedrag van de ene rekening naar een andere."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-eb1a4ec4-fcfd-a4e2-4dd8-8162a28adb27</t>
+  </si>
+  <si>
+    <t>"Overdracht"@nl</t>
+  </si>
+  <si>
+    <t>"Het overgaan van een voorwerp, zaak of verantwoordelijkheid van de ene partij naar een andere."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-90b0bb24-31bd-3709-3be1-ce984e2e04f4</t>
+  </si>
+  <si>
+    <t>"Overdragen tbv executie"@nl</t>
+  </si>
+  <si>
+    <t>"Het overdragen van een zaak of voorwerp ten behoeve van de uitvoering van een rechterlijke beslissing."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-cb8a9a83-65d9-844b-89f6-38ee07abd5ee</t>
+  </si>
+  <si>
+    <t>"Overdragen"@nl</t>
+  </si>
+  <si>
+    <t>"De overgang van verantwoordelijkheid tussen ketenpartner(s) ten aanzien van een beslagvoorwerp."@nl</t>
+  </si>
+  <si>
+    <t>"Persoon"@nl</t>
+  </si>
+  <si>
+    <t>"Een rechtspersoon of een natuurlijk persoon."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-e8c02b1f-7796-6137-4bec-fb2f514ea56b","Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4697be7b-cabb-3b17-a239-3693d901184d</t>
+  </si>
+  <si>
+    <t>"Prijsgeven"@nl</t>
+  </si>
+  <si>
+    <t>"Het afstand doen van rechten op een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c</t>
+  </si>
+  <si>
+    <t>"Procestoestand"@nl</t>
+  </si>
+  <si>
+    <t>"Een geheel van omstandigheden waarin een beslagproces zich op een gegeven moment bevindt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621</t>
+  </si>
+  <si>
+    <t>"Rechthebbende"@nl</t>
+  </si>
+  <si>
+    <t>"Een andere persoon dan de beslagene die om teruggave van het voorwerp vraagt (vanuit een klaagschrift) of in aanmerking komt om het voorwerp aan terug te geven."@nl</t>
+  </si>
+  <si>
+    <t>"Rechtspersoon"@nl</t>
+  </si>
+  <si>
+    <t>"Een organisatie, waaronder begrepen een samenwerkingsverband, die als drager van subjectieve rechten en plichten optreedt."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-9083f370-93d6-c3b5-2868-936d857f462f","Begrip:Id-dd785c92-16b9-59e1-08f4-8e0cb03b0407"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-43688909-a30b-098b-caed-b2a12d487c5b</t>
+  </si>
+  <si>
+    <t>"Rechtszaak strafrecht"@nl</t>
+  </si>
+  <si>
+    <t>"Een strafrechtelijke procedure tussen een verdachte en het Openbaar Ministerie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-184281a9-9f0b-84f2-3d83-815830c462ae</t>
+  </si>
+  <si>
+    <t>"Redelijkerwijs rechthebbende"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon van wie op grond van de beschikbare feiten aannemelijk is dat deze recht heeft op een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4a739b37-f796-5bae-a40e-a7f82fbc92b5</t>
+  </si>
+  <si>
+    <t>"Relateren"@nl</t>
+  </si>
+  <si>
+    <t>"Het leggen van een inhoudelijke of administratieve relatie tussen objecten, zaken of gegevens."@nl</t>
+  </si>
+  <si>
+    <t>"Roerende zaak"@nl</t>
+  </si>
+  <si>
+    <t>"Een voor menselijke beheersing vatbaar stoffelijk object dat niet een onroerende zaak is."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-81b4d500-8ceb-d448-db73-0b54f6d4a172</t>
+  </si>
+  <si>
+    <t>"Rol"@nl</t>
+  </si>
+  <si>
+    <t>"Een eenduidige aanduiding van een verzameling verantwoordelijkheden, taken en bevoegdheden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-2d52aade-44c5-9f22-5965-da23f4d38c7c</t>
+  </si>
+  <si>
+    <t>"Samenvoegen"@nl</t>
+  </si>
+  <si>
+    <t>"Het tot één nieuw voorwerp bundelen van afzonderlijk in beslag genomen voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a8ff7679-a7a2-4c7f-53f9-b5b3e3361322</t>
+  </si>
+  <si>
+    <t>"Samenvoeging"@nl</t>
+  </si>
+  <si>
+    <t>"Het combineren van twee of meer zaken, dossiers of verzamelingen tot één geheel."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-dd785c92-16b9-59e1-08f4-8e0cb03b0407</t>
+  </si>
+  <si>
+    <t>"Samenwerkingsverband"@nl</t>
+  </si>
+  <si>
+    <t>"Geheel van partijen dat gezamenlijk een bepaald doel nastreeft."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1f4c5ee-77ab-f3c2-f37b-382879df0b23</t>
+  </si>
+  <si>
+    <t>"Slachtoffermaatregel"@nl</t>
+  </si>
+  <si>
+    <t>"Maatregel waarbij een veroordeelde wordt verplicht een geldbedrag ten behoeve van het slachtoffer te betalen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818</t>
+  </si>
+  <si>
+    <t>"Soort beslaghandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Een typering van een beslaghandeling."@nl</t>
+  </si>
+  <si>
+    <t>"EB 2026-05-01: Ik vraag me af of dit een begrip is dat thuishoort in een begrippenkader. Komt zoiets als 'Soort beslaghandeling' niet pas om de hoek kijken bij de stap van een begrippenkader naar een conceptueel model?"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-588f3f68-e563-db5b-7030-5f9664e0501e</t>
+  </si>
+  <si>
+    <t>"Splitsen"@nl</t>
+  </si>
+  <si>
+    <t>"Het opdelen van een beslagvoorwerp in meerdere afzonderlijke delen."@nl</t>
+  </si>
+  <si>
+    <t>"Bij het splitsen van een beslagvoorwerp ontstaan nieuwe beslagen en beslagvoorwerpen ter vervanging van het origineel, omdat elk beslag en beslagvoorwerp op eigen wijze afgehandeld moet kunnen worden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-3d181d15-1919-ddd6-4b3a-5f78b4af2139</t>
+  </si>
+  <si>
+    <t>"Splitsing"@nl</t>
+  </si>
+  <si>
+    <t>"Het opdelen van een zaak, dossier of verzameling in afzonderlijke delen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-100fc58e-baed-ce15-f33b-0990c7aac7e3</t>
+  </si>
+  <si>
+    <t>"Storten"@nl</t>
+  </si>
+  <si>
+    <t>"Het overmaken of in ontvangst nemen van een geldbedrag op een rekening."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0adcbefe-036a-144f-7897-5b35ce859a85</t>
+  </si>
+  <si>
+    <t>"Storting"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-6b949c90-7848-2885-dd92-d0051aaa7dff</t>
+  </si>
+  <si>
+    <t>"Strafzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Een door het Openbaar Ministerie ingestelde procedure bij de strafrechter, waarin één of meer verdachten worden berecht ter zake van één of meer strafbare feiten."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5b5401c6-70fb-609e-6267-92358853596e</t>
+  </si>
+  <si>
+    <t>"Taxatie"@nl</t>
+  </si>
+  <si>
+    <t>"De vaststelling van de waarde van een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8606bfb7-1a7a-bc92-5af6-f183046ae448</t>
+  </si>
+  <si>
+    <t>"Taxatiewaarde"@nl</t>
+  </si>
+  <si>
+    <t>"Een onderbouwde waarde van een beslagvoorwerp op een specifieke peildatum, bepaald volgens een passende waarderingsmethode en expliciete uitgangspunten, ten behoeve van een vooraf gedefinieerd doel (bijv. beslag, verkoop)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be</t>
+  </si>
+  <si>
+    <t>"Taxeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het vaststellen van de waarde van een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ca74d3bf-0c2a-6d4d-5424-7efbebda693b</t>
+  </si>
+  <si>
+    <t>"Teruggave"@nl</t>
+  </si>
+  <si>
+    <t>"De handeling waarbij een in beslag genomen voorwerp wordt teruggegeven aan de rechthebbende."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d</t>
+  </si>
+  <si>
+    <t>"Teruggeven"@nl</t>
+  </si>
+  <si>
+    <t>"Het feitelijk afgeven van een voorwerp aan degene die daarop recht heeft."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-bd706e91-05f2-de2f-99fb-650f9cae86f7</t>
+  </si>
+  <si>
+    <t>"Toetsen hovj"@nl</t>
+  </si>
+  <si>
+    <t>"Het beoordelen door de hulpofficier van justitie of aan de gestelde voorwaarden is voldaan."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1514e0e-4b11-1aa1-c7dc-f26843ca05f0</t>
+  </si>
+  <si>
+    <t>"Toetsing"@nl</t>
+  </si>
+  <si>
+    <t>"Het beoordelen of aan vastgestelde voorwaarden, regels of normen is voldaan."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-09ef3bf4-ad6a-a964-cae2-d60f066927e8</t>
+  </si>
+  <si>
+    <t>"Uitspraak"@nl</t>
+  </si>
+  <si>
+    <t>"Het geheel van ter terechtzitting door de Rechtspraak uitgesproken oordelen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-b57d6283-0baa-19f3-0889-0fc1f90d7f65</t>
+  </si>
+  <si>
+    <t>"Verbeurd verklaren"@nl</t>
+  </si>
+  <si>
+    <t>"Het bij rechterlijke beslissing laten overgaan van de eigendom van een voorwerp op de Staat als straf."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-804b3e52-ba2e-f49b-fc69-0e2e1fb08b01</t>
+  </si>
+  <si>
+    <t>"Vergoeden"@nl</t>
+  </si>
+  <si>
+    <t>"Het betalen van een geldbedrag ter compensatie van schade of kosten."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-effe4d76-6647-a026-d398-ac6f393d956b</t>
+  </si>
+  <si>
+    <t>"Verkoop"@nl</t>
+  </si>
+  <si>
+    <t>"De uitwinning of vervreemding van een beslagvoorwerp met het doel de vordering te voldoen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b</t>
+  </si>
+  <si>
+    <t>"Verkopen"@nl</t>
+  </si>
+  <si>
+    <t>"Het overdragen van een voorwerp tegen betaling."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-b649c83e-832f-c5f5-a797-d0bedf1110d6</t>
+  </si>
+  <si>
+    <t>"Vermogensrecht"@nl</t>
+  </si>
+  <si>
+    <t>"Een subjectief recht op een goed, een dienst of een andere prestatie die uiteindelijk tot stoffelijk voordeel leidt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-61d0b99e-4379-4eeb-8a2d-d628f3bcf9a8</t>
+  </si>
+  <si>
+    <t>"Vernietigen"@nl</t>
+  </si>
+  <si>
+    <t>"Het onbruikbaar maken of doen verdwijnen van een voorwerp."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-33f3f9f6-a5e0-ab8c-e3ce-05284db47565</t>
+  </si>
+  <si>
+    <t>"Vernietiging"@nl</t>
+  </si>
+  <si>
+    <t>"Het onbruikbaar maken of doen verdwijnen van een voorwerp waardoor het niet meer kan worden gebruikt of teruggegeven."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604</t>
+  </si>
+  <si>
+    <t>"Verplaatsen"@nl</t>
+  </si>
+  <si>
+    <t>"De logistieke vervoersbeweging van een beslagvoorwerp (roerende zaak of stoffelijk overschot) tussen locaties."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'. Daar wordt gesproken over TRANSPORTEREN. Is dat hetzelfde als VERPLAATSEN?"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-092ba025-52a1-af44-1ec0-03ac09832dea</t>
+  </si>
+  <si>
+    <t>"Verplaatsing"@nl</t>
+  </si>
+  <si>
+    <t>"Het overbrengen van een in beslag genomen voorwerp van de ene locatie naar een andere."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-424d3790-4f35-ed97-7232-d7d7dfbdbe25</t>
+  </si>
+  <si>
+    <t>"Vervallen aan de staat"@nl</t>
+  </si>
+  <si>
+    <t>"Het overgaan van de eigendom van een voorwerp op de Staat op grond van een wettelijke beslissing."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9d5149ec-9a91-f9ce-5e5a-53f8a3365b85</t>
+  </si>
+  <si>
+    <t>"Voertuig"@nl</t>
+  </si>
+  <si>
+    <t>"Elk middel dat is bedoeld of geschikt om personen of goederen te vervoeren over weg, water, spoor of door de lucht."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fb6b89ac-3c2a-8e17-eb30-455f0269a083</t>
+  </si>
+  <si>
+    <t>"Voorleggen hOvJ"@nl</t>
+  </si>
+  <si>
+    <t>"Het ter beoordeling aanbieden van een zaak aan de hulpofficier van justitie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d52c31a2-f220-8d74-2816-2753f3769760</t>
+  </si>
+  <si>
+    <t>"Voorleggen OM"@nl</t>
+  </si>
+  <si>
+    <t>"Het ter beoordeling aanbieden van een zaak aan het Openbaar Ministerie."@nl</t>
+  </si>
+  <si>
+    <t>"Voorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Een onroerende zaak, vermogensrecht of roerende zaak (waaronder dier)."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-789e6d2d-cd8d-98dd-bfe7-2cc1177c92a2","Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e","Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb","Begrip:Id-b649c83e-832f-c5f5-a797-d0bedf1110d6","Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-789e6d2d-cd8d-98dd-bfe7-2cc1177c92a2</t>
+  </si>
+  <si>
+    <t>"Voorwerpcategorie"@nl</t>
+  </si>
+  <si>
+    <t>"Goederencategorie"@nl</t>
+  </si>
+  <si>
+    <t>"Een verzameling van voorwerpen die op grond van één of meer gedefinieerde kenmerken als behorend tot dezelfde klasse worden aangemerkt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c2d131fb-e6bc-7725-4a77-8caf939c7cf8</t>
+  </si>
+  <si>
+    <t>"Werkopdracht beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Opdracht tot het uitvoeren van werkzaamheden met betrekking tot beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-249d0a16-d496-fe7e-69c1-c26c2ca4c376</t>
+  </si>
+  <si>
+    <t>"Zaak (BW)"@nl</t>
+  </si>
+  <si>
+    <t>"Een voor menselijke beheersing vatbaar stoffelijke object."@nl</t>
+  </si>
+  <si>
+    <t>[{"NLSBBNaamBrondocument":"Burgerlijk Wetboek - Boek 3","NLSBBUitleg":false,"NLSBBURL":false,"NLSBBBronverwijzing":false}]</t>
+  </si>
+  <si>
+    <t>"Zaak"@nl</t>
+  </si>
+  <si>
+    <t>"Een samenhangende hoeveelheid werk met een goed gedefinieerde aanleiding en eindresultaat."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-43688909-a30b-098b-caed-b2a12d487c5b","Begrip:Id-7cfb4fd3-49bc-2ca4-83ef-9a2aef13f222","Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08</t>
+  </si>
+  <si>
+    <t>"Zekerheidstellen"@nl</t>
+  </si>
+  <si>
+    <t>"Het veiligstellen van vermogen of voorwerpen teneinde te waarborgen dat een toekomstige financiële sanctie (zoals een geldboete, schadevergoedingsmaatregel of ontneming) daadwerkelijk kan worden verhaald."@nl</t>
+  </si>
+  <si>
     <t>"Definitie opgesteld met hulp van ChatGPT."@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6</t>
-  </si>
-  <si>
-    <t>"Achterhalen waarheid"@nl</t>
-  </si>
-  <si>
-    <t>"Het veiligstellen en onderzoeken van voorwerpen of gegevens die kunnen bijdragen aan het vaststellen van de feiten en omstandigheden van een strafbaar feit, teneinde de materiële waarheid in het strafproces te achterhalen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-2f300aa8-6e57-e42c-b962-eb1ad70ee980</t>
-  </si>
-  <si>
-    <t>"Afname afstandverklaring"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij de beslagene of rechthebbende verklaart afstand te nemen van het beslagvoorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-eaea5461-5322-95aa-10d5-da9bda358feb</t>
-  </si>
-  <si>
-    <t>ChatGPT – Semantic Review 01</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e9d43e6f-32ce-5056-6947-21b0e0343469</t>
-  </si>
-  <si>
-    <t>"Een locatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0f48dc14-e263-3478-30c9-1a4e99473cbc</t>
-  </si>
-  <si>
-    <t>Begrip:Id-2ffe6d0f-df5f-7c71-8829-1da2adf6a17c</t>
-  </si>
-  <si>
-    <t>"Een afgebakende ruimte binnen een beslagbewaarlocatie die is bestemd voor het bewaren van beslagvoorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1691472e-de30-fd37-242a-4023c87e3bde</t>
-  </si>
-  <si>
-    <t>"Het bewaren van een beslagvoorwerp gedurende de periode waarin daarop strafvorderlijk beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0c79c3d8-bdd3-b152-fa07-ac4cad6f33a7</t>
-  </si>
-  <si>
-    <t>"Beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Het strafvorderlijk dwangmiddel beslag dat rust op een voorwerp op basis van een beslaggrondslag met een beslagdoel."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d","Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9","Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e"</t>
-  </si>
-  <si>
-    <t>"Overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-3989598e-4421-f771-2c30-be4aaabbe84b</t>
-  </si>
-  <si>
-    <t>"Beslagbeheerder"@nl</t>
-  </si>
-  <si>
-    <t>"Persoon of organisatie die verantwoordelijk is voor het beheer van in beslag genomen voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>"ChatGPT"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-245ba0cc-b46c-3743-f8ee-c976743b48cc</t>
-  </si>
-  <si>
-    <t>"Beslagbeslissing"@nl</t>
-  </si>
-  <si>
-    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
-  </si>
-  <si>
-    <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
-  </si>
-  <si>
-    <t>ChatGPT – Semantic Review 02</t>
-  </si>
-  <si>
-    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
-  </si>
-  <si>
-    <t>"Beslagbewaarder"@nl</t>
-  </si>
-  <si>
-    <t>"Persoon of organisatie die verantwoordelijk is voor de feitelijke bewaring van beslagvoorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>"@nl"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagdoel"@nl</t>
-  </si>
-  <si>
-    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
-  </si>
-  <si>
-    <t>"Beslagdossier"@nl</t>
-  </si>
-  <si>
-    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
-  </si>
-  <si>
-    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
-  </si>
-  <si>
-    <t>"Beslagene"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
-  </si>
-  <si>
-    <t>"Beslaggrondslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagtitel"@nl</t>
-  </si>
-  <si>
-    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
-  </si>
-  <si>
-    <t>"Beslaghandeling"@nl</t>
-  </si>
-  <si>
-    <t>"Beslaggebeurtenis"@nl</t>
-  </si>
-  <si>
-    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
-  </si>
-  <si>
-    <t>"Beslagportaal"@nl</t>
-  </si>
-  <si>
-    <t>"Informatiesysteem voor de registratie en ondersteuning van processen rondom strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
-  </si>
-  <si>
-    <t>"Beslagproces"@nl</t>
-  </si>
-  <si>
-    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
-  </si>
-  <si>
-    <t>"Beslagrol"@nl</t>
-  </si>
-  <si>
-    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
-  </si>
-  <si>
-    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
-  </si>
-  <si>
-    <t>"Beslagstatus"@nl</t>
-  </si>
-  <si>
-    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
-  </si>
-  <si>
-    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
-  </si>
-  <si>
-    <t>"Beslagstuk"@nl</t>
-  </si>
-  <si>
-    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
-  </si>
-  <si>
-    <t>"Beslagvoorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagobject"@nl</t>
-  </si>
-  <si>
-    <t>"Een voorwerp waarop beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
-  </si>
-  <si>
-    <t>"Beslagzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Samenhangend geheel van gegevens en handelingen met betrekking tot een strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
-  </si>
-  <si>
-    <t>"Beslissen over beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Over beslag beslissen"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
-  </si>
-  <si>
-    <t>"Besluitname"@nl</t>
-  </si>
-  <si>
-    <t>Het vormen en vaststellen van een besluit.</t>
-  </si>
-  <si>
-    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
-  </si>
-  <si>
-    <t>"Bewijs van ontvangst"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
-  </si>
-  <si>
-    <t>"Buitenlands beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
-  </si>
-  <si>
-    <t>"Conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
-  </si>
-  <si>
-    <t>"Deponeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
-  </si>
-  <si>
-    <t>"Dier"@nl</t>
-  </si>
-  <si>
-    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
-  </si>
-  <si>
-    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
-  </si>
-  <si>
-    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
-  </si>
-  <si>
-    <t>"Eigenaar"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
-  </si>
-  <si>
-    <t>"Forensisch onderzoek"@nl</t>
-  </si>
-  <si>
-    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
-  </si>
-  <si>
-    <t>"Functionaris"@nl</t>
-  </si>
-  <si>
-    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
-  </si>
-  <si>
-    <t>"Geldboete"@nl</t>
-  </si>
-  <si>
-    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
-  </si>
-  <si>
-    <t>"Goed"@nl</t>
-  </si>
-  <si>
-    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
-  </si>
-  <si>
-    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
-  </si>
-  <si>
-    <t>"In beslag nemen"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
-  </si>
-  <si>
-    <t>"Inbeheername"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
-  </si>
-  <si>
-    <t>"Inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"Inbeslagname"@nl</t>
-  </si>
-  <si>
-    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
-  </si>
-  <si>
-    <t>"Inbewaringname"@nl</t>
-  </si>
-  <si>
-    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
-  </si>
-  <si>
-    <t>"Internationaal beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
-  </si>
-  <si>
-    <t>"Kennisgeving van inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"KVI"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
-  </si>
-  <si>
-    <t>"Ketenbeslaghuis"@nl</t>
-  </si>
-  <si>
-    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ccfae3bb-46be-0eac-3cf9-8cb4b9301522</t>
-  </si>
-  <si>
-    <t>"Ketenpartner"@nl</t>
-  </si>
-  <si>
-    <t>"De rechtspersoon waarvan de functionaris een rol heeft in het beslagproces."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b92f545-d3f4-7775-845e-2b4d8d7d7339</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag beschikking/arrest ontvangen"@nl</t>
-  </si>
-  <si>
-    <t>"Het ontvangen van een klaagschrift tegen een beschikking of arrest inzake beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c38718ba-8796-ee51-b1af-f20619ea8d7e</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag intrekken"@nl</t>
-  </si>
-  <si>
-    <t>"Het door de indiener beëindigen van een eerder ingediend klaagschrift."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c9e37df7-a24c-7d35-ce7a-93c18f184746</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag ontvangen"@nl</t>
-  </si>
-  <si>
-    <t>"Het ontvangen van een klaagschrift dat betrekking heeft op beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89190bf7-9961-04e0-3769-f03df5a4b1af</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Een bij de Rechtspraak ingediende klacht of verzoek ten aanzien van de toepassing van beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Klassiek beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94 Sv."@nl</t>
-  </si>
-  <si>
-    <t>"Locatie"@nl</t>
-  </si>
-  <si>
-    <t>"Een bepaald punt of afgebakend gebied in de ruimte."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-af7b5f03-2b9a-72c0-a1de-2959bc89a3f4</t>
-  </si>
-  <si>
-    <t>"Machtiging tot conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Een door de rechter-commissaris verleende machtiging tot het leggen of handhaven van conservatoir beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8</t>
-  </si>
-  <si>
-    <t>"Natuurlijk persoon"@nl</t>
-  </si>
-  <si>
-    <t>"Natuurlijke persoon"@nl</t>
-  </si>
-  <si>
-    <t>"Een mens, in juridische context beschouwd als een drager van subjectieve rechten en plichten."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb</t>
-  </si>
-  <si>
-    <t>"Onroerende zaak"@nl</t>
-  </si>
-  <si>
-    <t>"Grond, nog niet gewonnen delfstoffen, met de grond verenigde beplantingen, alsmede gebouwen en andere werken zoals viaducten die al dan niet rechtstreeks duurzaam met de grond zijn verenigd (wortel en nagelvast)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'. In die definitie wordt art. 3:3.1 BW als bron genoemd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a415d88a-0766-091f-7ea5-e2863a832873</t>
-  </si>
-  <si>
-    <t>"Ontbinden verkoop"@nl</t>
-  </si>
-  <si>
-    <t>"Het ongedaan maken van een eerder gesloten verkoopovereenkomst."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a1df63b-27e8-389e-5b77-0a423db2ba3e</t>
-  </si>
-  <si>
-    <t>"Ontbinding verkoop"@nl</t>
-  </si>
-  <si>
-    <t>"Ontbinding ná levering van het beslagvoorwerp door de koper wanneer dit is toegestaan vanuit de voorwaarden die door de DRZ aan de verkoop zijn verbonden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-01124c7a-0890-9d62-881c-7458464cefdf</t>
-  </si>
-  <si>
-    <t>"Ontnemingsmaatregel"@nl</t>
-  </si>
-  <si>
-    <t>"Maatregel waarbij de veroordeelde wordt verplicht een geldbedrag aan de Staat te betalen ter ontneming van wederrechtelijk verkregen voordeel."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-2b9d7e51-3f8d-028f-c3fb-810af6f80d74</t>
-  </si>
-  <si>
-    <t>"Ontnemingszaak"@nl</t>
-  </si>
-  <si>
-    <t>"Zaak waarin wordt beoordeeld of wederrechtelijk verkregen voordeel moet worden ontnomen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba5b8b30-5bc3-0df5-a0e4-a6891903560d</t>
-  </si>
-  <si>
-    <t>"Onttrekken maatschappelijk verkeer"@nl</t>
-  </si>
-  <si>
-    <t>"Het door rechterlijke beslissing blijvend uit de maatschappij nemen van een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fe9d369c-f9bd-1765-bfc8-c0aca4fb3aea</t>
-  </si>
-  <si>
-    <t>"Ontvanger"@nl</t>
-  </si>
-  <si>
-    <t>"De (rechts)persoon aan wie een inbeslaggenomen voorwerp feitelijk wordt teruggegeven."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4a1714cb-91ba-f0d5-3d7a-1f939579cdbd</t>
-  </si>
-  <si>
-    <t>"Opbrengst"@nl</t>
-  </si>
-  <si>
-    <t>"Geldbedrag dat wordt verkregen uit de verkoop of vervreemding van een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7cfb4fd3-49bc-2ca4-83ef-9a2aef13f222</t>
-  </si>
-  <si>
-    <t>"Opvolgingszaak"@nl</t>
-  </si>
-  <si>
-    <t>"Bundeling van opsporings- en/of handhavings-handelingen waarmee opvolging wordt gegeven aan signalen uit de samenleving en van ketenpartners zoals aangiften, tips, incidenten en eigen waarnemingen en signaleringen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx' (maar enigszins ingekort)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9083f370-93d6-c3b5-2868-936d857f462f</t>
-  </si>
-  <si>
-    <t>"Organisatie"@nl</t>
-  </si>
-  <si>
-    <t>"Een doelgerichte samenbundeling van kennis, vaardigheden en capaciteit (of middelen) om te voorzien in de behoefte aan producten en/of diensten."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e8c02b1f-7796-6137-4bec-fb2f514ea56b</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx' (maar enigszins ingekort)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-967318df-37f5-494b-5fa3-f9ddecc3b218</t>
-  </si>
-  <si>
-    <t>"Overboeken"@nl</t>
-  </si>
-  <si>
-    <t>"De financiële beweging van een beslagvoorwerp (vermogensrecht) van de ene bankrekening naar een andere."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-3be3ab34-744c-1952-798e-6f61ea022664</t>
-  </si>
-  <si>
-    <t>"Overboeking"@nl</t>
-  </si>
-  <si>
-    <t>"De overdracht van een geldbedrag van de ene rekening naar een andere."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-eb1a4ec4-fcfd-a4e2-4dd8-8162a28adb27</t>
-  </si>
-  <si>
-    <t>"Overdracht"@nl</t>
-  </si>
-  <si>
-    <t>"Het overgaan van een voorwerp, zaak of verantwoordelijkheid van de ene partij naar een andere."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-90b0bb24-31bd-3709-3be1-ce984e2e04f4</t>
-  </si>
-  <si>
-    <t>"Overdragen tbv executie"@nl</t>
-  </si>
-  <si>
-    <t>"Het overdragen van een zaak of voorwerp ten behoeve van de uitvoering van een rechterlijke beslissing."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-cb8a9a83-65d9-844b-89f6-38ee07abd5ee</t>
-  </si>
-  <si>
-    <t>"Overdragen"@nl</t>
-  </si>
-  <si>
-    <t>"De overgang van verantwoordelijkheid tussen ketenpartner(s) ten aanzien van een beslagvoorwerp."@nl</t>
-  </si>
-  <si>
-    <t>"Persoon"@nl</t>
-  </si>
-  <si>
-    <t>"Een rechtspersoon of een natuurlijk persoon."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-e8c02b1f-7796-6137-4bec-fb2f514ea56b","Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4697be7b-cabb-3b17-a239-3693d901184d</t>
-  </si>
-  <si>
-    <t>"Prijsgeven"@nl</t>
-  </si>
-  <si>
-    <t>"Het afstand doen van rechten op een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c</t>
-  </si>
-  <si>
-    <t>"Procestoestand"@nl</t>
-  </si>
-  <si>
-    <t>"Een geheel van omstandigheden waarin een beslagproces zich op een gegeven moment bevindt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621</t>
-  </si>
-  <si>
-    <t>"Rechthebbende"@nl</t>
-  </si>
-  <si>
-    <t>"Een andere persoon dan de beslagene die om teruggave van het voorwerp vraagt (vanuit een klaagschrift) of in aanmerking komt om het voorwerp aan terug te geven."@nl</t>
-  </si>
-  <si>
-    <t>"Rechtspersoon"@nl</t>
-  </si>
-  <si>
-    <t>"Een organisatie, waaronder begrepen een samenwerkingsverband, die als drager van subjectieve rechten en plichten optreedt."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-9083f370-93d6-c3b5-2868-936d857f462f","Begrip:Id-dd785c92-16b9-59e1-08f4-8e0cb03b0407"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-43688909-a30b-098b-caed-b2a12d487c5b</t>
-  </si>
-  <si>
-    <t>"Rechtszaak strafrecht"@nl</t>
-  </si>
-  <si>
-    <t>"Een strafrechtelijke procedure tussen een verdachte en het Openbaar Ministerie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-184281a9-9f0b-84f2-3d83-815830c462ae</t>
-  </si>
-  <si>
-    <t>"Redelijkerwijs rechthebbende"@nl</t>
-  </si>
-  <si>
-    <t>"Persoon van wie op grond van de beschikbare feiten aannemelijk is dat deze recht heeft op een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4a739b37-f796-5bae-a40e-a7f82fbc92b5</t>
-  </si>
-  <si>
-    <t>"Relateren"@nl</t>
-  </si>
-  <si>
-    <t>"Het leggen van een inhoudelijke of administratieve relatie tussen objecten, zaken of gegevens."@nl</t>
-  </si>
-  <si>
-    <t>"Roerende zaak"@nl</t>
-  </si>
-  <si>
-    <t>"Een voor menselijke beheersing vatbaar stoffelijk object dat niet een onroerende zaak is."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-81b4d500-8ceb-d448-db73-0b54f6d4a172</t>
-  </si>
-  <si>
-    <t>"Rol"@nl</t>
-  </si>
-  <si>
-    <t>"Een eenduidige aanduiding van een verzameling verantwoordelijkheden, taken en bevoegdheden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-2d52aade-44c5-9f22-5965-da23f4d38c7c</t>
-  </si>
-  <si>
-    <t>"Samenvoegen"@nl</t>
-  </si>
-  <si>
-    <t>"Het tot één nieuw voorwerp bundelen van afzonderlijk in beslag genomen voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a8ff7679-a7a2-4c7f-53f9-b5b3e3361322</t>
-  </si>
-  <si>
-    <t>"Samenvoeging"@nl</t>
-  </si>
-  <si>
-    <t>"Het combineren van twee of meer zaken, dossiers of verzamelingen tot één geheel."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-dd785c92-16b9-59e1-08f4-8e0cb03b0407</t>
-  </si>
-  <si>
-    <t>"Samenwerkingsverband"@nl</t>
-  </si>
-  <si>
-    <t>"Geheel van partijen dat gezamenlijk een bepaald doel nastreeft."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1f4c5ee-77ab-f3c2-f37b-382879df0b23</t>
-  </si>
-  <si>
-    <t>"Slachtoffermaatregel"@nl</t>
-  </si>
-  <si>
-    <t>"Maatregel waarbij een veroordeelde wordt verplicht een geldbedrag ten behoeve van het slachtoffer te betalen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818</t>
-  </si>
-  <si>
-    <t>"Soort beslaghandeling"@nl</t>
-  </si>
-  <si>
-    <t>"Een typering van een beslaghandeling."@nl</t>
-  </si>
-  <si>
-    <t>"EB 2026-05-01: Ik vraag me af of dit een begrip is dat thuishoort in een begrippenkader. Komt zoiets als 'Soort beslaghandeling' niet pas om de hoek kijken bij de stap van een begrippenkader naar een conceptueel model?"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-588f3f68-e563-db5b-7030-5f9664e0501e</t>
-  </si>
-  <si>
-    <t>"Splitsen"@nl</t>
-  </si>
-  <si>
-    <t>"Het opdelen van een beslagvoorwerp in meerdere afzonderlijke delen."@nl</t>
-  </si>
-  <si>
-    <t>"Bij het splitsen van een beslagvoorwerp ontstaan nieuwe beslagen en beslagvoorwerpen ter vervanging van het origineel, omdat elk beslag en beslagvoorwerp op eigen wijze afgehandeld moet kunnen worden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-3d181d15-1919-ddd6-4b3a-5f78b4af2139</t>
-  </si>
-  <si>
-    <t>"Splitsing"@nl</t>
-  </si>
-  <si>
-    <t>"Het opdelen van een zaak, dossier of verzameling in afzonderlijke delen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-100fc58e-baed-ce15-f33b-0990c7aac7e3</t>
-  </si>
-  <si>
-    <t>"Storten"@nl</t>
-  </si>
-  <si>
-    <t>"Het overmaken of in ontvangst nemen van een geldbedrag op een rekening."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0adcbefe-036a-144f-7897-5b35ce859a85</t>
-  </si>
-  <si>
-    <t>"Storting"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-6b949c90-7848-2885-dd92-d0051aaa7dff</t>
-  </si>
-  <si>
-    <t>"Strafzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Een door het Openbaar Ministerie ingestelde procedure bij de strafrechter, waarin één of meer verdachten worden berecht ter zake van één of meer strafbare feiten."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5b5401c6-70fb-609e-6267-92358853596e</t>
-  </si>
-  <si>
-    <t>"Taxatie"@nl</t>
-  </si>
-  <si>
-    <t>"De vaststelling van de waarde van een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8606bfb7-1a7a-bc92-5af6-f183046ae448</t>
-  </si>
-  <si>
-    <t>"Taxatiewaarde"@nl</t>
-  </si>
-  <si>
-    <t>"Een onderbouwde waarde van een beslagvoorwerp op een specifieke peildatum, bepaald volgens een passende waarderingsmethode en expliciete uitgangspunten, ten behoeve van een vooraf gedefinieerd doel (bijv. beslag, verkoop)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be</t>
-  </si>
-  <si>
-    <t>"Taxeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het vaststellen van de waarde van een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ca74d3bf-0c2a-6d4d-5424-7efbebda693b</t>
-  </si>
-  <si>
-    <t>"Teruggave"@nl</t>
-  </si>
-  <si>
-    <t>"De handeling waarbij een in beslag genomen voorwerp wordt teruggegeven aan de rechthebbende."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d</t>
-  </si>
-  <si>
-    <t>"Teruggeven"@nl</t>
-  </si>
-  <si>
-    <t>"Het feitelijk afgeven van een voorwerp aan degene die daarop recht heeft."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-bd706e91-05f2-de2f-99fb-650f9cae86f7</t>
-  </si>
-  <si>
-    <t>"Toetsen hovj"@nl</t>
-  </si>
-  <si>
-    <t>"Het beoordelen door de hulpofficier van justitie of aan de gestelde voorwaarden is voldaan."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1514e0e-4b11-1aa1-c7dc-f26843ca05f0</t>
-  </si>
-  <si>
-    <t>"Toetsing"@nl</t>
-  </si>
-  <si>
-    <t>"Het beoordelen of aan vastgestelde voorwaarden, regels of normen is voldaan."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-09ef3bf4-ad6a-a964-cae2-d60f066927e8</t>
-  </si>
-  <si>
-    <t>"Uitspraak"@nl</t>
-  </si>
-  <si>
-    <t>"Het geheel van ter terechtzitting door de Rechtspraak uitgesproken oordelen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-b57d6283-0baa-19f3-0889-0fc1f90d7f65</t>
-  </si>
-  <si>
-    <t>"Verbeurd verklaren"@nl</t>
-  </si>
-  <si>
-    <t>"Het bij rechterlijke beslissing laten overgaan van de eigendom van een voorwerp op de Staat als straf."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-804b3e52-ba2e-f49b-fc69-0e2e1fb08b01</t>
-  </si>
-  <si>
-    <t>"Vergoeden"@nl</t>
-  </si>
-  <si>
-    <t>"Het betalen van een geldbedrag ter compensatie van schade of kosten."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-effe4d76-6647-a026-d398-ac6f393d956b</t>
-  </si>
-  <si>
-    <t>"Verkoop"@nl</t>
-  </si>
-  <si>
-    <t>"De uitwinning of vervreemding van een beslagvoorwerp met het doel de vordering te voldoen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b</t>
-  </si>
-  <si>
-    <t>"Verkopen"@nl</t>
-  </si>
-  <si>
-    <t>"Het overdragen van een voorwerp tegen betaling."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-b649c83e-832f-c5f5-a797-d0bedf1110d6</t>
-  </si>
-  <si>
-    <t>"Vermogensrecht"@nl</t>
-  </si>
-  <si>
-    <t>"Een subjectief recht op een goed, een dienst of een andere prestatie die uiteindelijk tot stoffelijk voordeel leidt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-61d0b99e-4379-4eeb-8a2d-d628f3bcf9a8</t>
-  </si>
-  <si>
-    <t>"Vernietigen"@nl</t>
-  </si>
-  <si>
-    <t>"Het onbruikbaar maken of doen verdwijnen van een voorwerp."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-33f3f9f6-a5e0-ab8c-e3ce-05284db47565</t>
-  </si>
-  <si>
-    <t>"Vernietiging"@nl</t>
-  </si>
-  <si>
-    <t>"Het onbruikbaar maken of doen verdwijnen van een voorwerp waardoor het niet meer kan worden gebruikt of teruggegeven."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604</t>
-  </si>
-  <si>
-    <t>"Verplaatsen"@nl</t>
-  </si>
-  <si>
-    <t>"De logistieke vervoersbeweging van een beslagvoorwerp (roerende zaak of stoffelijk overschot) tussen locaties."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'. Daar wordt gesproken over TRANSPORTEREN. Is dat hetzelfde als VERPLAATSEN?"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-092ba025-52a1-af44-1ec0-03ac09832dea</t>
-  </si>
-  <si>
-    <t>"Verplaatsing"@nl</t>
-  </si>
-  <si>
-    <t>"Het overbrengen van een in beslag genomen voorwerp van de ene locatie naar een andere."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-424d3790-4f35-ed97-7232-d7d7dfbdbe25</t>
-  </si>
-  <si>
-    <t>"Vervallen aan de staat"@nl</t>
-  </si>
-  <si>
-    <t>"Het overgaan van de eigendom van een voorwerp op de Staat op grond van een wettelijke beslissing."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9d5149ec-9a91-f9ce-5e5a-53f8a3365b85</t>
-  </si>
-  <si>
-    <t>"Voertuig"@nl</t>
-  </si>
-  <si>
-    <t>"Elk middel dat is bedoeld of geschikt om personen of goederen te vervoeren over weg, water, spoor of door de lucht."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fb6b89ac-3c2a-8e17-eb30-455f0269a083</t>
-  </si>
-  <si>
-    <t>"Voorleggen hOvJ"@nl</t>
-  </si>
-  <si>
-    <t>"Het ter beoordeling aanbieden van een zaak aan de hulpofficier van justitie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d52c31a2-f220-8d74-2816-2753f3769760</t>
-  </si>
-  <si>
-    <t>"Voorleggen OM"@nl</t>
-  </si>
-  <si>
-    <t>"Het ter beoordeling aanbieden van een zaak aan het Openbaar Ministerie."@nl</t>
-  </si>
-  <si>
-    <t>"Voorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Een onroerende zaak, vermogensrecht of roerende zaak (waaronder dier)."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-789e6d2d-cd8d-98dd-bfe7-2cc1177c92a2","Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e","Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb","Begrip:Id-b649c83e-832f-c5f5-a797-d0bedf1110d6","Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-789e6d2d-cd8d-98dd-bfe7-2cc1177c92a2</t>
-  </si>
-  <si>
-    <t>"Voorwerpcategorie"@nl</t>
-  </si>
-  <si>
-    <t>"Goederencategorie"@nl</t>
-  </si>
-  <si>
-    <t>"Een verzameling van voorwerpen die op grond van één of meer gedefinieerde kenmerken als behorend tot dezelfde klasse worden aangemerkt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c2d131fb-e6bc-7725-4a77-8caf939c7cf8</t>
-  </si>
-  <si>
-    <t>"Werkopdracht beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Opdracht tot het uitvoeren van werkzaamheden met betrekking tot beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-249d0a16-d496-fe7e-69c1-c26c2ca4c376</t>
-  </si>
-  <si>
-    <t>"Zaak (BW)"@nl</t>
-  </si>
-  <si>
-    <t>"Een voor menselijke beheersing vatbaar stoffelijke object."@nl</t>
-  </si>
-  <si>
-    <t>[{"NLSBBNaamBrondocument":"Burgerlijk Wetboek - Boek 3","NLSBBUitleg":false,"NLSBBURL":false,"NLSBBBronverwijzing":false}]</t>
-  </si>
-  <si>
-    <t>"Zaak"@nl</t>
-  </si>
-  <si>
-    <t>"Een samenhangende hoeveelheid werk met een goed gedefinieerde aanleiding en eindresultaat."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-43688909-a30b-098b-caed-b2a12d487c5b","Begrip:Id-7cfb4fd3-49bc-2ca4-83ef-9a2aef13f222","Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08</t>
-  </si>
-  <si>
-    <t>"Zekerheidstellen"@nl</t>
-  </si>
-  <si>
-    <t>"Het veiligstellen van vermogen of voorwerpen teneinde te waarborgen dat een toekomstige financiële sanctie (zoals een geldboete, schadevergoedingsmaatregel of ontneming) daadwerkelijk kan worden verhaald."@nl</t>
-  </si>
-  <si>
     <t>Begrip:Id-c754fa6e-8705-af2d-1167-99c22b91a624</t>
   </si>
   <si>
@@ -1334,12 +1352,24 @@
     <t>Rol verduidelijkt.</t>
   </si>
   <si>
+    <t>Inhoudelijk</t>
+  </si>
+  <si>
+    <t>Definitie juridisch aangescherpt.</t>
+  </si>
+  <si>
+    <t>Doelstelling abstracter geformuleerd.</t>
+  </si>
+  <si>
+    <t>Afstand van voorwerp i.p.v. beslagvoorwerp verduidelijkt.</t>
+  </si>
+  <si>
+    <t>Begripstype</t>
+  </si>
+  <si>
     <t>PROV</t>
   </si>
   <si>
-    <t>Begripstype</t>
-  </si>
-  <si>
     <t>Activiteit</t>
   </si>
   <si>
@@ -1358,19 +1388,7 @@
     <t>Agent</t>
   </si>
   <si>
-    <t>"Het geheel van activiteiten gericht op het administreren van strafvorderlijk beslag en het beheren van de voorwerpen waarop strafvorderlijk beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Beslagbeheer"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagbewaarlocatie"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagbewaarruimte"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagbewaring"@nl</t>
+    <t>Doel/Activiteit</t>
   </si>
 </sst>
 </file>
@@ -1445,14 +1463,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1761,7 +1778,7 @@
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="9.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -1792,7 +1809,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1905,7 +1922,7 @@
       <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>46</v>
       </c>
       <c r="W2" t="s">
@@ -1931,7 +1948,7 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="W3" t="s">
@@ -1957,11 +1974,14 @@
       <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>55</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
@@ -1974,22 +1994,22 @@
       <c r="C5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>443</v>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" t="s">
+        <v>58</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
@@ -1997,25 +2017,25 @@
       <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO6" t="s">
         <v>59</v>
-      </c>
-      <c r="P6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
@@ -2023,22 +2043,22 @@
       <c r="C7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>62</v>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AO7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
@@ -2046,22 +2066,22 @@
       <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>64</v>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" t="s">
+        <v>69</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
         <v>43</v>
@@ -2070,27 +2090,27 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="R9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AJ9" t="s">
         <v>48</v>
       </c>
       <c r="AO9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
         <v>43</v>
@@ -2099,21 +2119,21 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="AJ10" t="s">
         <v>48</v>
       </c>
       <c r="AO10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
@@ -2122,24 +2142,24 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AJ11" t="s">
         <v>48</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2148,19 +2168,19 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AJ12" t="s">
         <v>48</v>
       </c>
       <c r="AO12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
@@ -2174,30 +2194,30 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="L13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="R13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="X13" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AJ13" t="s">
         <v>48</v>
       </c>
       <c r="AO13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
@@ -2206,18 +2226,18 @@
         <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="AO14" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
@@ -2226,24 +2246,24 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="W15" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s">
         <v>48</v>
       </c>
       <c r="AO15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
@@ -2252,30 +2272,30 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="Q16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R16" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="s">
         <v>48</v>
       </c>
       <c r="AO16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
         <v>43</v>
@@ -2284,33 +2304,33 @@
         <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="M17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="X17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AJ17" t="s">
         <v>48</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
         <v>43</v>
@@ -2319,21 +2339,21 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="AJ18" t="s">
         <v>48</v>
       </c>
       <c r="AO18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
         <v>43</v>
@@ -2342,24 +2362,24 @@
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="R19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
@@ -2368,27 +2388,27 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="L20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="X20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
@@ -2397,21 +2417,21 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="AJ21" t="s">
         <v>48</v>
       </c>
       <c r="AO21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
@@ -2420,18 +2440,18 @@
         <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="AO22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
@@ -2440,27 +2460,27 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>127</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="L23" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AJ23" t="s">
         <v>48</v>
       </c>
       <c r="AO23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
@@ -2469,21 +2489,21 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="AJ24" t="s">
         <v>48</v>
       </c>
       <c r="AO24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
@@ -2492,27 +2512,27 @@
         <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="W25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ25" t="s">
         <v>48</v>
       </c>
       <c r="AO25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
@@ -2521,21 +2541,21 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
@@ -2544,24 +2564,24 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="L27" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AJ27" t="s">
         <v>48</v>
       </c>
       <c r="AO27" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
@@ -2570,27 +2590,27 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="R28" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="S28" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="s">
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
@@ -2599,16 +2619,16 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="P29" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R29" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2616,7 +2636,7 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -2625,21 +2645,21 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
       </c>
       <c r="AO30" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s">
         <v>43</v>
@@ -2648,27 +2668,27 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="L31" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="S31" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ31" t="s">
         <v>48</v>
       </c>
       <c r="AO31" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -2677,24 +2697,24 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="W32" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s">
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -2703,24 +2723,24 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="S33" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -2729,24 +2749,24 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="P34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AJ34" t="s">
         <v>48</v>
       </c>
       <c r="AO34" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2755,21 +2775,21 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>175</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
       </c>
       <c r="AO35" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
@@ -2778,16 +2798,16 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="L36" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R36" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2795,7 +2815,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2804,24 +2824,24 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="W37" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ37" t="s">
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -2830,10 +2850,10 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2841,7 +2861,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2850,24 +2870,24 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E39" t="s">
-        <v>189</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -2876,21 +2896,21 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
       </c>
       <c r="AO40" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -2899,27 +2919,27 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>194</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="R41" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S41" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ41" t="s">
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -2928,27 +2948,27 @@
         <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F42" t="s">
-        <v>198</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>204</v>
       </c>
       <c r="L42" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -2957,21 +2977,21 @@
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>202</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
         <v>43</v>
@@ -2980,10 +3000,10 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -2991,7 +3011,7 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -3000,21 +3020,21 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>208</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
       </c>
       <c r="AO45" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s">
         <v>43</v>
@@ -3023,21 +3043,21 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
       </c>
       <c r="AO46" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
         <v>43</v>
@@ -3046,21 +3066,21 @@
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>214</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
       </c>
       <c r="AO47" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
         <v>43</v>
@@ -3069,10 +3089,10 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3080,7 +3100,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3089,16 +3109,16 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>219</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="P49" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R49" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3106,22 +3126,22 @@
     </row>
     <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" t="s">
+        <v>226</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q50" t="s">
         <v>60</v>
-      </c>
-      <c r="B50" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" t="s">
-        <v>221</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>58</v>
       </c>
       <c r="AJ50" t="s">
         <v>48</v>
@@ -3129,7 +3149,7 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
         <v>43</v>
@@ -3138,21 +3158,21 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>224</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -3161,16 +3181,16 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G52" t="s">
-        <v>228</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="S52" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3178,7 +3198,7 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
         <v>43</v>
@@ -3187,27 +3207,27 @@
         <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>231</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>237</v>
       </c>
       <c r="R53" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="S53" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ53" t="s">
         <v>48</v>
       </c>
       <c r="AO53" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B54" t="s">
         <v>43</v>
@@ -3216,21 +3236,21 @@
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>236</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>242</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
       </c>
       <c r="AO54" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
@@ -3239,18 +3259,18 @@
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>239</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="AO55" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
@@ -3259,21 +3279,21 @@
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>242</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
       </c>
       <c r="AO56" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
@@ -3282,21 +3302,21 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>245</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
       </c>
       <c r="AO57" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s">
         <v>43</v>
@@ -3305,21 +3325,21 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
       </c>
       <c r="AO58" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s">
         <v>43</v>
@@ -3328,18 +3348,18 @@
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>251</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="AO59" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -3348,21 +3368,21 @@
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>260</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
       </c>
       <c r="AO60" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
@@ -3371,24 +3391,24 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>257</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>258</v>
+        <v>262</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="S61" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AJ61" t="s">
         <v>48</v>
       </c>
       <c r="AO61" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
@@ -3397,24 +3417,24 @@
         <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="S62" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AJ62" t="s">
         <v>48</v>
       </c>
       <c r="AO62" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -3423,21 +3443,21 @@
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>266</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>272</v>
       </c>
       <c r="AJ63" t="s">
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s">
         <v>43</v>
@@ -3446,21 +3466,21 @@
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>269</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
       </c>
       <c r="AO64" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -3469,21 +3489,21 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>272</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>278</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
       </c>
       <c r="AO65" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
@@ -3492,21 +3512,21 @@
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>275</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
       </c>
       <c r="AO66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
@@ -3515,21 +3535,21 @@
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>278</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="AJ67" t="s">
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3538,16 +3558,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
-      </c>
-      <c r="J68" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="Q68" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="T68" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3555,7 +3575,7 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -3564,21 +3584,21 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>290</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
       </c>
       <c r="AO69" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -3587,13 +3607,13 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>287</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>293</v>
       </c>
       <c r="R70" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AJ70" t="s">
         <v>48</v>
@@ -3601,7 +3621,7 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s">
         <v>43</v>
@@ -3610,24 +3630,24 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>290</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>296</v>
       </c>
       <c r="W71" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s">
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3636,16 +3656,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>292</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="S72" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="T72" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3653,7 +3673,7 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -3662,24 +3682,24 @@
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>296</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="S73" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B74" t="s">
         <v>43</v>
@@ -3688,21 +3708,21 @@
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>299</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
       </c>
       <c r="AO74" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s">
         <v>43</v>
@@ -3711,21 +3731,21 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>302</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
       </c>
       <c r="AO75" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3734,27 +3754,27 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>304</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>310</v>
       </c>
       <c r="R76" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="S76" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ76" t="s">
         <v>48</v>
       </c>
       <c r="AO76" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s">
         <v>43</v>
@@ -3763,21 +3783,21 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>307</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>313</v>
       </c>
       <c r="AJ77" t="s">
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B78" t="s">
         <v>43</v>
@@ -3786,24 +3806,24 @@
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>310</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="L78" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AJ78" t="s">
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B79" t="s">
         <v>43</v>
@@ -3812,21 +3832,21 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>313</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>319</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
       </c>
       <c r="AO79" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s">
         <v>43</v>
@@ -3835,24 +3855,24 @@
         <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>316</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>322</v>
       </c>
       <c r="S80" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
       </c>
       <c r="AO80" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
         <v>43</v>
@@ -3861,21 +3881,21 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>319</v>
-      </c>
-      <c r="J81" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
       </c>
       <c r="AO81" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B82" t="s">
         <v>43</v>
@@ -3884,24 +3904,24 @@
         <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>322</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R82" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ82" t="s">
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B83" t="s">
         <v>43</v>
@@ -3910,24 +3930,24 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>326</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>332</v>
       </c>
       <c r="L83" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B84" t="s">
         <v>43</v>
@@ -3936,21 +3956,21 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>330</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>336</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
       </c>
       <c r="AO84" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B85" t="s">
         <v>43</v>
@@ -3959,21 +3979,21 @@
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>333</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>339</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
       </c>
       <c r="AO85" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s">
         <v>43</v>
@@ -3982,21 +4002,21 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>336</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>334</v>
+        <v>341</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>339</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
       </c>
       <c r="AO86" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -4005,13 +4025,13 @@
         <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>344</v>
       </c>
       <c r="P87" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4019,7 +4039,7 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -4028,21 +4048,21 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>341</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>347</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
       </c>
       <c r="AO88" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -4051,21 +4071,21 @@
         <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>344</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>350</v>
       </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -4074,24 +4094,24 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>353</v>
       </c>
       <c r="W90" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ90" t="s">
         <v>48</v>
       </c>
       <c r="AO90" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -4100,21 +4120,21 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>356</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
       </c>
       <c r="AO91" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -4123,24 +4143,24 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>354</v>
+        <v>358</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="W92" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ92" t="s">
         <v>48</v>
       </c>
       <c r="AO92" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -4149,21 +4169,21 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
       </c>
       <c r="AO93" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -4172,21 +4192,21 @@
         <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>359</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>360</v>
+        <v>364</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>365</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
       </c>
       <c r="AO94" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -4195,21 +4215,21 @@
         <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -4218,21 +4238,21 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>365</v>
-      </c>
-      <c r="J96" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
       </c>
       <c r="AO96" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -4241,21 +4261,21 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>368</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
       </c>
       <c r="AO97" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -4264,24 +4284,24 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>371</v>
-      </c>
-      <c r="J98" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>377</v>
       </c>
       <c r="R98" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -4290,27 +4310,27 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>374</v>
-      </c>
-      <c r="J99" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="R99" t="s">
         <v>375</v>
       </c>
-      <c r="R99" t="s">
-        <v>370</v>
-      </c>
       <c r="W99" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ99" t="s">
         <v>48</v>
       </c>
       <c r="AO99" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -4319,13 +4339,13 @@
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>377</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="S100" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4333,7 +4353,7 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -4342,21 +4362,21 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>380</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>381</v>
+        <v>385</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
       </c>
       <c r="AO101" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -4365,21 +4385,21 @@
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>383</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>389</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
       </c>
       <c r="AO102" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -4388,24 +4408,24 @@
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>386</v>
-      </c>
-      <c r="J103" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>392</v>
       </c>
       <c r="W103" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AJ103" t="s">
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -4414,21 +4434,21 @@
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>390</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
       </c>
       <c r="AO104" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -4437,21 +4457,21 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
-      </c>
-      <c r="J105" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
       </c>
       <c r="AO105" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -4460,21 +4480,21 @@
         <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>396</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>397</v>
+        <v>401</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>402</v>
       </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -4483,21 +4503,21 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>399</v>
-      </c>
-      <c r="J107" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>405</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
       </c>
       <c r="AO107" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -4506,21 +4526,21 @@
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>402</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>408</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
       </c>
       <c r="AO108" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4529,30 +4549,30 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>404</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="L109" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="R109" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="T109" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AJ109" t="s">
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -4561,16 +4581,16 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E110" t="s">
-        <v>410</v>
-      </c>
-      <c r="J110" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>416</v>
       </c>
       <c r="R110" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4578,7 +4598,7 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -4587,21 +4607,21 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>413</v>
-      </c>
-      <c r="J111" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>419</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
       </c>
       <c r="AO111" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -4610,18 +4630,18 @@
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>416</v>
-      </c>
-      <c r="J112" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>422</v>
       </c>
       <c r="AI112" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4630,16 +4650,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>419</v>
-      </c>
-      <c r="J113" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>425</v>
       </c>
       <c r="Q113" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="T113" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4647,7 +4667,7 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -4656,10 +4676,10 @@
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>423</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>429</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4668,12 +4688,12 @@
         <v>48</v>
       </c>
       <c r="AO114" t="s">
-        <v>49</v>
+        <v>430</v>
       </c>
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -4682,16 +4702,16 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>426</v>
-      </c>
-      <c r="J115" s="5" t="s">
-        <v>427</v>
+        <v>432</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4701,66 +4721,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>444</v>
+      <c r="A2" t="s">
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>445</v>
+      <c r="A3" t="s">
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>446</v>
+      <c r="A4" t="s">
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C8" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -4770,66 +4823,99 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>428</v>
+      <c r="A1" t="s">
+        <v>434</v>
       </c>
       <c r="B1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C1" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>444</v>
+      <c r="A2" t="s">
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>445</v>
+      <c r="A3" t="s">
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>446</v>
+      <c r="A4" t="s">
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74601483-0C97-438A-826A-EDBBA5A39931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB62F1C5-2914-4DF6-BE46-C43BA23D6565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
     <sheet name="Redactieoverzicht" sheetId="2" r:id="rId2"/>
     <sheet name="Begripstypering" sheetId="3" r:id="rId3"/>
+    <sheet name="Suggesties" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="472">
   <si>
     <t>Titel</t>
   </si>
@@ -275,103 +276,106 @@
     <t>"Beslagbeslissing"@nl</t>
   </si>
   <si>
-    <t>"Beslissing waarbij wordt vastgesteld welke rechtsgevolgen voor een beslag of beslagvoorwerp worden toegepast."@nl</t>
+    <t>"Beslissing waarin wordt vastgesteld welke rechtsgevolgen voor een beslag of voorwerpen waarop beslag rust van toepassing zijn."@nl</t>
   </si>
   <si>
     <t>"Er wordt niet gedifferentieerd naar beheerbeslissing en eindbeslissing, omdat in veel gevallen niet eenduidig is vast te stellen wanneer sprake is van een beheerbeslissing en wanneer van een eindbeslissing."@nl</t>
   </si>
   <si>
+    <t>ChatGPT – Semantic Review 03</t>
+  </si>
+  <si>
+    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
+  </si>
+  <si>
+    <t>"Beslagbewaarder"@nl</t>
+  </si>
+  <si>
+    <t>"Persoon of organisatie die verantwoordelijk is voor de feitelijke bewaring van beslagvoorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>"@nl"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagdoel"@nl</t>
+  </si>
+  <si>
+    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
+  </si>
+  <si>
+    <t>"Beslagdossier"@nl</t>
+  </si>
+  <si>
+    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
+  </si>
+  <si>
+    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
+  </si>
+  <si>
+    <t>"Beslagene"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
+  </si>
+  <si>
+    <t>"Beslaggrondslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagtitel"@nl</t>
+  </si>
+  <si>
+    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
+  </si>
+  <si>
+    <t>"Beslaghandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Beslaggebeurtenis"@nl</t>
+  </si>
+  <si>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
+  </si>
+  <si>
     <t>ChatGPT – Semantic Review 02</t>
   </si>
   <si>
-    <t>Begrip:Id-95443970-f0e1-d59b-5310-653015ad6b25</t>
-  </si>
-  <si>
-    <t>"Beslagbewaarder"@nl</t>
-  </si>
-  <si>
-    <t>"Persoon of organisatie die verantwoordelijk is voor de feitelijke bewaring van beslagvoorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>"@nl"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagdoel"@nl</t>
-  </si>
-  <si>
-    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
-  </si>
-  <si>
-    <t>"Beslagdossier"@nl</t>
-  </si>
-  <si>
-    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
-  </si>
-  <si>
-    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
-  </si>
-  <si>
-    <t>"Beslagene"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
-  </si>
-  <si>
-    <t>"Beslaggrondslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagtitel"@nl</t>
-  </si>
-  <si>
-    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
-  </si>
-  <si>
-    <t>"Beslaghandeling"@nl</t>
-  </si>
-  <si>
-    <t>"Beslaggebeurtenis"@nl</t>
-  </si>
-  <si>
-    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
-  </si>
-  <si>
     <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
   </si>
   <si>
     <t>"Beslagportaal"@nl</t>
   </si>
   <si>
-    <t>"Informatiesysteem voor de registratie en ondersteuning van processen rondom strafvorderlijk beslag."@nl</t>
+    <t>"Informatiesysteem dat de registratie en ondersteuning van processen rondom strafvorderlijk beslag verzorgt."@nl</t>
   </si>
   <si>
     <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
@@ -428,7 +432,7 @@
     <t>"Beslagobject"@nl</t>
   </si>
   <si>
-    <t>"Een voorwerp waarop beslag rust."@nl</t>
+    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
   </si>
   <si>
     <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
@@ -440,7 +444,7 @@
     <t>"Beslagzaak"@nl</t>
   </si>
   <si>
-    <t>"Samenhangend geheel van gegevens en handelingen met betrekking tot een strafvorderlijk beslag."@nl</t>
+    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
   </si>
   <si>
     <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
@@ -1389,6 +1393,57 @@
   </si>
   <si>
     <t>Doel/Activiteit</t>
+  </si>
+  <si>
+    <t>"Juridisch begrip"@nl</t>
+  </si>
+  <si>
+    <t>"Informatiesysteem"@nl</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Betreft</t>
+  </si>
+  <si>
+    <t>Suggestie</t>
+  </si>
+  <si>
+    <t>Prioriteit</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Definitie</t>
+  </si>
+  <si>
+    <t>Maak expliciet onderscheid tussen beslag en beslagvoorwerpen.</t>
+  </si>
+  <si>
+    <t>Hoog</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Nieuw begrip</t>
+  </si>
+  <si>
+    <t>"Afdoening"@nl</t>
+  </si>
+  <si>
+    <t>Overweeg opname indien domein dit vereist.</t>
+  </si>
+  <si>
+    <t>Laag</t>
+  </si>
+  <si>
+    <t>"Afhandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Afwikkelen"@nl</t>
   </si>
 </sst>
 </file>
@@ -1432,12 +1487,17 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1463,13 +1523,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2144,7 +2205,7 @@
       <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="6" t="s">
         <v>82</v>
       </c>
       <c r="L11" t="s">
@@ -2325,12 +2386,12 @@
         <v>48</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
         <v>43</v>
@@ -2339,21 +2400,21 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="4" t="s">
         <v>114</v>
       </c>
+      <c r="J18" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="AJ18" t="s">
         <v>48</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
         <v>43</v>
@@ -2362,19 +2423,19 @@
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -2388,27 +2449,27 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="X20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
@@ -2417,21 +2478,21 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AJ21" t="s">
         <v>48</v>
       </c>
       <c r="AO21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
@@ -2440,10 +2501,10 @@
         <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AO22" t="s">
         <v>95</v>
@@ -2451,7 +2512,7 @@
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
@@ -2460,27 +2521,27 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
-      </c>
-      <c r="J23" s="4" t="s">
         <v>133</v>
       </c>
+      <c r="J23" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="L23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AJ23" t="s">
         <v>48</v>
       </c>
       <c r="AO23" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
@@ -2489,21 +2550,21 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="J24" s="4" t="s">
         <v>137</v>
       </c>
+      <c r="J24" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="AJ24" t="s">
         <v>48</v>
       </c>
       <c r="AO24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
@@ -2512,13 +2573,13 @@
         <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W25" t="s">
         <v>106</v>
@@ -2527,12 +2588,12 @@
         <v>48</v>
       </c>
       <c r="AO25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
@@ -2541,10 +2602,10 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
@@ -2555,7 +2616,7 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
@@ -2564,24 +2625,24 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="s">
         <v>48</v>
       </c>
       <c r="AO27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
@@ -2590,13 +2651,13 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S28" t="s">
         <v>70</v>
@@ -2605,12 +2666,12 @@
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
@@ -2619,16 +2680,16 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P29" t="s">
         <v>101</v>
       </c>
       <c r="R29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2636,7 +2697,7 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -2645,10 +2706,10 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
@@ -2659,7 +2720,7 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
         <v>43</v>
@@ -2668,27 +2729,27 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ31" t="s">
         <v>48</v>
       </c>
       <c r="AO31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -2697,10 +2758,10 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W32" t="s">
         <v>99</v>
@@ -2709,12 +2770,12 @@
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -2723,24 +2784,24 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -2749,13 +2810,13 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AJ34" t="s">
         <v>48</v>
@@ -2766,7 +2827,7 @@
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2775,10 +2836,10 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
@@ -2789,7 +2850,7 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
@@ -2798,16 +2859,16 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2815,7 +2876,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2824,10 +2885,10 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="W37" t="s">
         <v>106</v>
@@ -2841,7 +2902,7 @@
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -2850,10 +2911,10 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2861,7 +2922,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2870,24 +2931,24 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -2896,10 +2957,10 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
@@ -2910,7 +2971,7 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -2919,13 +2980,13 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S41" t="s">
         <v>70</v>
@@ -2934,12 +2995,12 @@
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -2948,27 +3009,27 @@
         <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -2977,21 +3038,21 @@
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
         <v>43</v>
@@ -3000,10 +3061,10 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -3011,7 +3072,7 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -3020,10 +3081,10 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
@@ -3034,7 +3095,7 @@
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
         <v>43</v>
@@ -3043,10 +3104,10 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
@@ -3057,7 +3118,7 @@
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
         <v>43</v>
@@ -3066,10 +3127,10 @@
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
@@ -3080,7 +3141,7 @@
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
         <v>43</v>
@@ -3089,10 +3150,10 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3100,7 +3161,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3109,16 +3170,16 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P49" t="s">
         <v>101</v>
       </c>
       <c r="R49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3135,10 +3196,10 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q50" t="s">
         <v>60</v>
@@ -3149,7 +3210,7 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
         <v>43</v>
@@ -3158,21 +3219,21 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -3181,16 +3242,16 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3198,7 +3259,7 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s">
         <v>43</v>
@@ -3207,27 +3268,27 @@
         <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R53" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S53" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ53" t="s">
         <v>48</v>
       </c>
       <c r="AO53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
         <v>43</v>
@@ -3236,10 +3297,10 @@
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
@@ -3250,7 +3311,7 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
@@ -3259,10 +3320,10 @@
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO55" t="s">
         <v>95</v>
@@ -3270,7 +3331,7 @@
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
@@ -3279,10 +3340,10 @@
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
@@ -3293,7 +3354,7 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
@@ -3302,10 +3363,10 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
@@ -3316,7 +3377,7 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s">
         <v>43</v>
@@ -3325,10 +3386,10 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
@@ -3339,7 +3400,7 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B59" t="s">
         <v>43</v>
@@ -3348,10 +3409,10 @@
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO59" t="s">
         <v>95</v>
@@ -3359,7 +3420,7 @@
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -3368,10 +3429,10 @@
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
@@ -3382,7 +3443,7 @@
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
@@ -3391,24 +3452,24 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AJ61" t="s">
         <v>48</v>
       </c>
       <c r="AO61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
@@ -3417,24 +3478,24 @@
         <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AJ62" t="s">
         <v>48</v>
       </c>
       <c r="AO62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -3443,10 +3504,10 @@
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AJ63" t="s">
         <v>48</v>
@@ -3457,7 +3518,7 @@
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B64" t="s">
         <v>43</v>
@@ -3466,10 +3527,10 @@
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
@@ -3480,7 +3541,7 @@
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -3489,10 +3550,10 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
@@ -3503,7 +3564,7 @@
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
@@ -3512,10 +3573,10 @@
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
@@ -3526,7 +3587,7 @@
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
@@ -3535,10 +3596,10 @@
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ67" t="s">
         <v>48</v>
@@ -3549,7 +3610,7 @@
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3558,16 +3619,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q68" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3575,7 +3636,7 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -3584,10 +3645,10 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
@@ -3598,7 +3659,7 @@
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -3607,13 +3668,13 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R70" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AJ70" t="s">
         <v>48</v>
@@ -3621,7 +3682,7 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B71" t="s">
         <v>43</v>
@@ -3630,10 +3691,10 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W71" t="s">
         <v>99</v>
@@ -3647,7 +3708,7 @@
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3656,16 +3717,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3673,7 +3734,7 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -3682,24 +3743,24 @@
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s">
         <v>43</v>
@@ -3708,10 +3769,10 @@
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
@@ -3722,7 +3783,7 @@
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B75" t="s">
         <v>43</v>
@@ -3731,10 +3792,10 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
@@ -3745,7 +3806,7 @@
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3754,27 +3815,27 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="R76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ76" t="s">
         <v>48</v>
       </c>
       <c r="AO76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B77" t="s">
         <v>43</v>
@@ -3783,10 +3844,10 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AJ77" t="s">
         <v>48</v>
@@ -3797,7 +3858,7 @@
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B78" t="s">
         <v>43</v>
@@ -3806,10 +3867,10 @@
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L78" t="s">
         <v>88</v>
@@ -3823,7 +3884,7 @@
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B79" t="s">
         <v>43</v>
@@ -3832,10 +3893,10 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
@@ -3846,7 +3907,7 @@
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s">
         <v>43</v>
@@ -3855,13 +3916,13 @@
         <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="S80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
@@ -3872,7 +3933,7 @@
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s">
         <v>43</v>
@@ -3881,10 +3942,10 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
@@ -3895,7 +3956,7 @@
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" t="s">
         <v>43</v>
@@ -3904,10 +3965,10 @@
         <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R82" t="s">
         <v>106</v>
@@ -3916,12 +3977,12 @@
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s">
         <v>43</v>
@@ -3930,13 +3991,13 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L83" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
@@ -3947,7 +4008,7 @@
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B84" t="s">
         <v>43</v>
@@ -3956,10 +4017,10 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
@@ -3970,7 +4031,7 @@
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B85" t="s">
         <v>43</v>
@@ -3979,10 +4040,10 @@
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
@@ -3993,19 +4054,19 @@
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>341</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" t="s">
+        <v>342</v>
+      </c>
+      <c r="J86" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>341</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
@@ -4016,7 +4077,7 @@
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -4025,13 +4086,13 @@
         <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4039,7 +4100,7 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -4048,10 +4109,10 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
@@ -4062,7 +4123,7 @@
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -4071,21 +4132,21 @@
         <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -4094,10 +4155,10 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="W90" t="s">
         <v>106</v>
@@ -4111,7 +4172,7 @@
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -4120,10 +4181,10 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
@@ -4134,7 +4195,7 @@
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -4143,10 +4204,10 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="W92" t="s">
         <v>106</v>
@@ -4160,7 +4221,7 @@
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -4169,10 +4230,10 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
@@ -4183,7 +4244,7 @@
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -4192,10 +4253,10 @@
         <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
@@ -4206,7 +4267,7 @@
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -4215,21 +4276,21 @@
         <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -4238,10 +4299,10 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
@@ -4252,7 +4313,7 @@
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -4261,10 +4322,10 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
@@ -4275,7 +4336,7 @@
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -4284,24 +4345,24 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R98" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -4310,13 +4371,13 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R99" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="W99" t="s">
         <v>106</v>
@@ -4330,7 +4391,7 @@
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -4339,13 +4400,13 @@
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4353,7 +4414,7 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -4362,10 +4423,10 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
@@ -4376,7 +4437,7 @@
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -4385,10 +4446,10 @@
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
@@ -4399,7 +4460,7 @@
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -4408,10 +4469,10 @@
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="W103" t="s">
         <v>106</v>
@@ -4420,12 +4481,12 @@
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -4434,10 +4495,10 @@
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
@@ -4448,7 +4509,7 @@
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -4457,10 +4518,10 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
@@ -4471,7 +4532,7 @@
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -4480,21 +4541,21 @@
         <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -4503,10 +4564,10 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
@@ -4517,7 +4578,7 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -4526,10 +4587,10 @@
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
@@ -4540,7 +4601,7 @@
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4549,30 +4610,30 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L109" t="s">
         <v>88</v>
       </c>
       <c r="R109" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T109" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AJ109" t="s">
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -4581,16 +4642,16 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E110" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="R110" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4598,7 +4659,7 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -4607,10 +4668,10 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
@@ -4621,7 +4682,7 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -4630,18 +4691,18 @@
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AI112" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4650,16 +4711,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q113" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T113" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4667,7 +4728,7 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -4676,10 +4737,10 @@
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4688,12 +4749,12 @@
         <v>48</v>
       </c>
       <c r="AO114" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -4702,16 +4763,16 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4721,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4730,13 +4791,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4744,10 +4805,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4755,10 +4816,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" t="s">
         <v>439</v>
-      </c>
-      <c r="C3" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,10 +4827,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s">
         <v>439</v>
-      </c>
-      <c r="C4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4777,43 +4838,87 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" t="s">
         <v>440</v>
       </c>
-      <c r="C5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>441</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>441</v>
-      </c>
-      <c r="C7" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>441</v>
-      </c>
-      <c r="C8" t="s">
-        <v>444</v>
+      <c r="C10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -4823,7 +4928,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4832,13 +4937,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4951,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4962,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4973,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,43 +4984,182 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" t="s">
         <v>451</v>
       </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>456</v>
+      </c>
+      <c r="C10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C12" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B4" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" t="s">
+        <v>471</v>
+      </c>
       <c r="C5" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>453</v>
-      </c>
-      <c r="C7" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>447</v>
-      </c>
-      <c r="C8" t="s">
-        <v>448</v>
+        <v>468</v>
+      </c>
+      <c r="D5" t="s">
+        <v>469</v>
+      </c>
+      <c r="E5" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB62F1C5-2914-4DF6-BE46-C43BA23D6565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2632415A-6AF5-4212-B54A-A58B0D2546B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="476">
   <si>
     <t>Titel</t>
   </si>
@@ -300,276 +300,279 @@
     <t>"Beslagdoel"@nl</t>
   </si>
   <si>
-    <t>"Het doel binnen de beslaggrondslag dat met het leggen van beslag wordt beoogd."@nl</t>
+    <t>"Het met het leggen en voortduren van strafvorderlijk beslag beoogde juridische of feitelijke doel."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-5bc8a97f-bf01-7798-1307-e907207e3ff6","Begrip:Id-d868c447-ed7a-0685-ce65-bf207d2f5a08","Begrip:Id-eff5fa11-97ce-00da-6865-526d96b06be2"</t>
   </si>
   <si>
+    <t>ChatGPT – Semantic Review 04</t>
+  </si>
+  <si>
     <t>Begrip:Id-64a12e53-0ecc-f81f-02cb-7f95200719bf</t>
   </si>
   <si>
     <t>"Beslagdossier"@nl</t>
   </si>
   <si>
-    <t>"Een administratief en juridisch dossier waarin alle beslagstukken worden vastgelegd over een gelegd beslag op voorwerpen, geld of vorderingen, vanaf het moment van beslaglegging tot en met de uiteindelijke afwikkeling."@nl</t>
+    <t>"Een samenhangende verzameling van gegevens en documenten met betrekking tot een beslagzaak."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
+  </si>
+  <si>
+    <t>"Beslagene"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon of organisatie ten laste van wie strafvorderlijk beslag is gelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
+  </si>
+  <si>
+    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
+  </si>
+  <si>
+    <t>"Beslaggrondslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagtitel"@nl</t>
+  </si>
+  <si>
+    <t>"De wettelijke grondslag waarop het leggen van strafvorderlijk beslag berust."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
+  </si>
+  <si>
+    <t>"Beslaghandeling"@nl</t>
+  </si>
+  <si>
+    <t>"Beslaggebeurtenis"@nl</t>
+  </si>
+  <si>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
+  </si>
+  <si>
+    <t>ChatGPT – Semantic Review 02</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
+  </si>
+  <si>
+    <t>"Beslagportaal"@nl</t>
+  </si>
+  <si>
+    <t>"Informatiesysteem dat de registratie en ondersteuning van processen rondom strafvorderlijk beslag verzorgt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
+  </si>
+  <si>
+    <t>"Beslagproces"@nl</t>
+  </si>
+  <si>
+    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
+  </si>
+  <si>
+    <t>"Beslagrol"@nl</t>
+  </si>
+  <si>
+    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
+  </si>
+  <si>
+    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
+  </si>
+  <si>
+    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
+  </si>
+  <si>
+    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
+  </si>
+  <si>
+    <t>"Beslagstatus"@nl</t>
+  </si>
+  <si>
+    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
+  </si>
+  <si>
+    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
+  </si>
+  <si>
+    <t>"Beslagstuk"@nl</t>
+  </si>
+  <si>
+    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
   </si>
   <si>
     <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57</t>
-  </si>
-  <si>
-    <t>"Beslagene"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon onder wie het beslag is gelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5d3a2268-5178-37b1-1cfa-dde0abea5883</t>
+    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
+  </si>
+  <si>
+    <t>"Beslagvoorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagobject"@nl</t>
+  </si>
+  <si>
+    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
+  </si>
+  <si>
+    <t>"Beslagzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
+  </si>
+  <si>
+    <t>"Beslissen over beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Over beslag beslissen"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
+  </si>
+  <si>
+    <t>"Besluitname"@nl</t>
+  </si>
+  <si>
+    <t>Het vormen en vaststellen van een besluit.</t>
+  </si>
+  <si>
+    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
+  </si>
+  <si>
+    <t>"Bewijs van ontvangst"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
+  </si>
+  <si>
+    <t>"Buitenlands beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
+  </si>
+  <si>
+    <t>"Conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
+  </si>
+  <si>
+    <t>"Deponeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
+  </si>
+  <si>
+    <t>"Dier"@nl</t>
+  </si>
+  <si>
+    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
+  </si>
+  <si>
+    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
+  </si>
+  <si>
+    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
+  </si>
+  <si>
+    <t>"Eigenaar"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
+  </si>
+  <si>
+    <t>"Forensisch onderzoek"@nl</t>
+  </si>
+  <si>
+    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
+  </si>
+  <si>
+    <t>"Functionaris"@nl</t>
+  </si>
+  <si>
+    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
   </si>
   <si>
     <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d</t>
-  </si>
-  <si>
-    <t>"Beslaggrondslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagtitel"@nl</t>
-  </si>
-  <si>
-    <t>"De juridische basis voor het leggen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2","Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892</t>
-  </si>
-  <si>
-    <t>"Beslaghandeling"@nl</t>
-  </si>
-  <si>
-    <t>"Beslaggebeurtenis"@nl</t>
-  </si>
-  <si>
-    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
-  </si>
-  <si>
-    <t>ChatGPT – Semantic Review 02</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
-  </si>
-  <si>
-    <t>"Beslagportaal"@nl</t>
-  </si>
-  <si>
-    <t>"Informatiesysteem dat de registratie en ondersteuning van processen rondom strafvorderlijk beslag verzorgt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94</t>
-  </si>
-  <si>
-    <t>"Beslagproces"@nl</t>
-  </si>
-  <si>
-    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
-  </si>
-  <si>
-    <t>"Beslagrol"@nl</t>
-  </si>
-  <si>
-    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
-  </si>
-  <si>
-    <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
-  </si>
-  <si>
-    <t>"Begrip:Id-5160cb41-f6db-2021-5593-a692a42f7a57","Begrip:Id-8598f831-5728-5d6c-196f-fc842f1ed621","Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1"</t>
-  </si>
-  <si>
-    <t>Begrip:Id-129f62b6-852d-7ea3-880b-e8ab4bb84719</t>
-  </si>
-  <si>
-    <t>"Beslagstatus"@nl</t>
-  </si>
-  <si>
-    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
-  </si>
-  <si>
-    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
-  </si>
-  <si>
-    <t>"Beslagstuk"@nl</t>
-  </si>
-  <si>
-    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
-  </si>
-  <si>
-    <t>"Beslagvoorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagobject"@nl</t>
-  </si>
-  <si>
-    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
-  </si>
-  <si>
-    <t>"Beslagzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
-  </si>
-  <si>
-    <t>"Beslissen over beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Over beslag beslissen"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
-  </si>
-  <si>
-    <t>"Besluitname"@nl</t>
-  </si>
-  <si>
-    <t>Het vormen en vaststellen van een besluit.</t>
-  </si>
-  <si>
-    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
-  </si>
-  <si>
-    <t>"Bewijs van ontvangst"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
-  </si>
-  <si>
-    <t>"Buitenlands beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
-  </si>
-  <si>
-    <t>"Conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
-  </si>
-  <si>
-    <t>"Deponeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
-  </si>
-  <si>
-    <t>"Dier"@nl</t>
-  </si>
-  <si>
-    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
-  </si>
-  <si>
-    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
-  </si>
-  <si>
-    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
-  </si>
-  <si>
-    <t>"Eigenaar"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
-  </si>
-  <si>
-    <t>"Forensisch onderzoek"@nl</t>
-  </si>
-  <si>
-    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
-  </si>
-  <si>
-    <t>"Functionaris"@nl</t>
-  </si>
-  <si>
-    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
-  </si>
-  <si>
     <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
   </si>
   <si>
@@ -1399,6 +1402,15 @@
   </si>
   <si>
     <t>"Informatiesysteem"@nl</t>
+  </si>
+  <si>
+    <t>Doel</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Juridisch begrip</t>
   </si>
   <si>
     <t>Type</t>
@@ -2273,27 +2285,27 @@
         <v>48</v>
       </c>
       <c r="AO13" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO14" t="s">
         <v>92</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
@@ -2319,30 +2331,30 @@
         <v>48</v>
       </c>
       <c r="AO15" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
         <v>101</v>
       </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>102</v>
       </c>
-      <c r="E16" t="s">
+      <c r="J16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="Q16" t="s">
         <v>104</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>105</v>
       </c>
       <c r="R16" t="s">
         <v>70</v>
@@ -2351,59 +2363,59 @@
         <v>48</v>
       </c>
       <c r="AO16" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>107</v>
       </c>
-      <c r="E17" t="s">
+      <c r="J17" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="M17" t="s">
         <v>88</v>
       </c>
       <c r="R17" t="s">
+        <v>109</v>
+      </c>
+      <c r="X17" t="s">
         <v>110</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AJ17" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO17" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO17" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
         <v>113</v>
       </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="J18" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="AJ18" t="s">
         <v>48</v>
@@ -2414,28 +2426,28 @@
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="J19" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="R19" t="s">
         <v>118</v>
       </c>
-      <c r="R19" t="s">
-        <v>119</v>
-      </c>
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -2449,65 +2461,65 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="L20" t="s">
         <v>121</v>
       </c>
-      <c r="L20" t="s">
+      <c r="X20" t="s">
         <v>122</v>
       </c>
-      <c r="X20" t="s">
-        <v>123</v>
-      </c>
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
         <v>124</v>
       </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="J21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="AJ21" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO21" t="s">
         <v>126</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
         <v>128</v>
       </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="J22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="AO22" t="s">
         <v>130</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
@@ -2582,7 +2594,7 @@
         <v>142</v>
       </c>
       <c r="W25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ25" t="s">
         <v>48</v>
@@ -2686,7 +2698,7 @@
         <v>158</v>
       </c>
       <c r="P29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R29" t="s">
         <v>159</v>
@@ -2822,12 +2834,12 @@
         <v>48</v>
       </c>
       <c r="AO34" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2836,10 +2848,10 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
@@ -2850,7 +2862,7 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
@@ -2859,13 +2871,13 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R36" t="s">
         <v>167</v>
@@ -2876,7 +2888,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2885,24 +2897,24 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ37" t="s">
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -2911,10 +2923,10 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2922,7 +2934,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2931,13 +2943,13 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AJ39" t="s">
         <v>48</v>
@@ -2948,7 +2960,7 @@
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -2957,10 +2969,10 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
@@ -2980,10 +2992,10 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R41" t="s">
         <v>152</v>
@@ -3000,7 +3012,7 @@
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -3009,16 +3021,16 @@
         <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AJ42" t="s">
         <v>48</v>
@@ -3029,7 +3041,7 @@
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -3038,21 +3050,21 @@
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
         <v>43</v>
@@ -3061,10 +3073,10 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -3072,7 +3084,7 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -3081,10 +3093,10 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
@@ -3095,7 +3107,7 @@
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
         <v>43</v>
@@ -3104,10 +3116,10 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
@@ -3118,7 +3130,7 @@
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
         <v>43</v>
@@ -3127,10 +3139,10 @@
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
@@ -3141,7 +3153,7 @@
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
         <v>43</v>
@@ -3150,10 +3162,10 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3170,13 +3182,13 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R49" t="s">
         <v>156</v>
@@ -3196,10 +3208,10 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q50" t="s">
         <v>60</v>
@@ -3210,7 +3222,7 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
         <v>43</v>
@@ -3219,10 +3231,10 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AJ51" t="s">
         <v>48</v>
@@ -3233,7 +3245,7 @@
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -3242,13 +3254,13 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -3259,7 +3271,7 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s">
         <v>43</v>
@@ -3268,13 +3280,13 @@
         <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S53" t="s">
         <v>167</v>
@@ -3283,12 +3295,12 @@
         <v>48</v>
       </c>
       <c r="AO53" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B54" t="s">
         <v>43</v>
@@ -3297,10 +3309,10 @@
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
@@ -3311,7 +3323,7 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
@@ -3320,18 +3332,18 @@
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO55" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
@@ -3340,10 +3352,10 @@
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
@@ -3354,7 +3366,7 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
@@ -3363,10 +3375,10 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
@@ -3377,7 +3389,7 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s">
         <v>43</v>
@@ -3386,10 +3398,10 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
@@ -3400,7 +3412,7 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B59" t="s">
         <v>43</v>
@@ -3409,18 +3421,18 @@
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO59" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -3429,10 +3441,10 @@
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
@@ -3443,7 +3455,7 @@
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
@@ -3452,10 +3464,10 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S61" t="s">
         <v>175</v>
@@ -3464,12 +3476,12 @@
         <v>48</v>
       </c>
       <c r="AO61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
@@ -3478,24 +3490,24 @@
         <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AJ62" t="s">
         <v>48</v>
       </c>
       <c r="AO62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -3504,21 +3516,21 @@
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ63" t="s">
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s">
         <v>43</v>
@@ -3527,10 +3539,10 @@
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
@@ -3541,7 +3553,7 @@
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -3550,10 +3562,10 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
@@ -3564,7 +3576,7 @@
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
@@ -3573,10 +3585,10 @@
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
@@ -3587,7 +3599,7 @@
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
@@ -3596,16 +3608,16 @@
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AJ67" t="s">
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
@@ -3619,16 +3631,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q68" t="s">
         <v>176</v>
       </c>
       <c r="T68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3636,7 +3648,7 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -3645,10 +3657,10 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
@@ -3659,7 +3671,7 @@
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -3668,13 +3680,13 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AJ70" t="s">
         <v>48</v>
@@ -3682,7 +3694,7 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B71" t="s">
         <v>43</v>
@@ -3691,10 +3703,10 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W71" t="s">
         <v>99</v>
@@ -3703,12 +3715,12 @@
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3717,16 +3729,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S72" t="s">
         <v>179</v>
       </c>
       <c r="T72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3734,7 +3746,7 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -3743,10 +3755,10 @@
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S73" t="s">
         <v>175</v>
@@ -3760,7 +3772,7 @@
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s">
         <v>43</v>
@@ -3769,10 +3781,10 @@
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
@@ -3783,7 +3795,7 @@
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B75" t="s">
         <v>43</v>
@@ -3792,10 +3804,10 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
@@ -3806,7 +3818,7 @@
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3815,13 +3827,13 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="S76" t="s">
         <v>167</v>
@@ -3830,12 +3842,12 @@
         <v>48</v>
       </c>
       <c r="AO76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B77" t="s">
         <v>43</v>
@@ -3844,21 +3856,21 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AJ77" t="s">
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B78" t="s">
         <v>43</v>
@@ -3867,10 +3879,10 @@
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L78" t="s">
         <v>88</v>
@@ -3879,12 +3891,12 @@
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s">
         <v>43</v>
@@ -3893,10 +3905,10 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
@@ -3907,7 +3919,7 @@
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
         <v>43</v>
@@ -3916,13 +3928,13 @@
         <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
@@ -3933,7 +3945,7 @@
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B81" t="s">
         <v>43</v>
@@ -3942,10 +3954,10 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
@@ -3956,7 +3968,7 @@
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B82" t="s">
         <v>43</v>
@@ -3965,24 +3977,24 @@
         <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ82" t="s">
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s">
         <v>43</v>
@@ -3991,24 +4003,24 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L83" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s">
         <v>43</v>
@@ -4017,10 +4029,10 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
@@ -4031,7 +4043,7 @@
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
         <v>43</v>
@@ -4040,10 +4052,10 @@
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
@@ -4054,19 +4066,19 @@
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>342</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" t="s">
+        <v>343</v>
+      </c>
+      <c r="J86" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>342</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
@@ -4077,7 +4089,7 @@
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -4086,10 +4098,10 @@
         <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P87" t="s">
         <v>175</v>
@@ -4100,7 +4112,7 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -4109,10 +4121,10 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
@@ -4123,7 +4135,7 @@
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -4132,21 +4144,21 @@
         <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -4155,13 +4167,13 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="W90" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ90" t="s">
         <v>48</v>
@@ -4172,7 +4184,7 @@
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -4181,10 +4193,10 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
@@ -4195,7 +4207,7 @@
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -4204,13 +4216,13 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="W92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ92" t="s">
         <v>48</v>
@@ -4221,7 +4233,7 @@
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -4230,10 +4242,10 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
@@ -4244,7 +4256,7 @@
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -4253,10 +4265,10 @@
         <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
@@ -4267,7 +4279,7 @@
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -4276,10 +4288,10 @@
         <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AJ95" t="s">
         <v>48</v>
@@ -4290,7 +4302,7 @@
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -4299,10 +4311,10 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
@@ -4313,7 +4325,7 @@
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -4322,10 +4334,10 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
@@ -4336,7 +4348,7 @@
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -4345,24 +4357,24 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R98" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -4371,16 +4383,16 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R99" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ99" t="s">
         <v>48</v>
@@ -4391,7 +4403,7 @@
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -4400,10 +4412,10 @@
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S100" t="s">
         <v>167</v>
@@ -4414,7 +4426,7 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -4423,10 +4435,10 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
@@ -4437,7 +4449,7 @@
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -4446,10 +4458,10 @@
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
@@ -4460,7 +4472,7 @@
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -4469,24 +4481,24 @@
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="W103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AJ103" t="s">
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -4495,10 +4507,10 @@
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
@@ -4509,7 +4521,7 @@
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -4518,10 +4530,10 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
@@ -4532,7 +4544,7 @@
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -4541,21 +4553,21 @@
         <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -4564,10 +4576,10 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
@@ -4578,7 +4590,7 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -4587,10 +4599,10 @@
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
@@ -4610,19 +4622,19 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L109" t="s">
         <v>88</v>
       </c>
       <c r="R109" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T109" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ109" t="s">
         <v>48</v>
@@ -4633,7 +4645,7 @@
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -4642,13 +4654,13 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E110" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R110" t="s">
         <v>167</v>
@@ -4659,7 +4671,7 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -4668,10 +4680,10 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
@@ -4682,7 +4694,7 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -4691,13 +4703,13 @@
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AI112" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
@@ -4711,16 +4723,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T113" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4728,7 +4740,7 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -4737,10 +4749,10 @@
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4749,12 +4761,12 @@
         <v>48</v>
       </c>
       <c r="AO114" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -4763,16 +4775,16 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4782,7 +4794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4791,13 +4803,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4817,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4828,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" t="s">
         <v>440</v>
-      </c>
-      <c r="C3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4839,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" t="s">
         <v>440</v>
-      </c>
-      <c r="C4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4850,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,10 +4861,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,10 +4872,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,10 +4883,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,21 +4894,21 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4904,10 +4916,10 @@
         <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4915,9 +4927,53 @@
         <v>137</v>
       </c>
       <c r="B12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>441</v>
+      </c>
+      <c r="C14" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>441</v>
+      </c>
+      <c r="C16" t="s">
         <v>440</v>
       </c>
     </row>
@@ -4928,7 +4984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4937,13 +4993,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4951,10 +5007,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4962,10 +5018,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4973,10 +5029,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4984,10 +5040,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4995,10 +5051,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5006,10 +5062,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5017,10 +5073,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5028,21 +5084,21 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -5050,10 +5106,10 @@
         <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -5061,10 +5117,54 @@
         <v>137</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>451</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>459</v>
+      </c>
+      <c r="C14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>460</v>
+      </c>
+      <c r="C16" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -5079,87 +5179,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" t="s">
         <v>469</v>
-      </c>
-      <c r="E3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E4" t="s">
         <v>469</v>
-      </c>
-      <c r="E4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C5" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D5" t="s">
+        <v>473</v>
+      </c>
+      <c r="E5" t="s">
         <v>469</v>
-      </c>
-      <c r="E5" t="s">
-        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2632415A-6AF5-4212-B54A-A58B0D2546B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F56047-2103-4F3A-8E46-7C618DC7DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="480">
   <si>
     <t>Titel</t>
   </si>
@@ -354,7 +354,7 @@
     <t>"Beslaggebeurtenis"@nl</t>
   </si>
   <si>
-    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag."@nl</t>
+    <t>"Een activiteit die wordt uitgevoerd in het kader van het leggen, beheren of afwikkelen van strafvorderlijk beslag en die onderdeel uitmaakt van een beslagproces."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-20fbc366-da27-84cd-471d-3dc31d5b2818","Begrip:Id-7c43a980-a529-8d26-d9c5-46712970dd94"</t>
@@ -363,7 +363,7 @@
     <t>"Begrip:Id-4042164b-ee4b-7808-0ab1-842d69305d9d","Begrip:Id-60ca76c7-a48e-47b9-15ee-2fb9ad6c9f4b","Begrip:Id-654dfa9f-d10e-7b3c-eb67-2077adaad8be","Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478","Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50","Begrip:Id-e2598bbe-bab5-f454-a722-c8379608d604"</t>
   </si>
   <si>
-    <t>ChatGPT – Semantic Review 02</t>
+    <t>ChatGPT – Semantic Review 05</t>
   </si>
   <si>
     <t>Begrip:Id-7d991a97-eacd-e3b5-54d8-cf48bf53beb8</t>
@@ -381,7 +381,7 @@
     <t>"Beslagproces"@nl</t>
   </si>
   <si>
-    <t>"Het samenhangende geheel van beslaghandelingen dat wordt uitgevoerd vanaf het leggen tot en met de afwikkeling van een beslag."@nl</t>
+    <t>"Een samenhangend geheel van beslaghandelingen waarmee strafvorderlijk beslag gedurende zijn levenscyclus wordt uitgevoerd en afgehandeld."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-596dd23f-385d-aecd-fa46-d98a4e69a892","Begrip:Id-9717bcdf-19c1-a288-24a7-7ec01ae26b5c"</t>
@@ -390,7 +390,7 @@
     <t>"Beslagrol"@nl</t>
   </si>
   <si>
-    <t>"De verantwoordelijkheid of functie die een persoon of organisatie vervult binnen een beslagproces."@nl</t>
+    <t>"Een rol die de verantwoordelijkheden en bevoegdheden van een persoon of organisatie binnen een beslagproces beschrijft."@nl</t>
   </si>
   <si>
     <t>"Het begrip Persoon wordt hier gebruikt in de juridische zin, en kan daarom ook een rechtspersoon betreffen."@nl</t>
@@ -405,264 +405,264 @@
     <t>"Beslagstatus"@nl</t>
   </si>
   <si>
-    <t>"De eenduidige, administratieve aanduiding van de fase waarin een beslagvoorwerp zich bevindt."@nl</t>
+    <t>"De administratieve aanduiding van de actuele toestand waarin een beslagvoorwerp zich binnen het beslagproces bevindt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
+  </si>
+  <si>
+    <t>"Beslagstuk"@nl</t>
+  </si>
+  <si>
+    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
+  </si>
+  <si>
+    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
+  </si>
+  <si>
+    <t>"Beslagvoorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagobject"@nl</t>
+  </si>
+  <si>
+    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
+  </si>
+  <si>
+    <t>"Beslagzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
+  </si>
+  <si>
+    <t>"Beslissen over beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Over beslag beslissen"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
+  </si>
+  <si>
+    <t>"Besluitname"@nl</t>
+  </si>
+  <si>
+    <t>Het vormen en vaststellen van een besluit.</t>
+  </si>
+  <si>
+    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
+  </si>
+  <si>
+    <t>"Bewijs van ontvangst"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
+  </si>
+  <si>
+    <t>"Buitenlands beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
+  </si>
+  <si>
+    <t>"Conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
+  </si>
+  <si>
+    <t>"Deponeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
+  </si>
+  <si>
+    <t>"Dier"@nl</t>
+  </si>
+  <si>
+    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
+  </si>
+  <si>
+    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
+  </si>
+  <si>
+    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
+  </si>
+  <si>
+    <t>"Eigenaar"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
+  </si>
+  <si>
+    <t>"Forensisch onderzoek"@nl</t>
+  </si>
+  <si>
+    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
+  </si>
+  <si>
+    <t>"Functionaris"@nl</t>
+  </si>
+  <si>
+    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
+  </si>
+  <si>
+    <t>"Geldboete"@nl</t>
+  </si>
+  <si>
+    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
+  </si>
+  <si>
+    <t>"Goed"@nl</t>
+  </si>
+  <si>
+    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
+  </si>
+  <si>
+    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
+  </si>
+  <si>
+    <t>"In beslag nemen"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
+  </si>
+  <si>
+    <t>"Inbeheername"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
+  </si>
+  <si>
+    <t>"Inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"Inbeslagname"@nl</t>
+  </si>
+  <si>
+    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
+  </si>
+  <si>
+    <t>"Inbewaringname"@nl</t>
+  </si>
+  <si>
+    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
+  </si>
+  <si>
+    <t>"Internationaal beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
+  </si>
+  <si>
+    <t>"Kennisgeving van inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"KVI"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
+  </si>
+  <si>
+    <t>"Ketenbeslaghuis"@nl</t>
+  </si>
+  <si>
+    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
   </si>
   <si>
     <t>"2026-04-29 Toegevoegd door EB"@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-db13185d-3033-5d64-92d3-f7b7e9be28ce</t>
-  </si>
-  <si>
-    <t>"Beslagstuk"@nl</t>
-  </si>
-  <si>
-    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
-  </si>
-  <si>
-    <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
-  </si>
-  <si>
-    <t>"Beslagvoorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagobject"@nl</t>
-  </si>
-  <si>
-    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
-  </si>
-  <si>
-    <t>"Beslagzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
-  </si>
-  <si>
-    <t>"Beslissen over beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Over beslag beslissen"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
-  </si>
-  <si>
-    <t>"Besluitname"@nl</t>
-  </si>
-  <si>
-    <t>Het vormen en vaststellen van een besluit.</t>
-  </si>
-  <si>
-    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
-  </si>
-  <si>
-    <t>"Bewijs van ontvangst"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
-  </si>
-  <si>
-    <t>"Buitenlands beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
-  </si>
-  <si>
-    <t>"Conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
-  </si>
-  <si>
-    <t>"Deponeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
-  </si>
-  <si>
-    <t>"Dier"@nl</t>
-  </si>
-  <si>
-    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
-  </si>
-  <si>
-    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
-  </si>
-  <si>
-    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
-  </si>
-  <si>
-    <t>"Eigenaar"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
-  </si>
-  <si>
-    <t>"Forensisch onderzoek"@nl</t>
-  </si>
-  <si>
-    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
-  </si>
-  <si>
-    <t>"Functionaris"@nl</t>
-  </si>
-  <si>
-    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
-  </si>
-  <si>
-    <t>"Geldboete"@nl</t>
-  </si>
-  <si>
-    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
-  </si>
-  <si>
-    <t>"Goed"@nl</t>
-  </si>
-  <si>
-    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
-  </si>
-  <si>
-    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
-  </si>
-  <si>
-    <t>"In beslag nemen"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
-  </si>
-  <si>
-    <t>"Inbeheername"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
-  </si>
-  <si>
-    <t>"Inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"Inbeslagname"@nl</t>
-  </si>
-  <si>
-    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
-  </si>
-  <si>
-    <t>"Inbewaringname"@nl</t>
-  </si>
-  <si>
-    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
-  </si>
-  <si>
-    <t>"Internationaal beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
-  </si>
-  <si>
-    <t>"Kennisgeving van inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"KVI"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
-  </si>
-  <si>
-    <t>"Ketenbeslaghuis"@nl</t>
-  </si>
-  <si>
-    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
-  </si>
-  <si>
     <t>Begrip:Id-ccfae3bb-46be-0eac-3cf9-8cb4b9301522</t>
   </si>
   <si>
@@ -1371,6 +1371,9 @@
     <t>Afstand van voorwerp i.p.v. beslagvoorwerp verduidelijkt.</t>
   </si>
   <si>
+    <t>Inhoudelijke harmonisatie.</t>
+  </si>
+  <si>
     <t>Begripstype</t>
   </si>
   <si>
@@ -1411,6 +1414,15 @@
   </si>
   <si>
     <t>Juridisch begrip</t>
+  </si>
+  <si>
+    <t>"Activiteit"@nl</t>
+  </si>
+  <si>
+    <t>"Proces"@nl</t>
+  </si>
+  <si>
+    <t>"Toestand"@nl</t>
   </si>
   <si>
     <t>Type</t>
@@ -2499,50 +2511,50 @@
         <v>48</v>
       </c>
       <c r="AO21" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
         <v>127</v>
       </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="J22" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="AO22" t="s">
         <v>129</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
         <v>131</v>
       </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>132</v>
       </c>
-      <c r="E23" t="s">
+      <c r="J23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="L23" t="s">
         <v>134</v>
-      </c>
-      <c r="L23" t="s">
-        <v>135</v>
       </c>
       <c r="AJ23" t="s">
         <v>48</v>
@@ -2553,19 +2565,19 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
         <v>136</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="J24" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="AJ24" t="s">
         <v>48</v>
@@ -2576,22 +2588,22 @@
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
         <v>139</v>
       </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>140</v>
       </c>
-      <c r="E25" t="s">
+      <c r="J25" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="W25" t="s">
         <v>105</v>
@@ -2600,24 +2612,24 @@
         <v>48</v>
       </c>
       <c r="AO25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
         <v>144</v>
       </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="J26" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
@@ -2628,48 +2640,48 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
         <v>147</v>
       </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="J27" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="L27" t="s">
         <v>149</v>
       </c>
-      <c r="L27" t="s">
+      <c r="AJ27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO27" t="s">
         <v>150</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
         <v>152</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="J28" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="R28" t="s">
         <v>154</v>
-      </c>
-      <c r="R28" t="s">
-        <v>155</v>
       </c>
       <c r="S28" t="s">
         <v>70</v>
@@ -2678,30 +2690,30 @@
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
         <v>156</v>
       </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="J29" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="P29" t="s">
         <v>100</v>
       </c>
       <c r="R29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2709,19 +2721,19 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
         <v>160</v>
       </c>
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="J30" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
@@ -2732,48 +2744,48 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
         <v>163</v>
       </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="J31" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="L31" t="s">
         <v>165</v>
       </c>
-      <c r="L31" t="s">
+      <c r="S31" t="s">
         <v>166</v>
       </c>
-      <c r="S31" t="s">
+      <c r="AJ31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO31" t="s">
         <v>167</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
         <v>169</v>
       </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="J32" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="W32" t="s">
         <v>99</v>
@@ -2782,76 +2794,76 @@
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
         <v>172</v>
       </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="J33" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="S33" t="s">
         <v>174</v>
       </c>
-      <c r="S33" t="s">
-        <v>175</v>
-      </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
         <v>176</v>
       </c>
-      <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="J34" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="P34" t="s">
         <v>178</v>
       </c>
-      <c r="P34" t="s">
+      <c r="AJ34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO34" t="s">
         <v>179</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
         <v>181</v>
       </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="J35" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>183</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
@@ -2862,25 +2874,25 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>183</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
         <v>184</v>
       </c>
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="J36" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="L36" t="s">
         <v>186</v>
       </c>
-      <c r="L36" t="s">
-        <v>187</v>
-      </c>
       <c r="R36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2888,19 +2900,19 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
         <v>188</v>
       </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="J37" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="W37" t="s">
         <v>105</v>
@@ -2909,24 +2921,24 @@
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
         <v>191</v>
       </c>
-      <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="J38" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2934,45 +2946,45 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
         <v>194</v>
       </c>
-      <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>195</v>
       </c>
-      <c r="E39" t="s">
+      <c r="J39" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
         <v>198</v>
       </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="J40" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
@@ -2983,7 +2995,7 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -2992,13 +3004,13 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
+        <v>200</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="R41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S41" t="s">
         <v>70</v>
@@ -3007,59 +3019,59 @@
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
         <v>203</v>
       </c>
-      <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>204</v>
       </c>
-      <c r="F42" t="s">
+      <c r="J42" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="L42" t="s">
         <v>206</v>
       </c>
-      <c r="L42" t="s">
-        <v>207</v>
-      </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" t="s">
         <v>208</v>
       </c>
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="J43" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="AJ43" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO43" t="s">
         <v>210</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO43" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
@@ -3173,7 +3185,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3191,7 +3203,7 @@
         <v>100</v>
       </c>
       <c r="R49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3240,7 +3252,7 @@
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
@@ -3263,7 +3275,7 @@
         <v>236</v>
       </c>
       <c r="S52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3289,7 +3301,7 @@
         <v>240</v>
       </c>
       <c r="S53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ53" t="s">
         <v>48</v>
@@ -3338,7 +3350,7 @@
         <v>247</v>
       </c>
       <c r="AO55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
@@ -3427,7 +3439,7 @@
         <v>259</v>
       </c>
       <c r="AO59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
@@ -3470,7 +3482,7 @@
         <v>265</v>
       </c>
       <c r="S61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AJ61" t="s">
         <v>48</v>
@@ -3525,7 +3537,7 @@
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
@@ -3617,12 +3629,12 @@
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3637,7 +3649,7 @@
         <v>288</v>
       </c>
       <c r="Q68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T68" t="s">
         <v>289</v>
@@ -3715,7 +3727,7 @@
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
@@ -3735,7 +3747,7 @@
         <v>300</v>
       </c>
       <c r="S72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T72" t="s">
         <v>301</v>
@@ -3761,13 +3773,13 @@
         <v>304</v>
       </c>
       <c r="S73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
@@ -3836,7 +3848,7 @@
         <v>237</v>
       </c>
       <c r="S76" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ76" t="s">
         <v>48</v>
@@ -3865,7 +3877,7 @@
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
@@ -3891,7 +3903,7 @@
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
@@ -4015,7 +4027,7 @@
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
@@ -4104,7 +4116,7 @@
         <v>346</v>
       </c>
       <c r="P87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4153,7 +4165,7 @@
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
@@ -4297,7 +4309,7 @@
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
@@ -4369,7 +4381,7 @@
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
@@ -4418,7 +4430,7 @@
         <v>385</v>
       </c>
       <c r="S100" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4562,7 +4574,7 @@
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
@@ -4613,7 +4625,7 @@
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4640,7 +4652,7 @@
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
@@ -4663,7 +4675,7 @@
         <v>418</v>
       </c>
       <c r="R110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4714,7 +4726,7 @@
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4784,7 +4796,7 @@
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4794,7 +4806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4913,7 +4925,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
         <v>443</v>
@@ -4924,7 +4936,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>443</v>
@@ -4975,6 +4987,50 @@
       </c>
       <c r="C16" t="s">
         <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C20" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -4984,7 +5040,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4996,10 +5052,10 @@
         <v>436</v>
       </c>
       <c r="B1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5007,10 +5063,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5018,10 +5074,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,10 +5085,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5040,10 +5096,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5051,10 +5107,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5062,10 +5118,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5073,10 +5129,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5084,10 +5140,10 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5095,32 +5151,32 @@
         <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
         <v>411</v>
       </c>
       <c r="C11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5128,10 +5184,10 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -5139,10 +5195,10 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -5150,10 +5206,10 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -5161,10 +5217,54 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C16" t="s">
-        <v>452</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>462</v>
+      </c>
+      <c r="C17" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>463</v>
+      </c>
+      <c r="C18" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
+        <v>464</v>
+      </c>
+      <c r="C20" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5179,87 +5279,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D3" t="s">
+        <v>477</v>
+      </c>
+      <c r="E3" t="s">
         <v>473</v>
-      </c>
-      <c r="E3" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" t="s">
         <v>473</v>
-      </c>
-      <c r="E4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E5" t="s">
         <v>473</v>
-      </c>
-      <c r="E5" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F56047-2103-4F3A-8E46-7C618DC7DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F24666D-C53A-4EF9-8DD4-76AF2145244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="482">
   <si>
     <t>Titel</t>
   </si>
@@ -246,7 +246,7 @@
     <t>"Beslag"@nl</t>
   </si>
   <si>
-    <t>"Het strafvorderlijk dwangmiddel beslag dat rust op een voorwerp op basis van een beslaggrondslag met een beslagdoel."@nl</t>
+    <t>"Een dwangmiddel waarbij de beschikking over een voorwerp of vermogensbestanddeel krachtens de wet wordt beperkt ten behoeve van een strafvorderlijk doel."@nl</t>
   </si>
   <si>
     <t>"Begrip:Id-440dfbbb-fb6d-6ddb-a2ac-51c65dbaca1d","Begrip:Id-ed0256e4-f033-e2d6-4f89-ddb1faff482c"</t>
@@ -255,7 +255,7 @@
     <t>"Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9","Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e"</t>
   </si>
   <si>
-    <t>"Overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+    <t>ChatGPT – Semantic Review 06</t>
   </si>
   <si>
     <t>Begrip:Id-3989598e-4421-f771-2c30-be4aaabbe84b</t>
@@ -414,366 +414,363 @@
     <t>"Beslagstuk"@nl</t>
   </si>
   <si>
-    <t>"Een formeel document dat het leggen, voortzetten, beheren of afwikkelen van een beslag vastlegt en onderdeel uitmaakt van het beslagdossier."@nl</t>
+    <t>"Een document waarin gegevens of besluiten over het leggen, beheren, voortzetten of afwikkelen van strafvorderlijk beslag zijn vastgelegd en dat onderdeel uitmaakt van een beslagdossier."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
+  </si>
+  <si>
+    <t>"Beslagvoorwerp"@nl</t>
+  </si>
+  <si>
+    <t>"Beslagobject"@nl</t>
+  </si>
+  <si>
+    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
+  </si>
+  <si>
+    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
+  </si>
+  <si>
+    <t>"Beslagzaak"@nl</t>
+  </si>
+  <si>
+    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
+  </si>
+  <si>
+    <t>"Beslissen over beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Over beslag beslissen"@nl</t>
+  </si>
+  <si>
+    <t>"Een activiteit waarbij een beslissing wordt genomen over het leggen, voortzetten, wijzigen of beëindigen van strafvorderlijk beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
+  </si>
+  <si>
+    <t>"Besluitname"@nl</t>
+  </si>
+  <si>
+    <t>"De activiteit waarbij een besluit wordt gevormd en vastgesteld."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
+  </si>
+  <si>
+    <t>"Bewijs van ontvangst"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
+  </si>
+  <si>
+    <t>"Buitenlands beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
+  </si>
+  <si>
+    <t>"Conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
+  </si>
+  <si>
+    <t>"Deponeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
+  </si>
+  <si>
+    <t>"Dier"@nl</t>
+  </si>
+  <si>
+    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
+  </si>
+  <si>
+    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
+  </si>
+  <si>
+    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
+  </si>
+  <si>
+    <t>"Eigenaar"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
+  </si>
+  <si>
+    <t>"Forensisch onderzoek"@nl</t>
+  </si>
+  <si>
+    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
+  </si>
+  <si>
+    <t>"Functionaris"@nl</t>
+  </si>
+  <si>
+    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
+  </si>
+  <si>
+    <t>"Geldboete"@nl</t>
+  </si>
+  <si>
+    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
+  </si>
+  <si>
+    <t>"Goed"@nl</t>
+  </si>
+  <si>
+    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
+  </si>
+  <si>
+    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
+  </si>
+  <si>
+    <t>"In beslag nemen"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
+  </si>
+  <si>
+    <t>"Inbeheername"@nl</t>
+  </si>
+  <si>
+    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
+  </si>
+  <si>
+    <t>"Inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"Inbeslagname"@nl</t>
+  </si>
+  <si>
+    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
+  </si>
+  <si>
+    <t>"Inbewaringname"@nl</t>
+  </si>
+  <si>
+    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
+  </si>
+  <si>
+    <t>"Internationaal beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
+  </si>
+  <si>
+    <t>"Kennisgeving van inbeslagneming"@nl</t>
+  </si>
+  <si>
+    <t>"KVI"@nl</t>
+  </si>
+  <si>
+    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
+  </si>
+  <si>
+    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
+  </si>
+  <si>
+    <t>"Ketenbeslaghuis"@nl</t>
+  </si>
+  <si>
+    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
+  </si>
+  <si>
+    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ccfae3bb-46be-0eac-3cf9-8cb4b9301522</t>
+  </si>
+  <si>
+    <t>"Ketenpartner"@nl</t>
+  </si>
+  <si>
+    <t>"De rechtspersoon waarvan de functionaris een rol heeft in het beslagproces."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9b92f545-d3f4-7775-845e-2b4d8d7d7339</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag beschikking/arrest ontvangen"@nl</t>
+  </si>
+  <si>
+    <t>"Het ontvangen van een klaagschrift tegen een beschikking of arrest inzake beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c38718ba-8796-ee51-b1af-f20619ea8d7e</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag intrekken"@nl</t>
+  </si>
+  <si>
+    <t>"Het door de indiener beëindigen van een eerder ingediend klaagschrift."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-c9e37df7-a24c-7d35-ce7a-93c18f184746</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag ontvangen"@nl</t>
+  </si>
+  <si>
+    <t>"Het ontvangen van een klaagschrift dat betrekking heeft op beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-89190bf7-9961-04e0-3769-f03df5a4b1af</t>
+  </si>
+  <si>
+    <t>"Klaagschrift beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een bij de Rechtspraak ingediende klacht of verzoek ten aanzien van de toepassing van beslag."@nl</t>
+  </si>
+  <si>
+    <t>"Klassiek beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Beslag gebaseerd op art. 94 Sv."@nl</t>
+  </si>
+  <si>
+    <t>"Locatie"@nl</t>
+  </si>
+  <si>
+    <t>"Een bepaald punt of afgebakend gebied in de ruimte."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-af7b5f03-2b9a-72c0-a1de-2959bc89a3f4</t>
+  </si>
+  <si>
+    <t>"Machtiging tot conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een door de rechter-commissaris verleende machtiging tot het leggen of handhaven van conservatoir beslag."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8</t>
+  </si>
+  <si>
+    <t>"Natuurlijk persoon"@nl</t>
+  </si>
+  <si>
+    <t>"Natuurlijke persoon"@nl</t>
+  </si>
+  <si>
+    <t>"Een mens, in juridische context beschouwd als een drager van subjectieve rechten en plichten."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb</t>
+  </si>
+  <si>
+    <t>"Onroerende zaak"@nl</t>
+  </si>
+  <si>
+    <t>"Grond, nog niet gewonnen delfstoffen, met de grond verenigde beplantingen, alsmede gebouwen en andere werken zoals viaducten die al dan niet rechtstreeks duurzaam met de grond zijn verenigd (wortel en nagelvast)."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac</t>
+  </si>
+  <si>
+    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'. In die definitie wordt art. 3:3.1 BW als bron genoemd."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-a415d88a-0766-091f-7ea5-e2863a832873</t>
+  </si>
+  <si>
+    <t>"Ontbinden verkoop"@nl</t>
+  </si>
+  <si>
+    <t>"Het ongedaan maken van een eerder gesloten verkoopovereenkomst."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a1df63b-27e8-389e-5b77-0a423db2ba3e</t>
+  </si>
+  <si>
+    <t>"Ontbinding verkoop"@nl</t>
+  </si>
+  <si>
+    <t>"Ontbinding ná levering van het beslagvoorwerp door de koper wanneer dit is toegestaan vanuit de voorwaarden die door de DRZ aan de verkoop zijn verbonden."@nl</t>
   </si>
   <si>
     <t>"2026-06-02 N.a.v. mailtje van Theo Harder"@nl</t>
   </si>
   <si>
-    <t>Begrip:Id-9b57cea9-ae67-cf48-b5ac-a39c3d3a2e3f</t>
-  </si>
-  <si>
-    <t>"Beslagvoorwerp"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagobject"@nl</t>
-  </si>
-  <si>
-    <t>"Voorwerp waarop strafvorderlijk beslag rust."@nl</t>
-  </si>
-  <si>
-    <t>"Een beslagvoorwerp kan ook een verzameling van voorwerpen betreffen, bijvoorbeeld 'een partij voertuigen'. De betekenis van het begrip Voorwerp c.q. Beslagvoorwerp wijkt hier dus af van de intuïtieve betekenis."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8692ddf9-e586-9684-8728-6eb15a36cee9</t>
-  </si>
-  <si>
-    <t>"Beslagzaak"@nl</t>
-  </si>
-  <si>
-    <t>"Zaak waarin de gegevens en handelingen met betrekking tot een strafvorderlijk beslag worden vastgelegd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d1b636df-f9ef-310c-cdf5-84b28a4b3478</t>
-  </si>
-  <si>
-    <t>"Beslissen over beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Over beslag beslissen"@nl</t>
-  </si>
-  <si>
-    <t>"Beslagactiviteit waarbij een feitelijke beslissing over een beslagvoorwerp wordt genomen."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'.  Daar wordt de term OVER BESLAG BESLISSEN gebruikt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c6dbcc01-69aa-7abf-9fb7-9986f371f10c</t>
-  </si>
-  <si>
-    <t>"Besluitname"@nl</t>
-  </si>
-  <si>
-    <t>Het vormen en vaststellen van een besluit.</t>
-  </si>
-  <si>
-    <t>Begrip:Id-782b78ab-6d47-de69-2cb8-4693aefb2099</t>
-  </si>
-  <si>
-    <t>"Bewijs van ontvangst"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
-  </si>
-  <si>
-    <t>"Buitenlands beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
-  </si>
-  <si>
-    <t>"Conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
-  </si>
-  <si>
-    <t>"Deponeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
-  </si>
-  <si>
-    <t>"Dier"@nl</t>
-  </si>
-  <si>
-    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
-  </si>
-  <si>
-    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
-  </si>
-  <si>
-    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
-  </si>
-  <si>
-    <t>"Eigenaar"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
-  </si>
-  <si>
-    <t>"Forensisch onderzoek"@nl</t>
-  </si>
-  <si>
-    <t>"Een sporenonderzoek dat gedaan wordt ten behoeve van het strafrechtelijk onderzoek met als doel een analyse te maken van gebeurtenissen rond een misdrijf."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89fc0d86-feab-dce5-a16b-14384bf90f2d</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f51731f6-78b5-9973-0e98-96c4a800dd8d</t>
-  </si>
-  <si>
-    <t>"Functionaris"@nl</t>
-  </si>
-  <si>
-    <t>"Een persoon die één of meerdere rollen vervult in dienst van een organisatie."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c864aeb3-61db-a336-dd52-268b658fd02e</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit presentatie 'BIB Bedrijfslaag informatiediensten 14042026.pptx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-b0613c5a-9b15-73f4-0976-c8b0261f2205</t>
-  </si>
-  <si>
-    <t>"Geldboete"@nl</t>
-  </si>
-  <si>
-    <t>"Straf die bestaat uit de verplichting een geldbedrag te betalen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a5ec5c43-7afb-51bf-61cb-91c3a47efad7</t>
-  </si>
-  <si>
-    <t>"Goed"@nl</t>
-  </si>
-  <si>
-    <t>"Een zaak (binnen de context van het Burgerlijk Wetboek) of een vermogensrecht dat overdraagbaar is tussen personen."@nl</t>
-  </si>
-  <si>
-    <t>"LET OP: In het Beslag-domein wordt het begrip Goed vermeden. In plaats daarvan wordt het begrip Voorwerp gebruikt. Rationale hiervoor: het BW stelt dat een Goed alle Zaken en Vermogensrechten betreft. Het BW stelt ook expliciet dat Dier geen Zaak is, waarmee Dier dus ook geen Goed is. In het Beslag-domein dient Dier echter wél binnen de scope te liggen van datgene waarop beslag kan worden uitgevoerd. Daarom is Voorwerp als containerbegrip geïntroduceerd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-dba51235-56a7-f9cd-6c98-80b3aff09f50</t>
-  </si>
-  <si>
-    <t>"In beslag nemen"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij het dwangmiddel beslag op een voorwerp wordt toegepast."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c2fcc343-b5de-4c0f-5c50-0c0f0c251cf2</t>
-  </si>
-  <si>
-    <t>"Inbeheername"@nl</t>
-  </si>
-  <si>
-    <t>"De beslagactiviteit waarbij de beslagbeheerder het beslagvoorwerp tijdelijk onder zich neemt."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a2312469-fd38-a668-ae4a-f2c4c7c8b0bc</t>
-  </si>
-  <si>
-    <t>"Inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"Inbeslagname"@nl</t>
-  </si>
-  <si>
-    <t>"De toepassing van het strafvorderlijk dwangmiddel beslag op één of meer voorwerpen."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-5c9704d6-c3d9-4f86-dcfe-641ffeabe520</t>
-  </si>
-  <si>
-    <t>"Inbewaringname"@nl</t>
-  </si>
-  <si>
-    <t>"Het onder beheer nemen van een voorwerp ten behoeve van de bewaring daarvan."@nl</t>
-  </si>
-  <si>
-    <t>"Internationaal beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van een ander land door nederlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen die zich in nederland bevinden."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-d3913358-764a-0c40-c235-ae41d2b5805e</t>
-  </si>
-  <si>
-    <t>"Kennisgeving van inbeslagneming"@nl</t>
-  </si>
-  <si>
-    <t>"KVI"@nl</t>
-  </si>
-  <si>
-    <t>"Een overzicht van inbeslaggenomen voorwerpen waarmee het OM van een inbeslagneming op de hoogte wordt gesteld."@nl</t>
-  </si>
-  <si>
-    <t>"De opsporingsambtenaar maakt de KVI op t.b.v. het OM. De KVI is geen PV. Conform de wet en aanwijzing is de KVI alleen verplicht voor Klassiek beslag (94) en niet voor Conservatoir beslag (94a Sv)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-758fb5fc-bfad-345c-d64f-aee4e790fb2f</t>
-  </si>
-  <si>
-    <t>"Ketenbeslaghuis"@nl</t>
-  </si>
-  <si>
-    <t>"Een gespecialiseerde, centrale opslaglocatie en administratief knooppunt waar in beslag genomen goederen (zoals drugs, wapens, vals geld, auto's of administratie) worden beheerd, geregistreerd en opgeslagen tijdens strafrechtelijke onderzoeken."@nl</t>
-  </si>
-  <si>
-    <t>"2026-04-29 Toegevoegd door EB"@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ccfae3bb-46be-0eac-3cf9-8cb4b9301522</t>
-  </si>
-  <si>
-    <t>"Ketenpartner"@nl</t>
-  </si>
-  <si>
-    <t>"De rechtspersoon waarvan de functionaris een rol heeft in het beslagproces."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9b92f545-d3f4-7775-845e-2b4d8d7d7339</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag beschikking/arrest ontvangen"@nl</t>
-  </si>
-  <si>
-    <t>"Het ontvangen van een klaagschrift tegen een beschikking of arrest inzake beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c38718ba-8796-ee51-b1af-f20619ea8d7e</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag intrekken"@nl</t>
-  </si>
-  <si>
-    <t>"Het door de indiener beëindigen van een eerder ingediend klaagschrift."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-c9e37df7-a24c-7d35-ce7a-93c18f184746</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag ontvangen"@nl</t>
-  </si>
-  <si>
-    <t>"Het ontvangen van een klaagschrift dat betrekking heeft op beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-89190bf7-9961-04e0-3769-f03df5a4b1af</t>
-  </si>
-  <si>
-    <t>"Klaagschrift beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Een bij de Rechtspraak ingediende klacht of verzoek ten aanzien van de toepassing van beslag."@nl</t>
-  </si>
-  <si>
-    <t>"Klassiek beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94 Sv."@nl</t>
-  </si>
-  <si>
-    <t>"Locatie"@nl</t>
-  </si>
-  <si>
-    <t>"Een bepaald punt of afgebakend gebied in de ruimte."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-af7b5f03-2b9a-72c0-a1de-2959bc89a3f4</t>
-  </si>
-  <si>
-    <t>"Machtiging tot conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Een door de rechter-commissaris verleende machtiging tot het leggen of handhaven van conservatoir beslag."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ecdecb8f-1f43-9d9a-8bc8-6c57d67c2ba8</t>
-  </si>
-  <si>
-    <t>"Natuurlijk persoon"@nl</t>
-  </si>
-  <si>
-    <t>"Natuurlijke persoon"@nl</t>
-  </si>
-  <si>
-    <t>"Een mens, in juridische context beschouwd als een drager van subjectieve rechten en plichten."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-4a636974-c16e-6e3b-058b-4732c79a9ecb</t>
-  </si>
-  <si>
-    <t>"Onroerende zaak"@nl</t>
-  </si>
-  <si>
-    <t>"Grond, nog niet gewonnen delfstoffen, met de grond verenigde beplantingen, alsmede gebouwen en andere werken zoals viaducten die al dan niet rechtstreeks duurzaam met de grond zijn verenigd (wortel en nagelvast)."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-f3cea8e6-32c4-7f45-4fab-30ab2acadeac</t>
-  </si>
-  <si>
-    <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'. In die definitie wordt art. 3:3.1 BW als bron genoemd."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-a415d88a-0766-091f-7ea5-e2863a832873</t>
-  </si>
-  <si>
-    <t>"Ontbinden verkoop"@nl</t>
-  </si>
-  <si>
-    <t>"Het ongedaan maken van een eerder gesloten verkoopovereenkomst."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a1df63b-27e8-389e-5b77-0a423db2ba3e</t>
-  </si>
-  <si>
-    <t>"Ontbinding verkoop"@nl</t>
-  </si>
-  <si>
-    <t>"Ontbinding ná levering van het beslagvoorwerp door de koper wanneer dit is toegestaan vanuit de voorwaarden die door de DRZ aan de verkoop zijn verbonden."@nl</t>
-  </si>
-  <si>
     <t>Begrip:Id-01124c7a-0890-9d62-881c-7458464cefdf</t>
   </si>
   <si>
@@ -1425,6 +1422,9 @@
     <t>"Toestand"@nl</t>
   </si>
   <si>
+    <t>"Document"@nl</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1468,6 +1468,12 @@
   </si>
   <si>
     <t>"Afwikkelen"@nl</t>
+  </si>
+  <si>
+    <t>Onderzoeken of de definitie beter gebaseerd kan worden op functie of positie dan op verantwoordelijkheden en bevoegdheden.</t>
+  </si>
+  <si>
+    <t>Naar aanleiding van SR05</t>
   </si>
 </sst>
 </file>
@@ -2531,30 +2537,30 @@
         <v>128</v>
       </c>
       <c r="AO22" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
         <v>130</v>
       </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>131</v>
       </c>
-      <c r="E23" t="s">
+      <c r="J23" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="L23" t="s">
         <v>133</v>
-      </c>
-      <c r="L23" t="s">
-        <v>134</v>
       </c>
       <c r="AJ23" t="s">
         <v>48</v>
@@ -2565,19 +2571,19 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
         <v>135</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="J24" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="AJ24" t="s">
         <v>48</v>
@@ -2588,22 +2594,22 @@
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
         <v>138</v>
       </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>139</v>
       </c>
-      <c r="E25" t="s">
+      <c r="J25" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="W25" t="s">
         <v>105</v>
@@ -2612,76 +2618,76 @@
         <v>48</v>
       </c>
       <c r="AO25" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="AJ26" t="s">
         <v>48</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>145</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="L27" t="s">
         <v>147</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="AJ27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO27" t="s">
         <v>148</v>
-      </c>
-      <c r="L27" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="R28" t="s">
         <v>152</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="R28" t="s">
-        <v>154</v>
       </c>
       <c r="S28" t="s">
         <v>70</v>
@@ -2690,30 +2696,30 @@
         <v>48</v>
       </c>
       <c r="AO28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
+        <v>154</v>
+      </c>
+      <c r="J29" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>156</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="P29" t="s">
         <v>100</v>
       </c>
       <c r="R29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
@@ -2721,19 +2727,19 @@
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
+        <v>158</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>160</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
@@ -2744,48 +2750,48 @@
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="L31" t="s">
         <v>163</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="S31" t="s">
         <v>164</v>
       </c>
-      <c r="L31" t="s">
+      <c r="AJ31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO31" t="s">
         <v>165</v>
-      </c>
-      <c r="S31" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>167</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>169</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="W32" t="s">
         <v>99</v>
@@ -2794,76 +2800,76 @@
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="J33" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="S33" t="s">
         <v>172</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="S33" t="s">
-        <v>174</v>
-      </c>
       <c r="AJ33" t="s">
         <v>48</v>
       </c>
       <c r="AO33" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>174</v>
+      </c>
+      <c r="J34" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="P34" t="s">
         <v>176</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="AJ34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO34" t="s">
         <v>177</v>
-      </c>
-      <c r="P34" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
+        <v>179</v>
+      </c>
+      <c r="J35" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" t="s">
-        <v>181</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
@@ -2874,25 +2880,25 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="L36" t="s">
         <v>184</v>
       </c>
-      <c r="J36" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="L36" t="s">
-        <v>186</v>
-      </c>
       <c r="R36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AJ36" t="s">
         <v>48</v>
@@ -2900,19 +2906,19 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J37" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="s">
-        <v>188</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="W37" t="s">
         <v>105</v>
@@ -2921,24 +2927,24 @@
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
+        <v>189</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="s">
-        <v>191</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>192</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2946,45 +2952,45 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" t="s">
         <v>193</v>
       </c>
-      <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="J39" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E39" t="s">
-        <v>195</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>196</v>
-      </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>196</v>
+      </c>
+      <c r="J40" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>198</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
@@ -2995,7 +3001,7 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -3004,13 +3010,13 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="S41" t="s">
         <v>70</v>
@@ -3019,76 +3025,76 @@
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>201</v>
+      </c>
+      <c r="F42" t="s">
         <v>202</v>
       </c>
-      <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="J42" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F42" t="s">
+      <c r="L42" t="s">
         <v>204</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="L42" t="s">
-        <v>206</v>
-      </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" t="s">
+        <v>206</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="AJ43" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO43" t="s">
         <v>208</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO43" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>210</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" t="s">
-        <v>212</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -3096,19 +3102,19 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
-        <v>215</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
@@ -3119,19 +3125,19 @@
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>216</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="B46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
-        <v>218</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
@@ -3142,19 +3148,19 @@
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>218</v>
+      </c>
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>219</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
-        <v>221</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
@@ -3165,19 +3171,19 @@
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>221</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
+        <v>222</v>
+      </c>
+      <c r="J48" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="B48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" t="s">
-        <v>224</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3185,7 +3191,7 @@
     </row>
     <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
@@ -3194,16 +3200,16 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P49" t="s">
         <v>100</v>
       </c>
       <c r="R49" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AJ49" t="s">
         <v>48</v>
@@ -3220,10 +3226,10 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Q50" t="s">
         <v>60</v>
@@ -3234,48 +3240,48 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>228</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>229</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B51" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" t="s">
-        <v>231</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>232</v>
-      </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" t="s">
         <v>233</v>
       </c>
-      <c r="B52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="J52" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G52" t="s">
-        <v>235</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3283,48 +3289,48 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>235</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
+        <v>236</v>
+      </c>
+      <c r="J53" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B53" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="R53" t="s">
         <v>238</v>
       </c>
-      <c r="J53" s="4" t="s">
+      <c r="S53" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO53" t="s">
         <v>239</v>
-      </c>
-      <c r="R53" t="s">
-        <v>240</v>
-      </c>
-      <c r="S53" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO53" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>240</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>241</v>
+      </c>
+      <c r="J54" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="B54" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" t="s">
-        <v>243</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
@@ -3335,39 +3341,39 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" t="s">
+        <v>244</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B55" t="s">
-        <v>43</v>
-      </c>
-      <c r="C55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="AO55" t="s">
         <v>246</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="AO55" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" t="s">
         <v>248</v>
       </c>
-      <c r="B56" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="J56" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
@@ -3378,19 +3384,19 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>250</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" t="s">
         <v>251</v>
       </c>
-      <c r="B57" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" t="s">
-        <v>44</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="J57" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
@@ -3401,19 +3407,19 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>253</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" t="s">
         <v>254</v>
       </c>
-      <c r="B58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="J58" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
@@ -3424,39 +3430,39 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>256</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" t="s">
         <v>257</v>
       </c>
-      <c r="B59" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="J59" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="AO59" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>259</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" t="s">
         <v>260</v>
       </c>
-      <c r="B60" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="J60" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
@@ -3467,94 +3473,94 @@
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" t="s">
         <v>263</v>
       </c>
-      <c r="B61" t="s">
-        <v>43</v>
-      </c>
-      <c r="C61" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="J61" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="J61" s="4" t="s">
+      <c r="S61" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO61" t="s">
         <v>265</v>
-      </c>
-      <c r="S61" t="s">
-        <v>174</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO61" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>266</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" t="s">
         <v>267</v>
       </c>
-      <c r="B62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="J62" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J62" s="4" t="s">
+      <c r="S62" t="s">
         <v>269</v>
       </c>
-      <c r="S62" t="s">
+      <c r="AJ62" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO62" t="s">
         <v>270</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO62" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>271</v>
+      </c>
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" t="s">
         <v>272</v>
       </c>
-      <c r="B63" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="J63" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>274</v>
-      </c>
       <c r="AJ63" t="s">
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>274</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" t="s">
         <v>275</v>
       </c>
-      <c r="B64" t="s">
-        <v>43</v>
-      </c>
-      <c r="C64" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="J64" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
@@ -3565,19 +3571,19 @@
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
         <v>278</v>
       </c>
-      <c r="B65" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="J65" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
@@ -3588,19 +3594,19 @@
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
         <v>281</v>
       </c>
-      <c r="B66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C66" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="J66" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
@@ -3611,30 +3617,30 @@
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>283</v>
+      </c>
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
         <v>284</v>
       </c>
-      <c r="B67" t="s">
-        <v>43</v>
-      </c>
-      <c r="C67" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="J67" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>286</v>
-      </c>
       <c r="AJ67" t="s">
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3643,16 +3649,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
+        <v>286</v>
+      </c>
+      <c r="J68" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="J68" s="4" t="s">
+      <c r="Q68" t="s">
+        <v>173</v>
+      </c>
+      <c r="T68" t="s">
         <v>288</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>175</v>
-      </c>
-      <c r="T68" t="s">
-        <v>289</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3660,19 +3666,19 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>289</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" t="s">
         <v>290</v>
       </c>
-      <c r="B69" t="s">
-        <v>43</v>
-      </c>
-      <c r="C69" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="J69" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
@@ -3683,19 +3689,19 @@
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>292</v>
+      </c>
+      <c r="B70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C70" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" t="s">
         <v>293</v>
       </c>
-      <c r="B70" t="s">
-        <v>43</v>
-      </c>
-      <c r="C70" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="J70" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="R70" t="s">
         <v>115</v>
@@ -3706,19 +3712,19 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>295</v>
+      </c>
+      <c r="B71" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" t="s">
         <v>296</v>
       </c>
-      <c r="B71" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="J71" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="W71" t="s">
         <v>99</v>
@@ -3727,12 +3733,12 @@
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3741,16 +3747,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
+        <v>298</v>
+      </c>
+      <c r="J72" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="S72" t="s">
+        <v>176</v>
+      </c>
+      <c r="T72" t="s">
         <v>300</v>
-      </c>
-      <c r="S72" t="s">
-        <v>178</v>
-      </c>
-      <c r="T72" t="s">
-        <v>301</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3758,45 +3764,45 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" t="s">
         <v>302</v>
       </c>
-      <c r="B73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="J73" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="J73" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="S73" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>304</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" t="s">
         <v>305</v>
       </c>
-      <c r="B74" t="s">
-        <v>43</v>
-      </c>
-      <c r="C74" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="J74" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
@@ -3807,19 +3813,19 @@
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>307</v>
+      </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" t="s">
         <v>308</v>
       </c>
-      <c r="B75" t="s">
-        <v>43</v>
-      </c>
-      <c r="C75" t="s">
-        <v>44</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="J75" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
@@ -3830,7 +3836,7 @@
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3839,62 +3845,62 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
+        <v>310</v>
+      </c>
+      <c r="J76" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="R76" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S76" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AJ76" t="s">
         <v>48</v>
       </c>
       <c r="AO76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>312</v>
+      </c>
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" t="s">
         <v>313</v>
       </c>
-      <c r="B77" t="s">
-        <v>43</v>
-      </c>
-      <c r="C77" t="s">
-        <v>44</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="J77" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="J77" s="4" t="s">
-        <v>315</v>
-      </c>
       <c r="AJ77" t="s">
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>315</v>
+      </c>
+      <c r="B78" t="s">
+        <v>43</v>
+      </c>
+      <c r="C78" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" t="s">
         <v>316</v>
       </c>
-      <c r="B78" t="s">
-        <v>43</v>
-      </c>
-      <c r="C78" t="s">
-        <v>44</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="J78" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="L78" t="s">
         <v>88</v>
@@ -3903,24 +3909,24 @@
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>318</v>
+      </c>
+      <c r="B79" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79" t="s">
+        <v>44</v>
+      </c>
+      <c r="D79" t="s">
         <v>319</v>
       </c>
-      <c r="B79" t="s">
-        <v>43</v>
-      </c>
-      <c r="C79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="J79" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
@@ -3931,22 +3937,22 @@
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>321</v>
+      </c>
+      <c r="B80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" t="s">
         <v>322</v>
       </c>
-      <c r="B80" t="s">
-        <v>43</v>
-      </c>
-      <c r="C80" t="s">
-        <v>44</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="J80" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="S80" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
@@ -3957,19 +3963,19 @@
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>324</v>
+      </c>
+      <c r="B81" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" t="s">
         <v>325</v>
       </c>
-      <c r="B81" t="s">
-        <v>43</v>
-      </c>
-      <c r="C81" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="J81" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
@@ -3980,19 +3986,19 @@
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>327</v>
+      </c>
+      <c r="B82" t="s">
+        <v>43</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
         <v>328</v>
       </c>
-      <c r="B82" t="s">
-        <v>43</v>
-      </c>
-      <c r="C82" t="s">
-        <v>44</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="J82" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="R82" t="s">
         <v>105</v>
@@ -4001,50 +4007,50 @@
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>331</v>
+      </c>
+      <c r="B83" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" t="s">
         <v>332</v>
       </c>
-      <c r="B83" t="s">
-        <v>43</v>
-      </c>
-      <c r="C83" t="s">
-        <v>44</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="J83" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="J83" s="4" t="s">
+      <c r="L83" t="s">
         <v>334</v>
       </c>
-      <c r="L83" t="s">
-        <v>335</v>
-      </c>
       <c r="AJ83" t="s">
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>335</v>
+      </c>
+      <c r="B84" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84" t="s">
+        <v>44</v>
+      </c>
+      <c r="D84" t="s">
         <v>336</v>
       </c>
-      <c r="B84" t="s">
-        <v>43</v>
-      </c>
-      <c r="C84" t="s">
-        <v>44</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="J84" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
@@ -4055,19 +4061,19 @@
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>338</v>
+      </c>
+      <c r="B85" t="s">
+        <v>43</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" t="s">
         <v>339</v>
       </c>
-      <c r="B85" t="s">
-        <v>43</v>
-      </c>
-      <c r="C85" t="s">
-        <v>44</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="J85" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
@@ -4078,19 +4084,19 @@
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>341</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" t="s">
         <v>342</v>
       </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>343</v>
-      </c>
       <c r="J86" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
@@ -4101,22 +4107,22 @@
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>343</v>
+      </c>
+      <c r="B87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" t="s">
         <v>344</v>
       </c>
-      <c r="B87" t="s">
-        <v>43</v>
-      </c>
-      <c r="C87" t="s">
-        <v>44</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="J87" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="P87" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4124,19 +4130,19 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>346</v>
+      </c>
+      <c r="B88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" t="s">
         <v>347</v>
       </c>
-      <c r="B88" t="s">
-        <v>43</v>
-      </c>
-      <c r="C88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="J88" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
@@ -4147,42 +4153,42 @@
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>349</v>
+      </c>
+      <c r="B89" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" t="s">
         <v>350</v>
       </c>
-      <c r="B89" t="s">
-        <v>43</v>
-      </c>
-      <c r="C89" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="J89" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>352</v>
+      </c>
+      <c r="B90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" t="s">
         <v>353</v>
       </c>
-      <c r="B90" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" t="s">
-        <v>44</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="J90" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="W90" t="s">
         <v>105</v>
@@ -4196,19 +4202,19 @@
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>355</v>
+      </c>
+      <c r="B91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D91" t="s">
         <v>356</v>
       </c>
-      <c r="B91" t="s">
-        <v>43</v>
-      </c>
-      <c r="C91" t="s">
-        <v>44</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="J91" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
@@ -4219,19 +4225,19 @@
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>358</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" t="s">
         <v>359</v>
       </c>
-      <c r="B92" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="J92" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="W92" t="s">
         <v>105</v>
@@ -4245,19 +4251,19 @@
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>361</v>
+      </c>
+      <c r="B93" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" t="s">
         <v>362</v>
       </c>
-      <c r="B93" t="s">
-        <v>43</v>
-      </c>
-      <c r="C93" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="J93" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>364</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
@@ -4268,19 +4274,19 @@
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>364</v>
+      </c>
+      <c r="B94" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" t="s">
         <v>365</v>
       </c>
-      <c r="B94" t="s">
-        <v>43</v>
-      </c>
-      <c r="C94" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="J94" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
@@ -4291,42 +4297,42 @@
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>367</v>
+      </c>
+      <c r="B95" t="s">
+        <v>43</v>
+      </c>
+      <c r="C95" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" t="s">
         <v>368</v>
       </c>
-      <c r="B95" t="s">
-        <v>43</v>
-      </c>
-      <c r="C95" t="s">
-        <v>44</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="J95" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="J95" s="4" t="s">
-        <v>370</v>
-      </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>370</v>
+      </c>
+      <c r="B96" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" t="s">
         <v>371</v>
       </c>
-      <c r="B96" t="s">
-        <v>43</v>
-      </c>
-      <c r="C96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="J96" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
@@ -4337,19 +4343,19 @@
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>373</v>
+      </c>
+      <c r="B97" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" t="s">
         <v>374</v>
       </c>
-      <c r="B97" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" t="s">
-        <v>44</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="J97" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
@@ -4360,48 +4366,48 @@
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>376</v>
+      </c>
+      <c r="B98" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" t="s">
         <v>377</v>
       </c>
-      <c r="B98" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="J98" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="J98" s="4" t="s">
+      <c r="R98" t="s">
         <v>379</v>
       </c>
-      <c r="R98" t="s">
-        <v>380</v>
-      </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>379</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" t="s">
         <v>380</v>
       </c>
-      <c r="B99" t="s">
-        <v>43</v>
-      </c>
-      <c r="C99" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="J99" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="J99" s="4" t="s">
-        <v>382</v>
-      </c>
       <c r="R99" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="W99" t="s">
         <v>105</v>
@@ -4415,22 +4421,22 @@
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>382</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" t="s">
         <v>383</v>
       </c>
-      <c r="B100" t="s">
-        <v>43</v>
-      </c>
-      <c r="C100" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="J100" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="J100" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="S100" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AJ100" t="s">
         <v>48</v>
@@ -4438,19 +4444,19 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>385</v>
+      </c>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" t="s">
         <v>386</v>
       </c>
-      <c r="B101" t="s">
-        <v>43</v>
-      </c>
-      <c r="C101" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="J101" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
@@ -4461,19 +4467,19 @@
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>388</v>
+      </c>
+      <c r="B102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C102" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" t="s">
         <v>389</v>
       </c>
-      <c r="B102" t="s">
-        <v>43</v>
-      </c>
-      <c r="C102" t="s">
-        <v>44</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="J102" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
@@ -4484,19 +4490,19 @@
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>391</v>
+      </c>
+      <c r="B103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C103" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" t="s">
         <v>392</v>
       </c>
-      <c r="B103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C103" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="J103" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="W103" t="s">
         <v>105</v>
@@ -4505,24 +4511,24 @@
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>395</v>
+      </c>
+      <c r="B104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" t="s">
         <v>396</v>
       </c>
-      <c r="B104" t="s">
-        <v>43</v>
-      </c>
-      <c r="C104" t="s">
-        <v>44</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="J104" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
@@ -4533,19 +4539,19 @@
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>398</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" t="s">
         <v>399</v>
       </c>
-      <c r="B105" t="s">
-        <v>43</v>
-      </c>
-      <c r="C105" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="J105" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
@@ -4556,42 +4562,42 @@
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>401</v>
+      </c>
+      <c r="B106" t="s">
+        <v>43</v>
+      </c>
+      <c r="C106" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" t="s">
         <v>402</v>
       </c>
-      <c r="B106" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" t="s">
-        <v>44</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="J106" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="J106" s="4" t="s">
-        <v>404</v>
-      </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>404</v>
+      </c>
+      <c r="B107" t="s">
+        <v>43</v>
+      </c>
+      <c r="C107" t="s">
+        <v>44</v>
+      </c>
+      <c r="D107" t="s">
         <v>405</v>
       </c>
-      <c r="B107" t="s">
-        <v>43</v>
-      </c>
-      <c r="C107" t="s">
-        <v>44</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="J107" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
@@ -4602,19 +4608,19 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>407</v>
+      </c>
+      <c r="B108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108" t="s">
+        <v>44</v>
+      </c>
+      <c r="D108" t="s">
         <v>408</v>
       </c>
-      <c r="B108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C108" t="s">
-        <v>44</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="J108" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
@@ -4625,7 +4631,7 @@
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -4634,48 +4640,48 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
+        <v>410</v>
+      </c>
+      <c r="J109" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="L109" t="s">
         <v>88</v>
       </c>
       <c r="R109" t="s">
+        <v>412</v>
+      </c>
+      <c r="T109" t="s">
         <v>413</v>
       </c>
-      <c r="T109" t="s">
-        <v>414</v>
-      </c>
       <c r="AJ109" t="s">
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>414</v>
+      </c>
+      <c r="B110" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" t="s">
         <v>415</v>
       </c>
-      <c r="B110" t="s">
-        <v>43</v>
-      </c>
-      <c r="C110" t="s">
-        <v>44</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>416</v>
       </c>
-      <c r="E110" t="s">
+      <c r="J110" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="J110" s="4" t="s">
-        <v>418</v>
-      </c>
       <c r="R110" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AJ110" t="s">
         <v>48</v>
@@ -4683,19 +4689,19 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>418</v>
+      </c>
+      <c r="B111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" t="s">
+        <v>44</v>
+      </c>
+      <c r="D111" t="s">
         <v>419</v>
       </c>
-      <c r="B111" t="s">
-        <v>43</v>
-      </c>
-      <c r="C111" t="s">
-        <v>44</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="J111" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
@@ -4706,27 +4712,27 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>421</v>
+      </c>
+      <c r="B112" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" t="s">
+        <v>44</v>
+      </c>
+      <c r="D112" t="s">
         <v>422</v>
       </c>
-      <c r="B112" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" t="s">
-        <v>44</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="J112" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="J112" s="4" t="s">
+      <c r="AI112" t="s">
         <v>424</v>
-      </c>
-      <c r="AI112" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4735,16 +4741,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
+        <v>425</v>
+      </c>
+      <c r="J113" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="J113" s="4" t="s">
+      <c r="Q113" t="s">
+        <v>343</v>
+      </c>
+      <c r="T113" t="s">
         <v>427</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>344</v>
-      </c>
-      <c r="T113" t="s">
-        <v>428</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4752,19 +4758,19 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>428</v>
+      </c>
+      <c r="B114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" t="s">
         <v>429</v>
       </c>
-      <c r="B114" t="s">
-        <v>43</v>
-      </c>
-      <c r="C114" t="s">
-        <v>44</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="J114" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4773,30 +4779,30 @@
         <v>48</v>
       </c>
       <c r="AO114" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>432</v>
+      </c>
+      <c r="B115" t="s">
+        <v>43</v>
+      </c>
+      <c r="C115" t="s">
+        <v>44</v>
+      </c>
+      <c r="D115" t="s">
         <v>433</v>
       </c>
-      <c r="B115" t="s">
-        <v>43</v>
-      </c>
-      <c r="C115" t="s">
-        <v>44</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="J115" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="J115" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4806,7 +4812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -4815,13 +4821,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" t="s">
         <v>436</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>437</v>
-      </c>
-      <c r="C1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +4835,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C2" t="s">
         <v>439</v>
-      </c>
-      <c r="C2" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +4846,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +4857,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +4868,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,10 +4879,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" t="s">
         <v>443</v>
-      </c>
-      <c r="C6" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,10 +4890,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,10 +4901,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4906,10 +4912,10 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4917,32 +4923,32 @@
         <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4950,10 +4956,10 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4961,10 +4967,10 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4972,10 +4978,10 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4983,10 +4989,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4994,10 +5000,10 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5005,10 +5011,10 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5016,10 +5022,10 @@
         <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5027,10 +5033,54 @@
         <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>447</v>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" t="s">
+        <v>440</v>
+      </c>
+      <c r="C22" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>440</v>
+      </c>
+      <c r="C23" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>440</v>
+      </c>
+      <c r="C24" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -5040,7 +5090,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
@@ -5049,13 +5099,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C1" t="s">
         <v>448</v>
-      </c>
-      <c r="C1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5063,10 +5113,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C2" t="s">
         <v>450</v>
-      </c>
-      <c r="C2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5074,10 +5124,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C3" t="s">
         <v>452</v>
-      </c>
-      <c r="C3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5085,10 +5135,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C4" t="s">
         <v>452</v>
-      </c>
-      <c r="C4" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5096,10 +5146,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C5" t="s">
         <v>454</v>
-      </c>
-      <c r="C5" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5107,10 +5157,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" t="s">
         <v>450</v>
-      </c>
-      <c r="C6" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5118,10 +5168,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5129,10 +5179,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" t="s">
         <v>450</v>
-      </c>
-      <c r="C8" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5140,10 +5190,10 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5151,32 +5201,32 @@
         <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5184,10 +5234,10 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -5195,10 +5245,10 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -5206,10 +5256,10 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" t="s">
         <v>454</v>
-      </c>
-      <c r="C15" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -5217,10 +5267,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5228,10 +5278,10 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5239,10 +5289,10 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C18" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5250,10 +5300,10 @@
         <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5261,10 +5311,54 @@
         <v>124</v>
       </c>
       <c r="B20" t="s">
+        <v>463</v>
+      </c>
+      <c r="C20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" t="s">
         <v>464</v>
       </c>
-      <c r="C20" t="s">
-        <v>453</v>
+      <c r="C21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" t="s">
+        <v>461</v>
+      </c>
+      <c r="C22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>456</v>
+      </c>
+      <c r="C24" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -5274,10 +5368,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>465</v>
       </c>
@@ -5294,7 +5388,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>470</v>
       </c>
@@ -5311,7 +5405,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>474</v>
       </c>
@@ -5328,7 +5422,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>474</v>
       </c>
@@ -5345,7 +5439,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>474</v>
       </c>
@@ -5360,6 +5454,26 @@
       </c>
       <c r="E5" t="s">
         <v>473</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" t="s">
+        <v>472</v>
+      </c>
+      <c r="E6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F6" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Begrippenkader Beslag.xlsx
+++ b/excel/Begrippenkader Beslag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Mijn Documenten\GitHub\begrippenkader-beslag\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F24666D-C53A-4EF9-8DD4-76AF2145244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA99EFF1-0729-4BF1-B5C8-83A209BD9E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="483">
   <si>
     <t>Titel</t>
   </si>
@@ -468,73 +468,76 @@
     <t>"Bewijs van ontvangst"@nl</t>
   </si>
   <si>
-    <t>"Een overzicht van de bij een inbeslagneming inbeslaggenomen voorwerpen dat wordt verstrekt aan de beslagene."@nl</t>
+    <t>"Een document waarin de ontvangst van een voorwerp, document of geldbedrag wordt bevestigd."@nl</t>
   </si>
   <si>
     <t>"De opsporingsambtenaar maakt het Bewijs van ontvangst op en verstrekt het aan de Beslagene."@nl</t>
   </si>
   <si>
+    <t>ChatGPT – Semantic Review 07</t>
+  </si>
+  <si>
+    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
+  </si>
+  <si>
+    <t>"Buitenlands beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een vorm van beslag die wordt gelegd of uitgevoerd in het kader van internationale samenwerking met een andere staat."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
+  </si>
+  <si>
+    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
+  </si>
+  <si>
+    <t>"Conservatoir beslag"@nl</t>
+  </si>
+  <si>
+    <t>"Een vorm van beslag die wordt gelegd ter bewaring van verhaalsmogelijkheden of ten behoeve van een mogelijke ontnemingsmaatregel."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
+  </si>
+  <si>
+    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
+  </si>
+  <si>
+    <t>"Deponeren"@nl</t>
+  </si>
+  <si>
+    <t>"Het onderbrengen van een beslagvoorwerp op een aangewezen bewaarlocatie ten behoeve van bewaring."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
+  </si>
+  <si>
+    <t>"Dier"@nl</t>
+  </si>
+  <si>
+    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
+  </si>
+  <si>
+    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
+  </si>
+  <si>
+    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
+  </si>
+  <si>
+    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
+  </si>
+  <si>
+    <t>"Eigenaar"@nl</t>
+  </si>
+  <si>
+    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
+  </si>
+  <si>
     <t>"Definitie overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-8a89b0d7-d5ca-77c6-450b-28a5eaad3de9</t>
-  </si>
-  <si>
-    <t>"Buitenlands beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag dat op verzoek van nederlandse opsporingsdiensten of justitie door buitenlandse opsporingsdiensten of organisaties wordt gelegd op voorwerpen in het betreffende land."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9fe940a8-0462-1c07-6c4a-634cb1bd5c5e</t>
-  </si>
-  <si>
-    <t>Begrip:Id-9abcf6fc-3029-663b-10af-2346dd3a6351</t>
-  </si>
-  <si>
-    <t>"Conservatoir beslag"@nl</t>
-  </si>
-  <si>
-    <t>"Beslag gebaseerd op art. 94a Sv."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-1a319838-93ac-74fd-a959-f95195f05af2</t>
-  </si>
-  <si>
-    <t>Begrip:Id-fd583045-cab9-9f65-2b5d-20a5ece6c6b6</t>
-  </si>
-  <si>
-    <t>"Deponeren"@nl</t>
-  </si>
-  <si>
-    <t>"Het onderbrengen van een voorwerp op een aangewezen locatie ten behoeve van bewaring."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-0d3c6e8f-43b7-b23b-2b1d-99131054a12e</t>
-  </si>
-  <si>
-    <t>"Dier"@nl</t>
-  </si>
-  <si>
-    <t>"Een levend wezen, niet zijnde een mens."@nl</t>
-  </si>
-  <si>
-    <t>"Het BW stelt dat een dier geen Zaak is, maar dezelfde rechtsregels als op Zaak zijn erop van toepassing (art. 3:2a.1 BW). Binnen het beslagproces wordt Dier beschouwd als Roerende zaak en niet afzonderlijk onderkend."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-e0fd2c38-3271-31ae-5f28-f50f6c396ce5</t>
-  </si>
-  <si>
-    <t>"Definitie (en toelichting) overgenomen uit document '20210908 Ontologie ketenproces beslag v1.0.docx'."@nl</t>
-  </si>
-  <si>
-    <t>Begrip:Id-ba65708d-2d6b-2639-529b-01276e69bdd1</t>
-  </si>
-  <si>
-    <t>"Eigenaar"@nl</t>
-  </si>
-  <si>
-    <t>"De persoon met het meest omvattende recht dat een persoon op een voorwerp kan hebben."@nl</t>
   </si>
   <si>
     <t>Begrip:Id-cadf0452-7d69-ed6d-47ce-6c3a4556a42d</t>
@@ -1517,27 +1520,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1553,14 +1541,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1869,7 +1856,7 @@
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="10" max="10" width="9.140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -1900,7 +1887,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -2013,7 +2000,7 @@
       <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>46</v>
       </c>
       <c r="W2" t="s">
@@ -2039,7 +2026,7 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="W3" t="s">
@@ -2065,7 +2052,7 @@
       <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="AJ4" t="s">
@@ -2094,7 +2081,7 @@
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="1" t="s">
+      <c r="AO5" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2111,7 +2098,7 @@
       <c r="D6" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="P6" t="s">
@@ -2137,7 +2124,7 @@
       <c r="D7" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AJ7" t="s">
@@ -2166,7 +2153,7 @@
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
-      <c r="AO8" s="1" t="s">
+      <c r="AO8" s="4" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2183,7 +2170,7 @@
       <c r="D9" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="R9" t="s">
@@ -2212,7 +2199,7 @@
       <c r="D10" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="2" t="s">
         <v>78</v>
       </c>
       <c r="AJ10" t="s">
@@ -2235,7 +2222,7 @@
       <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="L11" t="s">
@@ -2244,7 +2231,7 @@
       <c r="AJ11" t="s">
         <v>48</v>
       </c>
-      <c r="AO11" s="2" t="s">
+      <c r="AO11" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2261,7 +2248,7 @@
       <c r="D12" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="L12" t="s">
@@ -2287,7 +2274,7 @@
       <c r="D13" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="L13" t="s">
@@ -2319,7 +2306,7 @@
       <c r="D14" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="2" t="s">
         <v>95</v>
       </c>
       <c r="AO14" t="s">
@@ -2339,7 +2326,7 @@
       <c r="D15" t="s">
         <v>97</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="2" t="s">
         <v>98</v>
       </c>
       <c r="W15" t="s">
@@ -2368,7 +2355,7 @@
       <c r="E16" t="s">
         <v>102</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="2" t="s">
         <v>103</v>
       </c>
       <c r="Q16" t="s">
@@ -2400,7 +2387,7 @@
       <c r="E17" t="s">
         <v>107</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M17" t="s">
@@ -2415,7 +2402,7 @@
       <c r="AJ17" t="s">
         <v>48</v>
       </c>
-      <c r="AO17" s="2" t="s">
+      <c r="AO17" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2432,7 +2419,7 @@
       <c r="D18" t="s">
         <v>113</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="2" t="s">
         <v>114</v>
       </c>
       <c r="AJ18" t="s">
@@ -2455,7 +2442,7 @@
       <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="2" t="s">
         <v>117</v>
       </c>
       <c r="R19" t="s">
@@ -2464,7 +2451,7 @@
       <c r="AJ19" t="s">
         <v>48</v>
       </c>
-      <c r="AO19" s="2" t="s">
+      <c r="AO19" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2481,7 +2468,7 @@
       <c r="D20" t="s">
         <v>119</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="2" t="s">
         <v>120</v>
       </c>
       <c r="L20" t="s">
@@ -2493,7 +2480,7 @@
       <c r="AJ20" t="s">
         <v>48</v>
       </c>
-      <c r="AO20" s="2" t="s">
+      <c r="AO20" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2510,7 +2497,7 @@
       <c r="D21" t="s">
         <v>124</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="2" t="s">
         <v>125</v>
       </c>
       <c r="AJ21" t="s">
@@ -2533,7 +2520,7 @@
       <c r="D22" t="s">
         <v>127</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="2" t="s">
         <v>128</v>
       </c>
       <c r="AO22" t="s">
@@ -2556,7 +2543,7 @@
       <c r="E23" t="s">
         <v>131</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="2" t="s">
         <v>132</v>
       </c>
       <c r="L23" t="s">
@@ -2582,7 +2569,7 @@
       <c r="D24" t="s">
         <v>135</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="2" t="s">
         <v>136</v>
       </c>
       <c r="AJ24" t="s">
@@ -2608,7 +2595,7 @@
       <c r="E25" t="s">
         <v>139</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="2" t="s">
         <v>140</v>
       </c>
       <c r="W25" t="s">
@@ -2634,13 +2621,13 @@
       <c r="D26" t="s">
         <v>142</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="2" t="s">
         <v>143</v>
       </c>
       <c r="AJ26" t="s">
         <v>48</v>
       </c>
-      <c r="AO26" s="1" t="s">
+      <c r="AO26" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2657,7 +2644,7 @@
       <c r="D27" t="s">
         <v>145</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="2" t="s">
         <v>146</v>
       </c>
       <c r="L27" t="s">
@@ -2683,7 +2670,7 @@
       <c r="D28" t="s">
         <v>150</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="2" t="s">
         <v>151</v>
       </c>
       <c r="R28" t="s">
@@ -2712,7 +2699,7 @@
       <c r="D29" t="s">
         <v>154</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="2" t="s">
         <v>155</v>
       </c>
       <c r="P29" t="s">
@@ -2723,6 +2710,9 @@
       </c>
       <c r="AJ29" t="s">
         <v>48</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
@@ -2738,14 +2728,14 @@
       <c r="D30" t="s">
         <v>158</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="3" t="s">
         <v>159</v>
       </c>
       <c r="AJ30" t="s">
         <v>48</v>
       </c>
       <c r="AO30" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
@@ -2761,7 +2751,7 @@
       <c r="D31" t="s">
         <v>161</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="2" t="s">
         <v>162</v>
       </c>
       <c r="L31" t="s">
@@ -2790,7 +2780,7 @@
       <c r="D32" t="s">
         <v>167</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="2" t="s">
         <v>168</v>
       </c>
       <c r="W32" t="s">
@@ -2800,38 +2790,38 @@
         <v>48</v>
       </c>
       <c r="AO32" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO33" t="s">
         <v>169</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" t="s">
-        <v>170</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="S33" t="s">
-        <v>172</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
@@ -2840,24 +2830,24 @@
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
-      </c>
-      <c r="J34" s="4" t="s">
         <v>175</v>
       </c>
+      <c r="J34" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="P34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ34" t="s">
         <v>48</v>
       </c>
       <c r="AO34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
         <v>43</v>
@@ -2866,10 +2856,10 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
-      </c>
-      <c r="J35" s="4" t="s">
         <v>180</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="AJ35" t="s">
         <v>48</v>
@@ -2880,7 +2870,7 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
@@ -2889,13 +2879,13 @@
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
-      </c>
-      <c r="J36" s="4" t="s">
         <v>183</v>
       </c>
+      <c r="J36" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="L36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R36" t="s">
         <v>164</v>
@@ -2906,7 +2896,7 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2915,10 +2905,10 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
-      </c>
-      <c r="J37" s="4" t="s">
         <v>187</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="W37" t="s">
         <v>105</v>
@@ -2927,12 +2917,12 @@
         <v>48</v>
       </c>
       <c r="AO37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
         <v>43</v>
@@ -2941,10 +2931,10 @@
         <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
-      </c>
-      <c r="J38" s="4" t="s">
         <v>190</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="AJ38" t="s">
         <v>48</v>
@@ -2952,7 +2942,7 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
@@ -2961,24 +2951,24 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
-      </c>
-      <c r="J39" s="4" t="s">
         <v>194</v>
       </c>
+      <c r="J39" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="AJ39" t="s">
         <v>48</v>
       </c>
       <c r="AO39" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
         <v>43</v>
@@ -2987,10 +2977,10 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
-      </c>
-      <c r="J40" s="4" t="s">
         <v>197</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="AJ40" t="s">
         <v>48</v>
@@ -3010,10 +3000,10 @@
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
-      </c>
-      <c r="J41" s="4" t="s">
         <v>199</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="R41" t="s">
         <v>149</v>
@@ -3025,12 +3015,12 @@
         <v>48</v>
       </c>
       <c r="AO41" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -3039,27 +3029,27 @@
         <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F42" t="s">
-        <v>202</v>
-      </c>
-      <c r="J42" s="4" t="s">
         <v>203</v>
       </c>
+      <c r="J42" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="L42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AJ42" t="s">
         <v>48</v>
       </c>
       <c r="AO42" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -3068,21 +3058,21 @@
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
-      </c>
-      <c r="J43" s="4" t="s">
         <v>207</v>
       </c>
+      <c r="J43" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="AJ43" t="s">
         <v>48</v>
       </c>
       <c r="AO43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
         <v>43</v>
@@ -3091,10 +3081,10 @@
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>210</v>
-      </c>
-      <c r="J44" s="4" t="s">
         <v>211</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="AJ44" t="s">
         <v>48</v>
@@ -3102,7 +3092,7 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -3111,10 +3101,10 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>213</v>
-      </c>
-      <c r="J45" s="4" t="s">
         <v>214</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="AJ45" t="s">
         <v>48</v>
@@ -3125,7 +3115,7 @@
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
         <v>43</v>
@@ -3134,10 +3124,10 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>216</v>
-      </c>
-      <c r="J46" s="4" t="s">
         <v>217</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="AJ46" t="s">
         <v>48</v>
@@ -3148,7 +3138,7 @@
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
         <v>43</v>
@@ -3157,10 +3147,10 @@
         <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>219</v>
-      </c>
-      <c r="J47" s="4" t="s">
         <v>220</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="AJ47" t="s">
         <v>48</v>
@@ -3171,7 +3161,7 @@
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
         <v>43</v>
@@ -3180,10 +3170,10 @@
         <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
-      </c>
-      <c r="J48" s="4" t="s">
         <v>223</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="AJ48" t="s">
         <v>48</v>
@@ -3200,10 +3190,10 @@
         <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
-      </c>
-      <c r="J49" s="4" t="s">
         <v>225</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="P49" t="s">
         <v>100</v>
@@ -3226,10 +3216,10 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
-      </c>
-      <c r="J50" s="4" t="s">
         <v>227</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="Q50" t="s">
         <v>60</v>
@@ -3240,7 +3230,7 @@
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
         <v>43</v>
@@ -3249,21 +3239,21 @@
         <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>229</v>
-      </c>
-      <c r="J51" s="4" t="s">
         <v>230</v>
       </c>
+      <c r="J51" s="2" t="s">
+        <v>231</v>
+      </c>
       <c r="AJ51" t="s">
         <v>48</v>
       </c>
       <c r="AO51" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -3272,16 +3262,16 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
-      </c>
-      <c r="J52" s="4" t="s">
         <v>234</v>
       </c>
+      <c r="J52" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="S52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AJ52" t="s">
         <v>48</v>
@@ -3289,7 +3279,7 @@
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s">
         <v>43</v>
@@ -3298,13 +3288,13 @@
         <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>236</v>
-      </c>
-      <c r="J53" s="4" t="s">
         <v>237</v>
       </c>
+      <c r="J53" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="R53" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S53" t="s">
         <v>164</v>
@@ -3313,12 +3303,12 @@
         <v>48</v>
       </c>
       <c r="AO53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
         <v>43</v>
@@ -3327,10 +3317,10 @@
         <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
-      </c>
-      <c r="J54" s="4" t="s">
         <v>242</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="AJ54" t="s">
         <v>48</v>
@@ -3341,7 +3331,7 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B55" t="s">
         <v>43</v>
@@ -3350,18 +3340,18 @@
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>244</v>
-      </c>
-      <c r="J55" s="4" t="s">
         <v>245</v>
       </c>
+      <c r="J55" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="AO55" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s">
         <v>43</v>
@@ -3370,10 +3360,10 @@
         <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>248</v>
-      </c>
-      <c r="J56" s="4" t="s">
         <v>249</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="AJ56" t="s">
         <v>48</v>
@@ -3384,7 +3374,7 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s">
         <v>43</v>
@@ -3393,10 +3383,10 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>251</v>
-      </c>
-      <c r="J57" s="4" t="s">
         <v>252</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="AJ57" t="s">
         <v>48</v>
@@ -3407,7 +3397,7 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s">
         <v>43</v>
@@ -3416,10 +3406,10 @@
         <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
-      </c>
-      <c r="J58" s="4" t="s">
         <v>255</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="AJ58" t="s">
         <v>48</v>
@@ -3430,7 +3420,7 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B59" t="s">
         <v>43</v>
@@ -3439,18 +3429,18 @@
         <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>257</v>
-      </c>
-      <c r="J59" s="4" t="s">
         <v>258</v>
       </c>
+      <c r="J59" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="AO59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s">
         <v>43</v>
@@ -3459,10 +3449,10 @@
         <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>260</v>
-      </c>
-      <c r="J60" s="4" t="s">
         <v>261</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="AJ60" t="s">
         <v>48</v>
@@ -3473,7 +3463,7 @@
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s">
         <v>43</v>
@@ -3482,24 +3472,24 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>263</v>
-      </c>
-      <c r="J61" s="4" t="s">
         <v>264</v>
       </c>
+      <c r="J61" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="S61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AJ61" t="s">
         <v>48</v>
       </c>
       <c r="AO61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
@@ -3508,24 +3498,24 @@
         <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>267</v>
-      </c>
-      <c r="J62" s="4" t="s">
         <v>268</v>
       </c>
+      <c r="J62" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="S62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AJ62" t="s">
         <v>48</v>
       </c>
       <c r="AO62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -3534,21 +3524,21 @@
         <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>272</v>
-      </c>
-      <c r="J63" s="4" t="s">
         <v>273</v>
       </c>
+      <c r="J63" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="AJ63" t="s">
         <v>48</v>
       </c>
       <c r="AO63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s">
         <v>43</v>
@@ -3557,10 +3547,10 @@
         <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>275</v>
-      </c>
-      <c r="J64" s="4" t="s">
         <v>276</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="AJ64" t="s">
         <v>48</v>
@@ -3571,7 +3561,7 @@
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -3580,10 +3570,10 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>278</v>
-      </c>
-      <c r="J65" s="4" t="s">
         <v>279</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="AJ65" t="s">
         <v>48</v>
@@ -3594,7 +3584,7 @@
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B66" t="s">
         <v>43</v>
@@ -3603,10 +3593,10 @@
         <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>281</v>
-      </c>
-      <c r="J66" s="4" t="s">
         <v>282</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="AJ66" t="s">
         <v>48</v>
@@ -3617,7 +3607,7 @@
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
@@ -3626,21 +3616,21 @@
         <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>284</v>
-      </c>
-      <c r="J67" s="4" t="s">
         <v>285</v>
       </c>
+      <c r="J67" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="AJ67" t="s">
         <v>48</v>
       </c>
       <c r="AO67" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
@@ -3649,16 +3639,16 @@
         <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>286</v>
-      </c>
-      <c r="J68" s="4" t="s">
         <v>287</v>
       </c>
+      <c r="J68" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="Q68" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AJ68" t="s">
         <v>48</v>
@@ -3666,7 +3656,7 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -3675,10 +3665,10 @@
         <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>290</v>
-      </c>
-      <c r="J69" s="4" t="s">
         <v>291</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="AJ69" t="s">
         <v>48</v>
@@ -3689,7 +3679,7 @@
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s">
         <v>43</v>
@@ -3698,10 +3688,10 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>293</v>
-      </c>
-      <c r="J70" s="4" t="s">
         <v>294</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="R70" t="s">
         <v>115</v>
@@ -3712,7 +3702,7 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B71" t="s">
         <v>43</v>
@@ -3721,10 +3711,10 @@
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>296</v>
-      </c>
-      <c r="J71" s="4" t="s">
         <v>297</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="W71" t="s">
         <v>99</v>
@@ -3733,12 +3723,12 @@
         <v>48</v>
       </c>
       <c r="AO71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -3747,16 +3737,16 @@
         <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>298</v>
-      </c>
-      <c r="J72" s="4" t="s">
         <v>299</v>
       </c>
+      <c r="J72" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="S72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AJ72" t="s">
         <v>48</v>
@@ -3764,7 +3754,7 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -3773,24 +3763,24 @@
         <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>302</v>
-      </c>
-      <c r="J73" s="4" t="s">
         <v>303</v>
       </c>
+      <c r="J73" s="2" t="s">
+        <v>304</v>
+      </c>
       <c r="S73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AJ73" t="s">
         <v>48</v>
       </c>
       <c r="AO73" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s">
         <v>43</v>
@@ -3799,10 +3789,10 @@
         <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>305</v>
-      </c>
-      <c r="J74" s="4" t="s">
         <v>306</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="AJ74" t="s">
         <v>48</v>
@@ -3813,7 +3803,7 @@
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B75" t="s">
         <v>43</v>
@@ -3822,10 +3812,10 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
-      </c>
-      <c r="J75" s="4" t="s">
         <v>309</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="AJ75" t="s">
         <v>48</v>
@@ -3836,7 +3826,7 @@
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
         <v>43</v>
@@ -3845,13 +3835,13 @@
         <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>310</v>
-      </c>
-      <c r="J76" s="4" t="s">
         <v>311</v>
       </c>
+      <c r="J76" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="R76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S76" t="s">
         <v>164</v>
@@ -3860,12 +3850,12 @@
         <v>48</v>
       </c>
       <c r="AO76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B77" t="s">
         <v>43</v>
@@ -3874,21 +3864,21 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>313</v>
-      </c>
-      <c r="J77" s="4" t="s">
         <v>314</v>
       </c>
+      <c r="J77" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="AJ77" t="s">
         <v>48</v>
       </c>
       <c r="AO77" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B78" t="s">
         <v>43</v>
@@ -3897,10 +3887,10 @@
         <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>316</v>
-      </c>
-      <c r="J78" s="4" t="s">
         <v>317</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="L78" t="s">
         <v>88</v>
@@ -3909,12 +3899,12 @@
         <v>48</v>
       </c>
       <c r="AO78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s">
         <v>43</v>
@@ -3923,10 +3913,10 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>319</v>
-      </c>
-      <c r="J79" s="4" t="s">
         <v>320</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="AJ79" t="s">
         <v>48</v>
@@ -3937,7 +3927,7 @@
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
         <v>43</v>
@@ -3946,13 +3936,13 @@
         <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>322</v>
-      </c>
-      <c r="J80" s="4" t="s">
         <v>323</v>
       </c>
+      <c r="J80" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="S80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AJ80" t="s">
         <v>48</v>
@@ -3963,7 +3953,7 @@
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B81" t="s">
         <v>43</v>
@@ -3972,10 +3962,10 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>325</v>
-      </c>
-      <c r="J81" s="4" t="s">
         <v>326</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="AJ81" t="s">
         <v>48</v>
@@ -3986,7 +3976,7 @@
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B82" t="s">
         <v>43</v>
@@ -3995,10 +3985,10 @@
         <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>328</v>
-      </c>
-      <c r="J82" s="4" t="s">
         <v>329</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="R82" t="s">
         <v>105</v>
@@ -4007,12 +3997,12 @@
         <v>48</v>
       </c>
       <c r="AO82" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s">
         <v>43</v>
@@ -4021,24 +4011,24 @@
         <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>332</v>
-      </c>
-      <c r="J83" s="4" t="s">
         <v>333</v>
       </c>
+      <c r="J83" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="L83" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AJ83" t="s">
         <v>48</v>
       </c>
       <c r="AO83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s">
         <v>43</v>
@@ -4047,10 +4037,10 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>336</v>
-      </c>
-      <c r="J84" s="4" t="s">
         <v>337</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="AJ84" t="s">
         <v>48</v>
@@ -4061,7 +4051,7 @@
     </row>
     <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
         <v>43</v>
@@ -4070,10 +4060,10 @@
         <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
-      </c>
-      <c r="J85" s="4" t="s">
         <v>340</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="AJ85" t="s">
         <v>48</v>
@@ -4084,19 +4074,19 @@
     </row>
     <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>342</v>
+      </c>
+      <c r="B86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" t="s">
+        <v>343</v>
+      </c>
+      <c r="J86" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="B86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" t="s">
-        <v>342</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="AJ86" t="s">
         <v>48</v>
@@ -4107,7 +4097,7 @@
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -4116,13 +4106,13 @@
         <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
-      </c>
-      <c r="J87" s="4" t="s">
         <v>345</v>
       </c>
+      <c r="J87" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="P87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AJ87" t="s">
         <v>48</v>
@@ -4130,7 +4120,7 @@
     </row>
     <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -4139,10 +4129,10 @@
         <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
-      </c>
-      <c r="J88" s="4" t="s">
         <v>348</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="AJ88" t="s">
         <v>48</v>
@@ -4153,7 +4143,7 @@
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -4162,21 +4152,21 @@
         <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>350</v>
-      </c>
-      <c r="J89" s="4" t="s">
         <v>351</v>
       </c>
+      <c r="J89" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AJ89" t="s">
         <v>48</v>
       </c>
       <c r="AO89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -4185,10 +4175,10 @@
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
-      </c>
-      <c r="J90" s="4" t="s">
         <v>354</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="W90" t="s">
         <v>105</v>
@@ -4202,7 +4192,7 @@
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -4211,10 +4201,10 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>356</v>
-      </c>
-      <c r="J91" s="4" t="s">
         <v>357</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="AJ91" t="s">
         <v>48</v>
@@ -4225,7 +4215,7 @@
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -4234,10 +4224,10 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
-      </c>
-      <c r="J92" s="4" t="s">
         <v>360</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="W92" t="s">
         <v>105</v>
@@ -4251,7 +4241,7 @@
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -4260,10 +4250,10 @@
         <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>362</v>
-      </c>
-      <c r="J93" s="4" t="s">
         <v>363</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="AJ93" t="s">
         <v>48</v>
@@ -4274,7 +4264,7 @@
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -4283,10 +4273,10 @@
         <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>365</v>
-      </c>
-      <c r="J94" s="4" t="s">
         <v>366</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="AJ94" t="s">
         <v>48</v>
@@ -4297,7 +4287,7 @@
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -4306,21 +4296,21 @@
         <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>368</v>
-      </c>
-      <c r="J95" s="4" t="s">
         <v>369</v>
       </c>
+      <c r="J95" s="2" t="s">
+        <v>370</v>
+      </c>
       <c r="AJ95" t="s">
         <v>48</v>
       </c>
       <c r="AO95" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -4329,10 +4319,10 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>371</v>
-      </c>
-      <c r="J96" s="4" t="s">
         <v>372</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="AJ96" t="s">
         <v>48</v>
@@ -4343,7 +4333,7 @@
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -4352,10 +4342,10 @@
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>374</v>
-      </c>
-      <c r="J97" s="4" t="s">
         <v>375</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="AJ97" t="s">
         <v>48</v>
@@ -4366,7 +4356,7 @@
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -4375,24 +4365,24 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>377</v>
-      </c>
-      <c r="J98" s="4" t="s">
         <v>378</v>
       </c>
+      <c r="J98" s="2" t="s">
+        <v>379</v>
+      </c>
       <c r="R98" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ98" t="s">
         <v>48</v>
       </c>
       <c r="AO98" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -4401,13 +4391,13 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>380</v>
-      </c>
-      <c r="J99" s="4" t="s">
         <v>381</v>
       </c>
+      <c r="J99" s="2" t="s">
+        <v>382</v>
+      </c>
       <c r="R99" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="W99" t="s">
         <v>105</v>
@@ -4421,7 +4411,7 @@
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -4430,10 +4420,10 @@
         <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>383</v>
-      </c>
-      <c r="J100" s="4" t="s">
         <v>384</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>385</v>
       </c>
       <c r="S100" t="s">
         <v>164</v>
@@ -4444,7 +4434,7 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -4453,10 +4443,10 @@
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>386</v>
-      </c>
-      <c r="J101" s="4" t="s">
         <v>387</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="AJ101" t="s">
         <v>48</v>
@@ -4467,7 +4457,7 @@
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -4476,10 +4466,10 @@
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>389</v>
-      </c>
-      <c r="J102" s="4" t="s">
         <v>390</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="AJ102" t="s">
         <v>48</v>
@@ -4490,7 +4480,7 @@
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -4499,10 +4489,10 @@
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>392</v>
-      </c>
-      <c r="J103" s="4" t="s">
         <v>393</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="W103" t="s">
         <v>105</v>
@@ -4511,12 +4501,12 @@
         <v>48</v>
       </c>
       <c r="AO103" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -4525,10 +4515,10 @@
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>396</v>
-      </c>
-      <c r="J104" s="4" t="s">
         <v>397</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>398</v>
       </c>
       <c r="AJ104" t="s">
         <v>48</v>
@@ -4539,7 +4529,7 @@
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -4548,10 +4538,10 @@
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
-      </c>
-      <c r="J105" s="4" t="s">
         <v>400</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>401</v>
       </c>
       <c r="AJ105" t="s">
         <v>48</v>
@@ -4562,7 +4552,7 @@
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -4571,21 +4561,21 @@
         <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>402</v>
-      </c>
-      <c r="J106" s="4" t="s">
         <v>403</v>
       </c>
+      <c r="J106" s="2" t="s">
+        <v>404</v>
+      </c>
       <c r="AJ106" t="s">
         <v>48</v>
       </c>
       <c r="AO106" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -4594,10 +4584,10 @@
         <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>405</v>
-      </c>
-      <c r="J107" s="4" t="s">
         <v>406</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="AJ107" t="s">
         <v>48</v>
@@ -4608,7 +4598,7 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -4617,10 +4607,10 @@
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>408</v>
-      </c>
-      <c r="J108" s="4" t="s">
         <v>409</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>410</v>
       </c>
       <c r="AJ108" t="s">
         <v>48</v>
@@ -4640,30 +4630,30 @@
         <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>410</v>
-      </c>
-      <c r="J109" s="4" t="s">
         <v>411</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>412</v>
       </c>
       <c r="L109" t="s">
         <v>88</v>
       </c>
       <c r="R109" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T109" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AJ109" t="s">
         <v>48</v>
       </c>
       <c r="AO109" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -4672,13 +4662,13 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E110" t="s">
-        <v>416</v>
-      </c>
-      <c r="J110" s="4" t="s">
         <v>417</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="R110" t="s">
         <v>164</v>
@@ -4689,7 +4679,7 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -4698,10 +4688,10 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>419</v>
-      </c>
-      <c r="J111" s="4" t="s">
         <v>420</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="AJ111" t="s">
         <v>48</v>
@@ -4712,7 +4702,7 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -4721,18 +4711,18 @@
         <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>422</v>
-      </c>
-      <c r="J112" s="4" t="s">
         <v>423</v>
       </c>
+      <c r="J112" s="2" t="s">
+        <v>424</v>
+      </c>
       <c r="AI112" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -4741,16 +4731,16 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>425</v>
-      </c>
-      <c r="J113" s="4" t="s">
         <v>426</v>
       </c>
+      <c r="J113" s="2" t="s">
+        <v>427</v>
+      </c>
       <c r="Q113" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T113" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AJ113" t="s">
         <v>48</v>
@@ -4758,7 +4748,7 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -4767,10 +4757,10 @@
         <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>429</v>
-      </c>
-      <c r="J114" s="4" t="s">
         <v>430</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="W114" t="s">
         <v>47</v>
@@ -4779,12 +4769,12 @@
         <v>48</v>
       </c>
       <c r="AO114" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -4793,16 +4783,16 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>433</v>
-      </c>
-      <c r="J115" s="4" t="s">
         <v>434</v>
       </c>
+      <c r="J115" s="2" t="s">
+        <v>435</v>
+      </c>
       <c r="AJ115" t="s">
         <v>48</v>
       </c>
       <c r="AO115" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4812,22 +4802,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4825,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4836,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" t="s">
         <v>440</v>
-      </c>
-      <c r="C3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4847,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" t="s">
         <v>440</v>
-      </c>
-      <c r="C4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4858,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4869,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4880,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4891,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,10 +4902,10 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4923,10 +4913,10 @@
         <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4924,10 @@
         <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4935,10 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4946,10 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13" t="s">
         <v>440</v>
-      </c>
-      <c r="C13" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4957,10 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
+        <v>441</v>
+      </c>
+      <c r="C14" t="s">
         <v>440</v>
-      </c>
-      <c r="C14" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,10 +4968,10 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" t="s">
         <v>440</v>
-      </c>
-      <c r="C15" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,10 +4979,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
+        <v>441</v>
+      </c>
+      <c r="C16" t="s">
         <v>440</v>
-      </c>
-      <c r="C16" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5000,10 +4990,10 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,10 +5001,10 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,10 +5012,10 @@
         <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C19" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5023,10 @@
         <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,10 +5034,10 @@
         <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5055,10 +5045,10 @@
         <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C22" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5066,10 +5056,10 @@
         <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,10 +5067,54 @@
         <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C24" t="s">
-        <v>446</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>441</v>
+      </c>
+      <c r="C25" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>441</v>
+      </c>
+      <c r="C26" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>441</v>
+      </c>
+      <c r="C27" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>441</v>
+      </c>
+      <c r="C28" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -5090,22 +5124,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,10 +5147,10 @@
         <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +5158,10 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,10 +5169,10 @@
         <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,10 +5180,10 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,10 +5191,10 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,10 +5202,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,10 +5213,10 @@
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,10 +5224,10 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5201,10 +5235,10 @@
         <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -5212,10 +5246,10 @@
         <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -5223,10 +5257,10 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5234,10 +5268,10 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -5245,10 +5279,10 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -5256,10 +5290,10 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -5267,10 +5301,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -5278,10 +5312,10 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5289,10 +5323,10 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5300,10 +5334,10 @@
         <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -5311,10 +5345,10 @@
         <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5322,10 +5356,10 @@
         <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C21" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5333,10 +5367,10 @@
         <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5344,10 +5378,10 @@
         <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5355,10 +5389,54 @@
         <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C24" t="s">
-        <v>452</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" t="s">
+        <v>465</v>
+      </c>
+      <c r="C25" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>457</v>
+      </c>
+      <c r="C26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>457</v>
+      </c>
+      <c r="C27" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>462</v>
+      </c>
+      <c r="C28" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -5373,107 +5451,107 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" t="s">
         <v>474</v>
-      </c>
-      <c r="B3" t="s">
-        <v>475</v>
-      </c>
-      <c r="C3" t="s">
-        <v>476</v>
-      </c>
-      <c r="D3" t="s">
-        <v>477</v>
-      </c>
-      <c r="E3" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" t="s">
+        <v>478</v>
+      </c>
+      <c r="E4" t="s">
         <v>474</v>
-      </c>
-      <c r="B4" t="s">
-        <v>478</v>
-      </c>
-      <c r="C4" t="s">
-        <v>476</v>
-      </c>
-      <c r="D4" t="s">
-        <v>477</v>
-      </c>
-      <c r="E4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E5" t="s">
         <v>474</v>
-      </c>
-      <c r="B5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C5" t="s">
-        <v>476</v>
-      </c>
-      <c r="D5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E5" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B6" t="s">
         <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
